--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="91">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -310,6 +310,12 @@
   </si>
   <si>
     <t>disfraces roci</t>
+  </si>
+  <si>
+    <t>circo</t>
+  </si>
+  <si>
+    <t>gas y calefacción</t>
   </si>
 </sst>
 </file>
@@ -1537,7 +1543,7 @@
         <v>15700</v>
       </c>
       <c r="E7" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F7" s="1">
         <v>27000</v>
@@ -1558,7 +1564,7 @@
         <v>23200</v>
       </c>
       <c r="L7" s="1">
-        <v>7500</v>
+        <v>7505</v>
       </c>
       <c r="M7" s="1">
         <v>25000</v>
@@ -1605,7 +1611,7 @@
       <c r="AB7" s="6"/>
       <c r="AC7" s="1">
         <f t="shared" si="0"/>
-        <v>175829</v>
+        <v>176334</v>
       </c>
       <c r="AD7" s="7">
         <f t="shared" si="1"/>
@@ -1623,15 +1629,15 @@
       </c>
       <c r="AH7" s="8">
         <f t="shared" si="3"/>
-        <v>62914.5</v>
+        <v>63167</v>
       </c>
       <c r="AI7" s="9">
         <f t="shared" si="4"/>
-        <v>72214.5</v>
+        <v>72467</v>
       </c>
       <c r="AJ7" s="10">
         <f t="shared" si="5"/>
-        <v>135129</v>
+        <v>135634</v>
       </c>
     </row>
     <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2051,9 +2057,6 @@
       <c r="AA13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC13" s="1" t="s">
-        <v>29</v>
-      </c>
     </row>
     <row r="14" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -2163,10 +2166,6 @@
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
         <v>4705.57</v>
       </c>
-      <c r="AC14" s="1" t="str">
-        <f>IF(Mayo!AB33&gt;0,Mayo!AB33,"")</f>
-        <v/>
-      </c>
     </row>
     <row r="15" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -2276,10 +2275,6 @@
         <f>IF(Junio!AB32&gt;0,Junio!AB32,"")</f>
         <v>21845.239999999998</v>
       </c>
-      <c r="AC15" s="1">
-        <f>IF(Junio!AC32&gt;0,Junio!AC32,"")</f>
-        <v>17322.899999999998</v>
-      </c>
     </row>
     <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -2389,10 +2384,6 @@
         <f>IF(Julio!AA33&gt;0,Julio!AA33,"")</f>
         <v>5000</v>
       </c>
-      <c r="AC16" s="1" t="str">
-        <f>IF(Julio!AB33&gt;0,Julio!AB33,"")</f>
-        <v/>
-      </c>
     </row>
     <row r="17" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -2502,10 +2493,6 @@
         <f>IF(Agosto!AA33&gt;0,Agosto!AA33,"")</f>
         <v>6388.06</v>
       </c>
-      <c r="AC17" s="1" t="str">
-        <f>IF(Agosto!AB33&gt;0,Agosto!AB33,"")</f>
-        <v/>
-      </c>
     </row>
     <row r="18" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -2547,13 +2534,13 @@
         <f>IF(Setiembre!J32&gt;0,Setiembre!J32,"")</f>
         <v/>
       </c>
-      <c r="K18" s="1" t="str">
+      <c r="K18" s="1">
         <f>IF(Setiembre!K32&gt;0,Setiembre!K32,"")</f>
-        <v/>
-      </c>
-      <c r="L18" s="1" t="str">
+        <v>23112.77</v>
+      </c>
+      <c r="L18" s="1">
         <f>IF(Setiembre!L32&gt;0,Setiembre!L32,"")</f>
-        <v/>
+        <v>7502.34</v>
       </c>
       <c r="M18" s="1" t="str">
         <f>IF(Setiembre!M32&gt;0,Setiembre!M32,"")</f>
@@ -2577,7 +2564,7 @@
       </c>
       <c r="R18" s="1">
         <f>IF(Setiembre!R32&gt;0,Setiembre!R32,"")</f>
-        <v>3616.7999999999997</v>
+        <v>5888.6799999999994</v>
       </c>
       <c r="S18" s="1" t="str">
         <f>IF(Setiembre!S32&gt;0,Setiembre!S32,"")</f>
@@ -2595,9 +2582,9 @@
         <f>IF(Setiembre!V32&gt;0,Setiembre!V32,"")</f>
         <v/>
       </c>
-      <c r="W18" s="1" t="str">
+      <c r="W18" s="1">
         <f>IF(Setiembre!W32&gt;0,Setiembre!W32,"")</f>
-        <v/>
+        <v>1947.54</v>
       </c>
       <c r="X18" s="1" t="str">
         <f>IF(Setiembre!X32&gt;0,Setiembre!X32,"")</f>
@@ -2611,13 +2598,9 @@
         <f>IF(Setiembre!Z32&gt;0,Setiembre!Z32,"")</f>
         <v/>
       </c>
-      <c r="AA18" s="1" t="str">
+      <c r="AA18" s="1">
         <f>IF(Setiembre!AA32&gt;0,Setiembre!AA32,"")</f>
-        <v/>
-      </c>
-      <c r="AC18" s="1" t="str">
-        <f>IF(Setiembre!AB32&gt;0,Setiembre!AB32,"")</f>
-        <v/>
+        <v>1901.1299999999999</v>
       </c>
     </row>
     <row r="19" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2728,10 +2711,6 @@
         <f>IF(Octubre!AA33&gt;0,Octubre!AA33,"")</f>
         <v/>
       </c>
-      <c r="AC19" s="1" t="str">
-        <f>IF(Octubre!AB33&gt;0,Octubre!AB33,"")</f>
-        <v/>
-      </c>
     </row>
     <row r="20" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -2841,10 +2820,6 @@
         <f>IF(Noviembre!AA32&gt;0,Noviembre!AA32,"")</f>
         <v/>
       </c>
-      <c r="AC20" s="1" t="str">
-        <f>IF(Noviembre!AB32&gt;0,Noviembre!AB32,"")</f>
-        <v/>
-      </c>
     </row>
     <row r="21" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
@@ -2952,10 +2927,6 @@
       </c>
       <c r="AA21" s="1" t="str">
         <f>IF(Diciembre!AA33&gt;0,Diciembre!AA33,"")</f>
-        <v/>
-      </c>
-      <c r="AC21" s="1" t="str">
-        <f>IF(Diciembre!AB33&gt;0,Diciembre!AB33,"")</f>
         <v/>
       </c>
     </row>
@@ -3547,7 +3518,7 @@
       </c>
       <c r="E29" s="1">
         <f>IF(ISNUMBER(Setiembre!E32),E7-Setiembre!E32,"")</f>
-        <v>-498</v>
+        <v>2</v>
       </c>
       <c r="F29" s="1">
         <f>IF(ISNUMBER(Setiembre!F32),F7-Setiembre!F32,"")</f>
@@ -3569,13 +3540,13 @@
         <f>IF(ISNUMBER(Setiembre!J32),J7-Setiembre!J32,"")</f>
         <v/>
       </c>
-      <c r="K29" s="1" t="str">
+      <c r="K29" s="1">
         <f>IF(ISNUMBER(Setiembre!K32),K7-Setiembre!K32,"")</f>
-        <v/>
-      </c>
-      <c r="L29" s="1" t="str">
+        <v>87.229999999999563</v>
+      </c>
+      <c r="L29" s="1">
         <f>IF(ISNUMBER(Setiembre!L32),L7-Setiembre!L32,"")</f>
-        <v/>
+        <v>2.6599999999998545</v>
       </c>
       <c r="M29" s="1" t="str">
         <f>IF(ISNUMBER(Setiembre!M32),M7-Setiembre!M32,"")</f>
@@ -3599,7 +3570,7 @@
       </c>
       <c r="R29" s="1">
         <f>IF(ISNUMBER(Setiembre!R32),R7-Setiembre!R32,"")</f>
-        <v>15383.2</v>
+        <v>13111.32</v>
       </c>
       <c r="S29" s="1" t="str">
         <f>IF(ISNUMBER(Setiembre!S32),S7-Setiembre!S32,"")</f>
@@ -3617,9 +3588,9 @@
         <f>IF(ISNUMBER(Setiembre!V32),V7-Setiembre!V32,"")</f>
         <v/>
       </c>
-      <c r="W29" s="1" t="str">
+      <c r="W29" s="1">
         <f>IF(ISNUMBER(Setiembre!W32),W7-Setiembre!W32,"")</f>
-        <v/>
+        <v>1052.46</v>
       </c>
       <c r="X29" s="1" t="str">
         <f>IF(ISNUMBER(Setiembre!X32),X7-Setiembre!X32,"")</f>
@@ -3633,13 +3604,13 @@
         <f>IF(ISNUMBER(Setiembre!Z32),Z7-Setiembre!Z32,"")</f>
         <v/>
       </c>
-      <c r="AA29" s="1" t="str">
+      <c r="AA29" s="1">
         <f>IF(ISNUMBER(Setiembre!AA32),AA7-Setiembre!AA32,"")</f>
-        <v/>
+        <v>3098.87</v>
       </c>
       <c r="AC29" s="12">
         <f t="shared" si="7"/>
-        <v>15164.09</v>
+        <v>17633.429999999997</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3999,7 +3970,7 @@
       </c>
       <c r="E33" s="12">
         <f t="shared" si="8"/>
-        <v>-858.81999999999971</v>
+        <v>-358.81999999999971</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" si="8"/>
@@ -4023,11 +3994,11 @@
       </c>
       <c r="K33" s="12">
         <f t="shared" si="8"/>
-        <v>14.069999999998345</v>
+        <v>101.29999999999791</v>
       </c>
       <c r="L33" s="12">
         <f t="shared" si="8"/>
-        <v>329.53999999999724</v>
+        <v>332.19999999999709</v>
       </c>
       <c r="M33" s="12">
         <f t="shared" si="8"/>
@@ -4051,7 +4022,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>19701.07</v>
+        <v>17429.189999999999</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4071,7 +4042,7 @@
       </c>
       <c r="W33" s="12">
         <f t="shared" si="8"/>
-        <v>1731.1399999999999</v>
+        <v>2783.6</v>
       </c>
       <c r="X33" s="12">
         <f t="shared" si="8"/>
@@ -4087,11 +4058,11 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>-17938.87</v>
+        <v>-14840</v>
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>3679.1499999999978</v>
+        <v>6148.4899999999943</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10478,7 +10449,7 @@
         <v>25</v>
       </c>
       <c r="Z1" s="33" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AA1" s="33" t="s">
         <v>27</v>
@@ -10647,7 +10618,10 @@
       <c r="O5" s="35"/>
       <c r="P5" s="35"/>
       <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
+      <c r="R5" s="35">
+        <f>263-19.4+177+0.14-3.22</f>
+        <v>417.52</v>
+      </c>
       <c r="S5" s="35"/>
       <c r="T5" s="35"/>
       <c r="U5" s="35"/>
@@ -10656,11 +10630,13 @@
       <c r="X5" s="35"/>
       <c r="Y5" s="35"/>
       <c r="Z5" s="35"/>
-      <c r="AA5" s="35"/>
+      <c r="AA5" s="35">
+        <v>42</v>
+      </c>
       <c r="AB5" s="36"/>
       <c r="AC5" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>459.52</v>
       </c>
       <c r="AD5" s="35"/>
     </row>
@@ -10677,14 +10653,19 @@
       <c r="H6" s="35"/>
       <c r="I6" s="35"/>
       <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
+      <c r="K6" s="35">
+        <v>23112.77</v>
+      </c>
       <c r="L6" s="35"/>
       <c r="M6" s="35"/>
       <c r="N6" s="35"/>
       <c r="O6" s="35"/>
       <c r="P6" s="35"/>
       <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
+      <c r="R6" s="35">
+        <f>542-7.64+587-9.62</f>
+        <v>1111.7400000000002</v>
+      </c>
       <c r="S6" s="35"/>
       <c r="T6" s="35"/>
       <c r="U6" s="35"/>
@@ -10693,13 +10674,17 @@
       <c r="X6" s="35"/>
       <c r="Y6" s="35"/>
       <c r="Z6" s="35"/>
-      <c r="AA6" s="35"/>
+      <c r="AA6" s="35">
+        <v>300</v>
+      </c>
       <c r="AB6" s="36"/>
       <c r="AC6" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD6" s="35"/>
+        <v>24524.510000000002</v>
+      </c>
+      <c r="AD6" s="35" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34">
@@ -10715,26 +10700,38 @@
       <c r="I7" s="35"/>
       <c r="J7" s="35"/>
       <c r="K7" s="35"/>
-      <c r="L7" s="35"/>
+      <c r="L7" s="35">
+        <f>7245.67+256.67</f>
+        <v>7502.34</v>
+      </c>
       <c r="M7" s="35"/>
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="35"/>
       <c r="Q7" s="35"/>
-      <c r="R7" s="35"/>
+      <c r="R7" s="35">
+        <f>755-12.38</f>
+        <v>742.62</v>
+      </c>
       <c r="S7" s="35"/>
       <c r="T7" s="35"/>
       <c r="U7" s="35"/>
       <c r="V7" s="35"/>
-      <c r="W7" s="35"/>
+      <c r="W7" s="35">
+        <f>1980-32.46</f>
+        <v>1947.54</v>
+      </c>
       <c r="X7" s="35"/>
       <c r="Y7" s="35"/>
       <c r="Z7" s="35"/>
-      <c r="AA7" s="35"/>
+      <c r="AA7" s="35">
+        <f>320-5.45+1244.58</f>
+        <v>1559.1299999999999</v>
+      </c>
       <c r="AB7" s="36"/>
       <c r="AC7" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11751.63</v>
       </c>
       <c r="AD7" s="35"/>
     </row>
@@ -11666,13 +11663,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="K32" s="12">
+        <f t="shared" si="1"/>
+        <v>23112.77</v>
+      </c>
+      <c r="L32" s="12">
+        <f t="shared" si="1"/>
+        <v>7502.34</v>
       </c>
       <c r="M32" s="12" t="str">
         <f t="shared" si="1"/>
@@ -11696,7 +11693,7 @@
       </c>
       <c r="R32" s="12">
         <f t="shared" si="1"/>
-        <v>3616.7999999999997</v>
+        <v>5888.6799999999994</v>
       </c>
       <c r="S32" s="12" t="str">
         <f t="shared" si="1"/>
@@ -11714,9 +11711,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="W32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="W32" s="12">
+        <f t="shared" si="1"/>
+        <v>1947.54</v>
       </c>
       <c r="X32" s="12" t="str">
         <f t="shared" si="1"/>
@@ -11730,9 +11727,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AA32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="AA32" s="12">
+        <f t="shared" si="1"/>
+        <v>1901.1299999999999</v>
       </c>
       <c r="AB32" s="38" t="str">
         <f t="shared" si="1"/>
@@ -11740,7 +11737,7 @@
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>
-        <v>39685.910000000003</v>
+        <v>76421.570000000007</v>
       </c>
       <c r="AD32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -1591,7 +1591,7 @@
         <v>5000</v>
       </c>
       <c r="U7" s="1">
-        <v>12500</v>
+        <v>13115</v>
       </c>
       <c r="V7" s="1">
         <v>1500</v>
@@ -1611,7 +1611,7 @@
       <c r="AB7" s="6"/>
       <c r="AC7" s="1">
         <f t="shared" si="0"/>
-        <v>176334</v>
+        <v>176949</v>
       </c>
       <c r="AD7" s="7">
         <f t="shared" si="1"/>
@@ -1629,15 +1629,15 @@
       </c>
       <c r="AH7" s="8">
         <f t="shared" si="3"/>
-        <v>63167</v>
+        <v>63474.5</v>
       </c>
       <c r="AI7" s="9">
         <f t="shared" si="4"/>
-        <v>72467</v>
+        <v>72774.5</v>
       </c>
       <c r="AJ7" s="10">
         <f t="shared" si="5"/>
-        <v>135634</v>
+        <v>136249</v>
       </c>
     </row>
     <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2574,9 +2574,9 @@
         <f>IF(Setiembre!T32&gt;0,Setiembre!T32,"")</f>
         <v/>
       </c>
-      <c r="U18" s="1" t="str">
+      <c r="U18" s="1">
         <f>IF(Setiembre!U32&gt;0,Setiembre!U32,"")</f>
-        <v/>
+        <v>13110.49</v>
       </c>
       <c r="V18" s="1" t="str">
         <f>IF(Setiembre!V32&gt;0,Setiembre!V32,"")</f>
@@ -3580,9 +3580,9 @@
         <f>IF(ISNUMBER(Setiembre!T32),T7-Setiembre!T32,"")</f>
         <v/>
       </c>
-      <c r="U29" s="1" t="str">
+      <c r="U29" s="1">
         <f>IF(ISNUMBER(Setiembre!U32),U7-Setiembre!U32,"")</f>
-        <v/>
+        <v>4.5100000000002183</v>
       </c>
       <c r="V29" s="1" t="str">
         <f>IF(ISNUMBER(Setiembre!V32),V7-Setiembre!V32,"")</f>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="AC29" s="12">
         <f t="shared" si="7"/>
-        <v>17633.429999999997</v>
+        <v>17637.939999999999</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="U33" s="12">
         <f t="shared" si="8"/>
-        <v>614.75</v>
+        <v>619.26000000000022</v>
       </c>
       <c r="V33" s="12">
         <f t="shared" si="8"/>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>6148.4899999999943</v>
+        <v>6152.9999999999964</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10795,7 +10795,10 @@
       <c r="R9" s="35"/>
       <c r="S9" s="35"/>
       <c r="T9" s="35"/>
-      <c r="U9" s="35"/>
+      <c r="U9" s="35">
+        <f>13329-218.51</f>
+        <v>13110.49</v>
+      </c>
       <c r="V9" s="35"/>
       <c r="W9" s="35"/>
       <c r="X9" s="35"/>
@@ -10805,7 +10808,7 @@
       <c r="AB9" s="36"/>
       <c r="AC9" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13110.49</v>
       </c>
       <c r="AD9" s="35"/>
     </row>
@@ -11703,9 +11706,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="U32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="U32" s="12">
+        <f t="shared" si="1"/>
+        <v>13110.49</v>
       </c>
       <c r="V32" s="12" t="str">
         <f t="shared" si="1"/>
@@ -11737,7 +11740,7 @@
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>
-        <v>76421.570000000007</v>
+        <v>89532.060000000012</v>
       </c>
       <c r="AD32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -1540,7 +1540,7 @@
         <v>4369</v>
       </c>
       <c r="D7" s="1">
-        <v>15700</v>
+        <v>15706.32</v>
       </c>
       <c r="E7" s="1">
         <v>500</v>
@@ -1611,7 +1611,7 @@
       <c r="AB7" s="6"/>
       <c r="AC7" s="1">
         <f t="shared" si="0"/>
-        <v>176949</v>
+        <v>176955.32</v>
       </c>
       <c r="AD7" s="7">
         <f t="shared" si="1"/>
@@ -1629,11 +1629,11 @@
       </c>
       <c r="AH7" s="8">
         <f t="shared" si="3"/>
-        <v>63474.5</v>
+        <v>63477.66</v>
       </c>
       <c r="AI7" s="9">
         <f t="shared" si="4"/>
-        <v>72774.5</v>
+        <v>72771.34</v>
       </c>
       <c r="AJ7" s="10">
         <f t="shared" si="5"/>
@@ -2502,13 +2502,13 @@
         <f>IF(Setiembre!B32&gt;0,Setiembre!B32,"")</f>
         <v/>
       </c>
-      <c r="C18" s="1" t="str">
+      <c r="C18" s="1">
         <f>IF(Setiembre!C32&gt;0,Setiembre!C32,"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="1" t="str">
+        <v>4369</v>
+      </c>
+      <c r="D18" s="1">
         <f>IF(Setiembre!D32&gt;0,Setiembre!D32,"")</f>
-        <v/>
+        <v>15706.32</v>
       </c>
       <c r="E18" s="1">
         <f>IF(Setiembre!E32&gt;0,Setiembre!E32,"")</f>
@@ -2530,9 +2530,9 @@
         <f>IF(Setiembre!I32&gt;0,Setiembre!I32,"")</f>
         <v>3687.55</v>
       </c>
-      <c r="J18" s="1" t="str">
+      <c r="J18" s="1">
         <f>IF(Setiembre!J32&gt;0,Setiembre!J32,"")</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="K18" s="1">
         <f>IF(Setiembre!K32&gt;0,Setiembre!K32,"")</f>
@@ -2546,9 +2546,9 @@
         <f>IF(Setiembre!M32&gt;0,Setiembre!M32,"")</f>
         <v/>
       </c>
-      <c r="N18" s="1" t="str">
+      <c r="N18" s="1">
         <f>IF(Setiembre!N32&gt;0,Setiembre!N32,"")</f>
-        <v/>
+        <v>810</v>
       </c>
       <c r="O18" s="1" t="str">
         <f>IF(Setiembre!O32&gt;0,Setiembre!O32,"")</f>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="R18" s="1">
         <f>IF(Setiembre!R32&gt;0,Setiembre!R32,"")</f>
-        <v>5888.6799999999994</v>
+        <v>8482.99</v>
       </c>
       <c r="S18" s="1" t="str">
         <f>IF(Setiembre!S32&gt;0,Setiembre!S32,"")</f>
@@ -3508,13 +3508,13 @@
         <f>IF(ISNUMBER(Setiembre!B32),B8-Setiembre!B32,"")</f>
         <v/>
       </c>
-      <c r="C29" s="1" t="str">
+      <c r="C29" s="1">
         <f>IF(ISNUMBER(Setiembre!C32),C7-Setiembre!C32,"")</f>
-        <v/>
-      </c>
-      <c r="D29" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="D29" s="1">
         <f>IF(ISNUMBER(Setiembre!D32),D7-Setiembre!D32,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E29" s="1">
         <f>IF(ISNUMBER(Setiembre!E32),E7-Setiembre!E32,"")</f>
@@ -3536,9 +3536,9 @@
         <f>IF(ISNUMBER(Setiembre!I32),I7-Setiembre!I32,"")</f>
         <v>62.449999999999818</v>
       </c>
-      <c r="J29" s="1" t="str">
+      <c r="J29" s="1">
         <f>IF(ISNUMBER(Setiembre!J32),J7-Setiembre!J32,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
         <f>IF(ISNUMBER(Setiembre!K32),K7-Setiembre!K32,"")</f>
@@ -3552,9 +3552,9 @@
         <f>IF(ISNUMBER(Setiembre!M32),M7-Setiembre!M32,"")</f>
         <v/>
       </c>
-      <c r="N29" s="1" t="str">
+      <c r="N29" s="1">
         <f>IF(ISNUMBER(Setiembre!N32),N7-Setiembre!N32,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O29" s="1" t="str">
         <f>IF(ISNUMBER(Setiembre!O32),O7-Setiembre!O32,"")</f>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="R29" s="1">
         <f>IF(ISNUMBER(Setiembre!R32),R7-Setiembre!R32,"")</f>
-        <v>13111.32</v>
+        <v>10517.01</v>
       </c>
       <c r="S29" s="1" t="str">
         <f>IF(ISNUMBER(Setiembre!S32),S7-Setiembre!S32,"")</f>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="AC29" s="12">
         <f t="shared" si="7"/>
-        <v>17637.939999999999</v>
+        <v>15043.629999999997</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>17429.189999999999</v>
+        <v>14834.88</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>6152.9999999999964</v>
+        <v>3558.6899999999951</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10832,7 +10832,10 @@
       <c r="O10" s="35"/>
       <c r="P10" s="35"/>
       <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
+      <c r="R10" s="35">
+        <f>263-4.57+952-16.36</f>
+        <v>1194.0700000000002</v>
+      </c>
       <c r="S10" s="35"/>
       <c r="T10" s="35"/>
       <c r="U10" s="35"/>
@@ -10845,7 +10848,7 @@
       <c r="AB10" s="36"/>
       <c r="AC10" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1194.0700000000002</v>
       </c>
       <c r="AD10" s="35"/>
     </row>
@@ -10855,7 +10858,9 @@
       </c>
       <c r="B11" s="35"/>
       <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
+      <c r="D11" s="35">
+        <v>15706.32</v>
+      </c>
       <c r="E11" s="35"/>
       <c r="F11" s="35"/>
       <c r="G11" s="35"/>
@@ -10869,7 +10874,10 @@
       <c r="O11" s="35"/>
       <c r="P11" s="35"/>
       <c r="Q11" s="35"/>
-      <c r="R11" s="35"/>
+      <c r="R11" s="35">
+        <f>746+720-12.65-53.11</f>
+        <v>1400.24</v>
+      </c>
       <c r="S11" s="35"/>
       <c r="T11" s="35"/>
       <c r="U11" s="35"/>
@@ -10882,7 +10890,7 @@
       <c r="AB11" s="36"/>
       <c r="AC11" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17106.560000000001</v>
       </c>
       <c r="AD11" s="35"/>
     </row>
@@ -10891,18 +10899,24 @@
         <v>11</v>
       </c>
       <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
+      <c r="C12" s="35">
+        <v>4369</v>
+      </c>
       <c r="D12" s="35"/>
       <c r="E12" s="35"/>
       <c r="F12" s="35"/>
       <c r="G12" s="35"/>
       <c r="H12" s="35"/>
       <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
+      <c r="J12" s="35">
+        <v>1000</v>
+      </c>
       <c r="K12" s="35"/>
       <c r="L12" s="35"/>
       <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
+      <c r="N12" s="35">
+        <v>810</v>
+      </c>
       <c r="O12" s="35"/>
       <c r="P12" s="35"/>
       <c r="Q12" s="35"/>
@@ -10919,7 +10933,7 @@
       <c r="AB12" s="36"/>
       <c r="AC12" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6179</v>
       </c>
       <c r="AD12" s="35"/>
     </row>
@@ -11634,13 +11648,13 @@
         <f t="shared" ref="B32:AC32" si="1">IF(COUNTA(B2:B31)&gt;0,SUM(B2:B31),"")</f>
         <v/>
       </c>
-      <c r="C32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="C32" s="12">
+        <f t="shared" si="1"/>
+        <v>4369</v>
+      </c>
+      <c r="D32" s="12">
+        <f t="shared" si="1"/>
+        <v>15706.32</v>
       </c>
       <c r="E32" s="12">
         <f t="shared" si="1"/>
@@ -11662,9 +11676,9 @@
         <f t="shared" si="1"/>
         <v>3687.55</v>
       </c>
-      <c r="J32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="J32" s="12">
+        <f t="shared" si="1"/>
+        <v>1000</v>
       </c>
       <c r="K32" s="12">
         <f t="shared" si="1"/>
@@ -11678,9 +11692,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="N32" s="12">
+        <f t="shared" si="1"/>
+        <v>810</v>
       </c>
       <c r="O32" s="12" t="str">
         <f t="shared" si="1"/>
@@ -11696,7 +11710,7 @@
       </c>
       <c r="R32" s="12">
         <f t="shared" si="1"/>
-        <v>5888.6799999999994</v>
+        <v>8482.99</v>
       </c>
       <c r="S32" s="12" t="str">
         <f t="shared" si="1"/>
@@ -11740,7 +11754,7 @@
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>
-        <v>89532.060000000012</v>
+        <v>114011.69000000002</v>
       </c>
       <c r="AD32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -1567,7 +1567,7 @@
         <v>7505</v>
       </c>
       <c r="M7" s="1">
-        <v>25000</v>
+        <v>23000</v>
       </c>
       <c r="N7" s="1">
         <v>810</v>
@@ -1611,7 +1611,7 @@
       <c r="AB7" s="6"/>
       <c r="AC7" s="1">
         <f t="shared" si="0"/>
-        <v>176955.32</v>
+        <v>174955.32</v>
       </c>
       <c r="AD7" s="7">
         <f t="shared" si="1"/>
@@ -1629,11 +1629,11 @@
       </c>
       <c r="AH7" s="8">
         <f t="shared" si="3"/>
-        <v>63477.66</v>
+        <v>64477.66</v>
       </c>
       <c r="AI7" s="9">
         <f t="shared" si="4"/>
-        <v>72771.34</v>
+        <v>71771.34</v>
       </c>
       <c r="AJ7" s="10">
         <f t="shared" si="5"/>
@@ -2550,9 +2550,9 @@
         <f>IF(Setiembre!N32&gt;0,Setiembre!N32,"")</f>
         <v>810</v>
       </c>
-      <c r="O18" s="1" t="str">
+      <c r="O18" s="1">
         <f>IF(Setiembre!O32&gt;0,Setiembre!O32,"")</f>
-        <v/>
+        <v>491.81</v>
       </c>
       <c r="P18" s="1">
         <f>IF(Setiembre!P32&gt;0,Setiembre!P32,"")</f>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="R18" s="1">
         <f>IF(Setiembre!R32&gt;0,Setiembre!R32,"")</f>
-        <v>8482.99</v>
+        <v>12279.42</v>
       </c>
       <c r="S18" s="1" t="str">
         <f>IF(Setiembre!S32&gt;0,Setiembre!S32,"")</f>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="AA18" s="1">
         <f>IF(Setiembre!AA32&gt;0,Setiembre!AA32,"")</f>
-        <v>1901.1299999999999</v>
+        <v>2171.13</v>
       </c>
     </row>
     <row r="19" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3556,9 +3556,9 @@
         <f>IF(ISNUMBER(Setiembre!N32),N7-Setiembre!N32,"")</f>
         <v>0</v>
       </c>
-      <c r="O29" s="1" t="str">
+      <c r="O29" s="1">
         <f>IF(ISNUMBER(Setiembre!O32),O7-Setiembre!O32,"")</f>
-        <v/>
+        <v>7508.19</v>
       </c>
       <c r="P29" s="1">
         <f>IF(ISNUMBER(Setiembre!P32),P7-Setiembre!P32,"")</f>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="R29" s="1">
         <f>IF(ISNUMBER(Setiembre!R32),R7-Setiembre!R32,"")</f>
-        <v>10517.01</v>
+        <v>6720.58</v>
       </c>
       <c r="S29" s="1" t="str">
         <f>IF(ISNUMBER(Setiembre!S32),S7-Setiembre!S32,"")</f>
@@ -3606,11 +3606,11 @@
       </c>
       <c r="AA29" s="1">
         <f>IF(ISNUMBER(Setiembre!AA32),AA7-Setiembre!AA32,"")</f>
-        <v>3098.87</v>
+        <v>2828.87</v>
       </c>
       <c r="AC29" s="12">
         <f t="shared" si="7"/>
-        <v>15043.629999999997</v>
+        <v>18485.39</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="8"/>
-        <v>6106.2000000000007</v>
+        <v>13614.39</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="8"/>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>14834.88</v>
+        <v>11038.449999999999</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4058,11 +4058,11 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>-14840</v>
+        <v>-15110</v>
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>3558.6899999999951</v>
+        <v>7000.4499999999935</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10920,7 +10920,10 @@
       <c r="O12" s="35"/>
       <c r="P12" s="35"/>
       <c r="Q12" s="35"/>
-      <c r="R12" s="35"/>
+      <c r="R12" s="35">
+        <f>898-14.72+0.94+785.75-14.29</f>
+        <v>1655.68</v>
+      </c>
       <c r="S12" s="35"/>
       <c r="T12" s="35"/>
       <c r="U12" s="35"/>
@@ -10929,11 +10932,13 @@
       <c r="X12" s="35"/>
       <c r="Y12" s="35"/>
       <c r="Z12" s="35"/>
-      <c r="AA12" s="35"/>
+      <c r="AA12" s="35">
+        <v>270</v>
+      </c>
       <c r="AB12" s="36"/>
       <c r="AC12" s="35">
         <f t="shared" si="0"/>
-        <v>6179</v>
+        <v>8104.68</v>
       </c>
       <c r="AD12" s="35"/>
     </row>
@@ -10991,10 +10996,16 @@
       <c r="L14" s="35"/>
       <c r="M14" s="35"/>
       <c r="N14" s="35"/>
-      <c r="O14" s="35"/>
+      <c r="O14" s="35">
+        <f>500-8.19</f>
+        <v>491.81</v>
+      </c>
       <c r="P14" s="35"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="35"/>
+      <c r="R14" s="35">
+        <f>180-2.95+197-3.23+80-5.9+240+460+450-7.38+248-4.07+315-5.72</f>
+        <v>2140.7500000000005</v>
+      </c>
       <c r="S14" s="35"/>
       <c r="T14" s="35"/>
       <c r="U14" s="35"/>
@@ -11007,7 +11018,7 @@
       <c r="AB14" s="36"/>
       <c r="AC14" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2632.5600000000004</v>
       </c>
       <c r="AD14" s="35"/>
     </row>
@@ -11696,9 +11707,9 @@
         <f t="shared" si="1"/>
         <v>810</v>
       </c>
-      <c r="O32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="O32" s="12">
+        <f t="shared" si="1"/>
+        <v>491.81</v>
       </c>
       <c r="P32" s="12">
         <f t="shared" si="1"/>
@@ -11710,7 +11721,7 @@
       </c>
       <c r="R32" s="12">
         <f t="shared" si="1"/>
-        <v>8482.99</v>
+        <v>12279.42</v>
       </c>
       <c r="S32" s="12" t="str">
         <f t="shared" si="1"/>
@@ -11746,7 +11757,7 @@
       </c>
       <c r="AA32" s="12">
         <f t="shared" si="1"/>
-        <v>1901.1299999999999</v>
+        <v>2171.13</v>
       </c>
       <c r="AB32" s="38" t="str">
         <f t="shared" si="1"/>
@@ -11754,7 +11765,7 @@
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>
-        <v>114011.69000000002</v>
+        <v>118569.93000000002</v>
       </c>
       <c r="AD32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -2542,9 +2542,9 @@
         <f>IF(Setiembre!L32&gt;0,Setiembre!L32,"")</f>
         <v>7502.34</v>
       </c>
-      <c r="M18" s="1" t="str">
+      <c r="M18" s="1">
         <f>IF(Setiembre!M32&gt;0,Setiembre!M32,"")</f>
-        <v/>
+        <v>23081.75</v>
       </c>
       <c r="N18" s="1">
         <f>IF(Setiembre!N32&gt;0,Setiembre!N32,"")</f>
@@ -2558,17 +2558,17 @@
         <f>IF(Setiembre!P32&gt;0,Setiembre!P32,"")</f>
         <v>1800</v>
       </c>
-      <c r="Q18" s="1" t="str">
+      <c r="Q18" s="1">
         <f>IF(Setiembre!Q32&gt;0,Setiembre!Q32,"")</f>
-        <v/>
+        <v>2508.1999999999998</v>
       </c>
       <c r="R18" s="1">
         <f>IF(Setiembre!R32&gt;0,Setiembre!R32,"")</f>
-        <v>12279.42</v>
-      </c>
-      <c r="S18" s="1" t="str">
+        <v>15551.64</v>
+      </c>
+      <c r="S18" s="1">
         <f>IF(Setiembre!S32&gt;0,Setiembre!S32,"")</f>
-        <v/>
+        <v>911.25</v>
       </c>
       <c r="T18" s="1" t="str">
         <f>IF(Setiembre!T32&gt;0,Setiembre!T32,"")</f>
@@ -2586,9 +2586,9 @@
         <f>IF(Setiembre!W32&gt;0,Setiembre!W32,"")</f>
         <v>1947.54</v>
       </c>
-      <c r="X18" s="1" t="str">
+      <c r="X18" s="1">
         <f>IF(Setiembre!X32&gt;0,Setiembre!X32,"")</f>
-        <v/>
+        <v>215</v>
       </c>
       <c r="Y18" s="1" t="str">
         <f>IF(Setiembre!Y32&gt;0,Setiembre!Y32,"")</f>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="AA18" s="1">
         <f>IF(Setiembre!AA32&gt;0,Setiembre!AA32,"")</f>
-        <v>2171.13</v>
+        <v>2297.0300000000002</v>
       </c>
     </row>
     <row r="19" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3548,9 +3548,9 @@
         <f>IF(ISNUMBER(Setiembre!L32),L7-Setiembre!L32,"")</f>
         <v>2.6599999999998545</v>
       </c>
-      <c r="M29" s="1" t="str">
+      <c r="M29" s="1">
         <f>IF(ISNUMBER(Setiembre!M32),M7-Setiembre!M32,"")</f>
-        <v/>
+        <v>-81.75</v>
       </c>
       <c r="N29" s="1">
         <f>IF(ISNUMBER(Setiembre!N32),N7-Setiembre!N32,"")</f>
@@ -3564,17 +3564,17 @@
         <f>IF(ISNUMBER(Setiembre!P32),P7-Setiembre!P32,"")</f>
         <v>0</v>
       </c>
-      <c r="Q29" s="1" t="str">
+      <c r="Q29" s="1">
         <f>IF(ISNUMBER(Setiembre!Q32),Q7-Setiembre!Q32,"")</f>
-        <v/>
+        <v>-8.1999999999998181</v>
       </c>
       <c r="R29" s="1">
         <f>IF(ISNUMBER(Setiembre!R32),R7-Setiembre!R32,"")</f>
-        <v>6720.58</v>
-      </c>
-      <c r="S29" s="1" t="str">
+        <v>3448.3600000000006</v>
+      </c>
+      <c r="S29" s="1">
         <f>IF(ISNUMBER(Setiembre!S32),S7-Setiembre!S32,"")</f>
-        <v/>
+        <v>1088.75</v>
       </c>
       <c r="T29" s="1" t="str">
         <f>IF(ISNUMBER(Setiembre!T32),T7-Setiembre!T32,"")</f>
@@ -3592,9 +3592,9 @@
         <f>IF(ISNUMBER(Setiembre!W32),W7-Setiembre!W32,"")</f>
         <v>1052.46</v>
       </c>
-      <c r="X29" s="1" t="str">
+      <c r="X29" s="1">
         <f>IF(ISNUMBER(Setiembre!X32),X7-Setiembre!X32,"")</f>
-        <v/>
+        <v>585</v>
       </c>
       <c r="Y29" s="1" t="str">
         <f>IF(ISNUMBER(Setiembre!Y32),Y7-Setiembre!Y32,"")</f>
@@ -3606,11 +3606,11 @@
       </c>
       <c r="AA29" s="1">
         <f>IF(ISNUMBER(Setiembre!AA32),AA7-Setiembre!AA32,"")</f>
-        <v>2828.87</v>
+        <v>2702.97</v>
       </c>
       <c r="AC29" s="12">
         <f t="shared" si="7"/>
-        <v>18485.39</v>
+        <v>16671.070000000003</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="M33" s="12">
         <f t="shared" si="8"/>
-        <v>-13596.369999999999</v>
+        <v>-13678.119999999999</v>
       </c>
       <c r="N33" s="12">
         <f t="shared" si="8"/>
@@ -4018,15 +4018,15 @@
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="8"/>
-        <v>50.820000000000164</v>
+        <v>42.620000000000346</v>
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>11038.449999999999</v>
+        <v>7766.23</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
-        <v>1935.6800000000003</v>
+        <v>3024.4300000000003</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="8"/>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="X33" s="12">
         <f t="shared" si="8"/>
-        <v>3179.7</v>
+        <v>3764.7</v>
       </c>
       <c r="Y33" s="12">
         <f t="shared" si="8"/>
@@ -4058,11 +4058,11 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>-15110</v>
+        <v>-15235.9</v>
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>7000.4499999999935</v>
+        <v>5186.1299999999956</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11042,7 +11042,10 @@
       <c r="O15" s="35"/>
       <c r="P15" s="35"/>
       <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
+      <c r="R15" s="35">
+        <f>761-13.2</f>
+        <v>747.8</v>
+      </c>
       <c r="S15" s="35"/>
       <c r="T15" s="35"/>
       <c r="U15" s="35"/>
@@ -11051,11 +11054,14 @@
       <c r="X15" s="35"/>
       <c r="Y15" s="35"/>
       <c r="Z15" s="35"/>
-      <c r="AA15" s="35"/>
+      <c r="AA15" s="35">
+        <f>128-2.1</f>
+        <v>125.9</v>
+      </c>
       <c r="AB15" s="36"/>
       <c r="AC15" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>873.69999999999993</v>
       </c>
       <c r="AD15" s="35"/>
     </row>
@@ -11085,14 +11091,16 @@
       <c r="U16" s="35"/>
       <c r="V16" s="35"/>
       <c r="W16" s="35"/>
-      <c r="X16" s="35"/>
+      <c r="X16" s="35">
+        <v>215</v>
+      </c>
       <c r="Y16" s="35"/>
       <c r="Z16" s="35"/>
       <c r="AA16" s="35"/>
       <c r="AB16" s="36"/>
       <c r="AC16" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="AD16" s="35"/>
     </row>
@@ -11152,9 +11160,15 @@
       <c r="N18" s="35"/>
       <c r="O18" s="35"/>
       <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
+      <c r="Q18" s="35">
+        <f>2550-41.8</f>
+        <v>2508.1999999999998</v>
+      </c>
       <c r="R18" s="35"/>
-      <c r="S18" s="35"/>
+      <c r="S18" s="35">
+        <f>926-14.75</f>
+        <v>911.25</v>
+      </c>
       <c r="T18" s="35"/>
       <c r="U18" s="35"/>
       <c r="V18" s="35"/>
@@ -11166,7 +11180,7 @@
       <c r="AB18" s="36"/>
       <c r="AC18" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3419.45</v>
       </c>
       <c r="AD18" s="35"/>
     </row>
@@ -11185,12 +11199,18 @@
       <c r="J19" s="35"/>
       <c r="K19" s="35"/>
       <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
+      <c r="M19" s="35">
+        <f>21570.71+1511.04</f>
+        <v>23081.75</v>
+      </c>
       <c r="N19" s="35"/>
       <c r="O19" s="35"/>
       <c r="P19" s="35"/>
       <c r="Q19" s="35"/>
-      <c r="R19" s="35"/>
+      <c r="R19" s="35">
+        <f>469+432+1666-7.31-26.74-8.53</f>
+        <v>2524.42</v>
+      </c>
       <c r="S19" s="35"/>
       <c r="T19" s="35"/>
       <c r="U19" s="35"/>
@@ -11203,7 +11223,7 @@
       <c r="AB19" s="36"/>
       <c r="AC19" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25606.17</v>
       </c>
       <c r="AD19" s="35"/>
     </row>
@@ -11699,9 +11719,9 @@
         <f t="shared" si="1"/>
         <v>7502.34</v>
       </c>
-      <c r="M32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="M32" s="12">
+        <f t="shared" si="1"/>
+        <v>23081.75</v>
       </c>
       <c r="N32" s="12">
         <f t="shared" si="1"/>
@@ -11715,17 +11735,17 @@
         <f t="shared" si="1"/>
         <v>1800</v>
       </c>
-      <c r="Q32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="Q32" s="12">
+        <f t="shared" si="1"/>
+        <v>2508.1999999999998</v>
       </c>
       <c r="R32" s="12">
         <f t="shared" si="1"/>
-        <v>12279.42</v>
-      </c>
-      <c r="S32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <v>15551.64</v>
+      </c>
+      <c r="S32" s="12">
+        <f t="shared" si="1"/>
+        <v>911.25</v>
       </c>
       <c r="T32" s="12" t="str">
         <f t="shared" si="1"/>
@@ -11743,9 +11763,9 @@
         <f t="shared" si="1"/>
         <v>1947.54</v>
       </c>
-      <c r="X32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="X32" s="12">
+        <f t="shared" si="1"/>
+        <v>215</v>
       </c>
       <c r="Y32" s="12" t="str">
         <f t="shared" si="1"/>
@@ -11757,7 +11777,7 @@
       </c>
       <c r="AA32" s="12">
         <f t="shared" si="1"/>
-        <v>2171.13</v>
+        <v>2297.0300000000002</v>
       </c>
       <c r="AB32" s="38" t="str">
         <f t="shared" si="1"/>
@@ -11765,7 +11785,7 @@
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>
-        <v>118569.93000000002</v>
+        <v>148684.25</v>
       </c>
       <c r="AD32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="R18" s="1">
         <f>IF(Setiembre!R32&gt;0,Setiembre!R32,"")</f>
-        <v>15551.64</v>
+        <v>17250.28</v>
       </c>
       <c r="S18" s="1">
         <f>IF(Setiembre!S32&gt;0,Setiembre!S32,"")</f>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="R29" s="1">
         <f>IF(ISNUMBER(Setiembre!R32),R7-Setiembre!R32,"")</f>
-        <v>3448.3600000000006</v>
+        <v>1749.7200000000012</v>
       </c>
       <c r="S29" s="1">
         <f>IF(ISNUMBER(Setiembre!S32),S7-Setiembre!S32,"")</f>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="AC29" s="12">
         <f t="shared" si="7"/>
-        <v>16671.070000000003</v>
+        <v>14972.430000000002</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>7766.23</v>
+        <v>6067.59</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>5186.1299999999956</v>
+        <v>3487.4899999999961</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11247,7 +11247,10 @@
       <c r="O20" s="35"/>
       <c r="P20" s="35"/>
       <c r="Q20" s="35"/>
-      <c r="R20" s="35"/>
+      <c r="R20" s="35">
+        <f>449+616-7.36-10.1</f>
+        <v>1047.5400000000002</v>
+      </c>
       <c r="S20" s="35"/>
       <c r="T20" s="35"/>
       <c r="U20" s="35"/>
@@ -11260,7 +11263,7 @@
       <c r="AB20" s="36"/>
       <c r="AC20" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1047.5400000000002</v>
       </c>
       <c r="AD20" s="35"/>
     </row>
@@ -11358,7 +11361,10 @@
       <c r="O23" s="35"/>
       <c r="P23" s="35"/>
       <c r="Q23" s="35"/>
-      <c r="R23" s="35"/>
+      <c r="R23" s="35">
+        <f>662-10.9</f>
+        <v>651.1</v>
+      </c>
       <c r="S23" s="35"/>
       <c r="T23" s="35"/>
       <c r="U23" s="35"/>
@@ -11371,7 +11377,7 @@
       <c r="AB23" s="36"/>
       <c r="AC23" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>651.1</v>
       </c>
       <c r="AD23" s="35"/>
     </row>
@@ -11741,7 +11747,7 @@
       </c>
       <c r="R32" s="12">
         <f t="shared" si="1"/>
-        <v>15551.64</v>
+        <v>17250.28</v>
       </c>
       <c r="S32" s="12">
         <f t="shared" si="1"/>
@@ -11785,7 +11791,7 @@
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>
-        <v>148684.25</v>
+        <v>150382.89000000001</v>
       </c>
       <c r="AD32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -2564,7 +2564,7 @@
       </c>
       <c r="R18" s="1">
         <f>IF(Setiembre!R32&gt;0,Setiembre!R32,"")</f>
-        <v>17250.28</v>
+        <v>17930.939999999999</v>
       </c>
       <c r="S18" s="1">
         <f>IF(Setiembre!S32&gt;0,Setiembre!S32,"")</f>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="R29" s="1">
         <f>IF(ISNUMBER(Setiembre!R32),R7-Setiembre!R32,"")</f>
-        <v>1749.7200000000012</v>
+        <v>1069.0600000000013</v>
       </c>
       <c r="S29" s="1">
         <f>IF(ISNUMBER(Setiembre!S32),S7-Setiembre!S32,"")</f>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="AC29" s="12">
         <f t="shared" si="7"/>
-        <v>14972.430000000002</v>
+        <v>14291.770000000002</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>6067.59</v>
+        <v>5386.93</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>3487.4899999999961</v>
+        <v>2806.8299999999963</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11362,8 +11362,8 @@
       <c r="P23" s="35"/>
       <c r="Q23" s="35"/>
       <c r="R23" s="35">
-        <f>662-10.9</f>
-        <v>651.1</v>
+        <f>662-10.9+692-11.34</f>
+        <v>1331.76</v>
       </c>
       <c r="S23" s="35"/>
       <c r="T23" s="35"/>
@@ -11377,7 +11377,7 @@
       <c r="AB23" s="36"/>
       <c r="AC23" s="35">
         <f t="shared" si="0"/>
-        <v>651.1</v>
+        <v>1331.76</v>
       </c>
       <c r="AD23" s="35"/>
     </row>
@@ -11747,7 +11747,7 @@
       </c>
       <c r="R32" s="12">
         <f t="shared" si="1"/>
-        <v>17250.28</v>
+        <v>17930.939999999999</v>
       </c>
       <c r="S32" s="12">
         <f t="shared" si="1"/>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>
-        <v>150382.89000000001</v>
+        <v>151063.55000000002</v>
       </c>
       <c r="AD32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -2552,11 +2552,11 @@
       </c>
       <c r="O18" s="1">
         <f>IF(Setiembre!O32&gt;0,Setiembre!O32,"")</f>
-        <v>491.81</v>
+        <v>4215.8100000000004</v>
       </c>
       <c r="P18" s="1">
         <f>IF(Setiembre!P32&gt;0,Setiembre!P32,"")</f>
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="Q18" s="1">
         <f>IF(Setiembre!Q32&gt;0,Setiembre!Q32,"")</f>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="R18" s="1">
         <f>IF(Setiembre!R32&gt;0,Setiembre!R32,"")</f>
-        <v>17930.939999999999</v>
+        <v>19256.53</v>
       </c>
       <c r="S18" s="1">
         <f>IF(Setiembre!S32&gt;0,Setiembre!S32,"")</f>
@@ -3558,11 +3558,11 @@
       </c>
       <c r="O29" s="1">
         <f>IF(ISNUMBER(Setiembre!O32),O7-Setiembre!O32,"")</f>
-        <v>7508.19</v>
+        <v>3784.1899999999996</v>
       </c>
       <c r="P29" s="1">
         <f>IF(ISNUMBER(Setiembre!P32),P7-Setiembre!P32,"")</f>
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="Q29" s="1">
         <f>IF(ISNUMBER(Setiembre!Q32),Q7-Setiembre!Q32,"")</f>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="R29" s="1">
         <f>IF(ISNUMBER(Setiembre!R32),R7-Setiembre!R32,"")</f>
-        <v>1069.0600000000013</v>
+        <v>-256.52999999999884</v>
       </c>
       <c r="S29" s="1">
         <f>IF(ISNUMBER(Setiembre!S32),S7-Setiembre!S32,"")</f>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="AC29" s="12">
         <f t="shared" si="7"/>
-        <v>14291.770000000002</v>
+        <v>7442.18</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4010,11 +4010,11 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="8"/>
-        <v>13614.39</v>
+        <v>9890.39</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="8"/>
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="8"/>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>5386.93</v>
+        <v>4061.34</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>2806.8299999999963</v>
+        <v>-4042.7600000000039</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11435,10 +11435,15 @@
       <c r="L25" s="35"/>
       <c r="M25" s="35"/>
       <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
+      <c r="O25" s="35">
+        <v>3724</v>
+      </c>
       <c r="P25" s="35"/>
       <c r="Q25" s="35"/>
-      <c r="R25" s="35"/>
+      <c r="R25" s="35">
+        <f>119.18+540-11.8-1.95-39.84+720</f>
+        <v>1325.5900000000001</v>
+      </c>
       <c r="S25" s="35"/>
       <c r="T25" s="35"/>
       <c r="U25" s="35"/>
@@ -11451,7 +11456,7 @@
       <c r="AB25" s="36"/>
       <c r="AC25" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5049.59</v>
       </c>
       <c r="AD25" s="35"/>
     </row>
@@ -11473,7 +11478,9 @@
       <c r="M26" s="35"/>
       <c r="N26" s="35"/>
       <c r="O26" s="35"/>
-      <c r="P26" s="35"/>
+      <c r="P26" s="35">
+        <v>1800</v>
+      </c>
       <c r="Q26" s="35"/>
       <c r="R26" s="35"/>
       <c r="S26" s="35"/>
@@ -11488,7 +11495,7 @@
       <c r="AB26" s="36"/>
       <c r="AC26" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="AD26" s="35"/>
     </row>
@@ -11735,11 +11742,11 @@
       </c>
       <c r="O32" s="12">
         <f t="shared" si="1"/>
-        <v>491.81</v>
+        <v>4215.8100000000004</v>
       </c>
       <c r="P32" s="12">
         <f t="shared" si="1"/>
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="Q32" s="12">
         <f t="shared" si="1"/>
@@ -11747,7 +11754,7 @@
       </c>
       <c r="R32" s="12">
         <f t="shared" si="1"/>
-        <v>17930.939999999999</v>
+        <v>19256.53</v>
       </c>
       <c r="S32" s="12">
         <f t="shared" si="1"/>
@@ -11791,7 +11798,7 @@
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>
-        <v>151063.55000000002</v>
+        <v>157913.14000000001</v>
       </c>
       <c r="AD32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -2552,7 +2552,7 @@
       </c>
       <c r="O18" s="1">
         <f>IF(Setiembre!O32&gt;0,Setiembre!O32,"")</f>
-        <v>4215.8100000000004</v>
+        <v>3396.5300000000007</v>
       </c>
       <c r="P18" s="1">
         <f>IF(Setiembre!P32&gt;0,Setiembre!P32,"")</f>
@@ -2564,15 +2564,15 @@
       </c>
       <c r="R18" s="1">
         <f>IF(Setiembre!R32&gt;0,Setiembre!R32,"")</f>
-        <v>19256.53</v>
+        <v>21907.1</v>
       </c>
       <c r="S18" s="1">
         <f>IF(Setiembre!S32&gt;0,Setiembre!S32,"")</f>
         <v>911.25</v>
       </c>
-      <c r="T18" s="1" t="str">
+      <c r="T18" s="1">
         <f>IF(Setiembre!T32&gt;0,Setiembre!T32,"")</f>
-        <v/>
+        <v>2189.06</v>
       </c>
       <c r="U18" s="1">
         <f>IF(Setiembre!U32&gt;0,Setiembre!U32,"")</f>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="O29" s="1">
         <f>IF(ISNUMBER(Setiembre!O32),O7-Setiembre!O32,"")</f>
-        <v>3784.1899999999996</v>
+        <v>4603.4699999999993</v>
       </c>
       <c r="P29" s="1">
         <f>IF(ISNUMBER(Setiembre!P32),P7-Setiembre!P32,"")</f>
@@ -3570,15 +3570,15 @@
       </c>
       <c r="R29" s="1">
         <f>IF(ISNUMBER(Setiembre!R32),R7-Setiembre!R32,"")</f>
-        <v>-256.52999999999884</v>
+        <v>-2907.0999999999985</v>
       </c>
       <c r="S29" s="1">
         <f>IF(ISNUMBER(Setiembre!S32),S7-Setiembre!S32,"")</f>
         <v>1088.75</v>
       </c>
-      <c r="T29" s="1" t="str">
+      <c r="T29" s="1">
         <f>IF(ISNUMBER(Setiembre!T32),T7-Setiembre!T32,"")</f>
-        <v/>
+        <v>2810.94</v>
       </c>
       <c r="U29" s="1">
         <f>IF(ISNUMBER(Setiembre!U32),U7-Setiembre!U32,"")</f>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="AC29" s="12">
         <f t="shared" si="7"/>
-        <v>7442.18</v>
+        <v>8421.83</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="8"/>
-        <v>9890.39</v>
+        <v>10709.67</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="8"/>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>4061.34</v>
+        <v>1410.7700000000004</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="T33" s="12">
         <f t="shared" si="8"/>
-        <v>1227.0300000000007</v>
+        <v>4037.9700000000007</v>
       </c>
       <c r="U33" s="12">
         <f t="shared" si="8"/>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>-4042.7600000000039</v>
+        <v>-3063.1100000000024</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11477,14 +11477,22 @@
       <c r="L26" s="35"/>
       <c r="M26" s="35"/>
       <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
+      <c r="O26" s="35">
+        <v>-819.28</v>
+      </c>
       <c r="P26" s="35">
         <v>1800</v>
       </c>
       <c r="Q26" s="35"/>
-      <c r="R26" s="35"/>
+      <c r="R26" s="35">
+        <f>444.94-7.49+481+1769.48-6.64-30.72</f>
+        <v>2650.5700000000006</v>
+      </c>
       <c r="S26" s="35"/>
-      <c r="T26" s="35"/>
+      <c r="T26" s="35">
+        <f>480-7.87+739.55-12.57+1006.45-16.5</f>
+        <v>2189.06</v>
+      </c>
       <c r="U26" s="35"/>
       <c r="V26" s="35"/>
       <c r="W26" s="35"/>
@@ -11495,7 +11503,7 @@
       <c r="AB26" s="36"/>
       <c r="AC26" s="35">
         <f t="shared" si="0"/>
-        <v>1800</v>
+        <v>5820.35</v>
       </c>
       <c r="AD26" s="35"/>
     </row>
@@ -11742,7 +11750,7 @@
       </c>
       <c r="O32" s="12">
         <f t="shared" si="1"/>
-        <v>4215.8100000000004</v>
+        <v>3396.5300000000007</v>
       </c>
       <c r="P32" s="12">
         <f t="shared" si="1"/>
@@ -11754,15 +11762,15 @@
       </c>
       <c r="R32" s="12">
         <f t="shared" si="1"/>
-        <v>19256.53</v>
+        <v>21907.1</v>
       </c>
       <c r="S32" s="12">
         <f t="shared" si="1"/>
         <v>911.25</v>
       </c>
-      <c r="T32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="T32" s="12">
+        <f t="shared" si="1"/>
+        <v>2189.06</v>
       </c>
       <c r="U32" s="12">
         <f t="shared" si="1"/>
@@ -11798,7 +11806,7 @@
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>
-        <v>157913.14000000001</v>
+        <v>161933.49000000002</v>
       </c>
       <c r="AD32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -2564,7 +2564,7 @@
       </c>
       <c r="R18" s="1">
         <f>IF(Setiembre!R32&gt;0,Setiembre!R32,"")</f>
-        <v>21907.1</v>
+        <v>24533.989999999998</v>
       </c>
       <c r="S18" s="1">
         <f>IF(Setiembre!S32&gt;0,Setiembre!S32,"")</f>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="W18" s="1">
         <f>IF(Setiembre!W32&gt;0,Setiembre!W32,"")</f>
-        <v>1947.54</v>
+        <v>3247.54</v>
       </c>
       <c r="X18" s="1">
         <f>IF(Setiembre!X32&gt;0,Setiembre!X32,"")</f>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="R29" s="1">
         <f>IF(ISNUMBER(Setiembre!R32),R7-Setiembre!R32,"")</f>
-        <v>-2907.0999999999985</v>
+        <v>-5533.989999999998</v>
       </c>
       <c r="S29" s="1">
         <f>IF(ISNUMBER(Setiembre!S32),S7-Setiembre!S32,"")</f>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="W29" s="1">
         <f>IF(ISNUMBER(Setiembre!W32),W7-Setiembre!W32,"")</f>
-        <v>1052.46</v>
+        <v>-247.53999999999996</v>
       </c>
       <c r="X29" s="1">
         <f>IF(ISNUMBER(Setiembre!X32),X7-Setiembre!X32,"")</f>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="AC29" s="12">
         <f t="shared" si="7"/>
-        <v>8421.83</v>
+        <v>4494.9400000000005</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>1410.7700000000004</v>
+        <v>-1216.119999999999</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="W33" s="12">
         <f t="shared" si="8"/>
-        <v>2783.6</v>
+        <v>1483.6</v>
       </c>
       <c r="X33" s="12">
         <f t="shared" si="8"/>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>-3063.1100000000024</v>
+        <v>-6990.0000000000018</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11495,7 +11495,9 @@
       </c>
       <c r="U26" s="35"/>
       <c r="V26" s="35"/>
-      <c r="W26" s="35"/>
+      <c r="W26" s="35">
+        <v>1300</v>
+      </c>
       <c r="X26" s="35"/>
       <c r="Y26" s="35"/>
       <c r="Z26" s="35"/>
@@ -11503,7 +11505,7 @@
       <c r="AB26" s="36"/>
       <c r="AC26" s="35">
         <f t="shared" si="0"/>
-        <v>5820.35</v>
+        <v>7120.35</v>
       </c>
       <c r="AD26" s="35"/>
     </row>
@@ -11601,7 +11603,10 @@
       <c r="O29" s="35"/>
       <c r="P29" s="35"/>
       <c r="Q29" s="35"/>
-      <c r="R29" s="35"/>
+      <c r="R29" s="35">
+        <f>1143+488-10.37+633-18.74-8+400</f>
+        <v>2626.8900000000003</v>
+      </c>
       <c r="S29" s="35"/>
       <c r="T29" s="35"/>
       <c r="U29" s="35"/>
@@ -11614,7 +11619,7 @@
       <c r="AB29" s="36"/>
       <c r="AC29" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2626.8900000000003</v>
       </c>
       <c r="AD29" s="35"/>
     </row>
@@ -11762,7 +11767,7 @@
       </c>
       <c r="R32" s="12">
         <f t="shared" si="1"/>
-        <v>21907.1</v>
+        <v>24533.989999999998</v>
       </c>
       <c r="S32" s="12">
         <f t="shared" si="1"/>
@@ -11782,7 +11787,7 @@
       </c>
       <c r="W32" s="12">
         <f t="shared" si="1"/>
-        <v>1947.54</v>
+        <v>3247.54</v>
       </c>
       <c r="X32" s="12">
         <f t="shared" si="1"/>
@@ -11806,7 +11811,7 @@
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>
-        <v>161933.49000000002</v>
+        <v>165860.38000000003</v>
       </c>
       <c r="AD32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -1546,10 +1546,7 @@
         <v>500</v>
       </c>
       <c r="F7" s="1">
-        <v>27000</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1100</v>
+        <v>27500</v>
       </c>
       <c r="H7" s="1">
         <v>3300</v>
@@ -1611,7 +1608,7 @@
       <c r="AB7" s="6"/>
       <c r="AC7" s="1">
         <f t="shared" si="0"/>
-        <v>174955.32</v>
+        <v>174355.32</v>
       </c>
       <c r="AD7" s="7">
         <f t="shared" si="1"/>
@@ -1629,15 +1626,15 @@
       </c>
       <c r="AH7" s="8">
         <f t="shared" si="3"/>
-        <v>64477.66</v>
+        <v>64177.66</v>
       </c>
       <c r="AI7" s="9">
         <f t="shared" si="4"/>
-        <v>71771.34</v>
+        <v>71471.34</v>
       </c>
       <c r="AJ7" s="10">
         <f t="shared" si="5"/>
-        <v>136249</v>
+        <v>135649</v>
       </c>
     </row>
     <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1654,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>27000</v>
+        <v>27500</v>
       </c>
       <c r="G8" s="1">
-        <v>1100</v>
+        <v>2200</v>
       </c>
       <c r="H8" s="1">
         <v>3300</v>
@@ -1669,13 +1666,13 @@
         <v>700</v>
       </c>
       <c r="K8" s="1">
-        <v>18000</v>
+        <v>26738</v>
       </c>
       <c r="L8" s="1">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="M8" s="1">
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="N8" s="1">
         <v>810</v>
@@ -1690,7 +1687,7 @@
         <v>2500</v>
       </c>
       <c r="R8" s="1">
-        <v>19000</v>
+        <v>20000</v>
       </c>
       <c r="S8" s="1">
         <v>2000</v>
@@ -1713,7 +1710,7 @@
       <c r="AB8" s="6"/>
       <c r="AC8" s="1">
         <f>SUM(B8:AB8)</f>
-        <v>159460</v>
+        <v>180298</v>
       </c>
       <c r="AD8" s="7">
         <f t="shared" si="1"/>
@@ -1731,15 +1728,15 @@
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="3"/>
-        <v>72230</v>
+        <v>75149</v>
       </c>
       <c r="AI8" s="9">
         <f t="shared" si="4"/>
-        <v>63980</v>
+        <v>74399</v>
       </c>
       <c r="AJ8" s="10">
         <f t="shared" si="5"/>
-        <v>136210</v>
+        <v>149548</v>
       </c>
     </row>
     <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1756,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>27000</v>
+        <v>27500</v>
       </c>
       <c r="G9" s="1">
         <v>1100</v>
@@ -1792,7 +1789,7 @@
         <v>2500</v>
       </c>
       <c r="R9" s="1">
-        <v>19000</v>
+        <v>20000</v>
       </c>
       <c r="S9" s="1">
         <v>2000</v>
@@ -1815,7 +1812,7 @@
       <c r="AB9" s="6"/>
       <c r="AC9" s="1">
         <f t="shared" si="0"/>
-        <v>138879</v>
+        <v>140379</v>
       </c>
       <c r="AD9" s="7">
         <f t="shared" si="1"/>
@@ -1833,15 +1830,15 @@
       </c>
       <c r="AH9" s="8">
         <f t="shared" si="3"/>
-        <v>61939.5</v>
+        <v>62689.5</v>
       </c>
       <c r="AI9" s="9">
         <f t="shared" si="4"/>
-        <v>53639.5</v>
+        <v>54389.5</v>
       </c>
       <c r="AJ9" s="10">
         <f t="shared" si="5"/>
-        <v>115579</v>
+        <v>117079</v>
       </c>
     </row>
     <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1891,7 +1888,7 @@
         <v>2500</v>
       </c>
       <c r="R10" s="1">
-        <v>19000</v>
+        <v>20000</v>
       </c>
       <c r="S10" s="1">
         <v>2000</v>
@@ -1914,7 +1911,7 @@
       <c r="AB10" s="6"/>
       <c r="AC10" s="1">
         <f t="shared" si="0"/>
-        <v>152510</v>
+        <v>153510</v>
       </c>
       <c r="AD10" s="7">
         <f t="shared" si="1"/>
@@ -1932,15 +1929,15 @@
       </c>
       <c r="AH10" s="8">
         <f t="shared" si="3"/>
-        <v>68755</v>
+        <v>69255</v>
       </c>
       <c r="AI10" s="9">
         <f t="shared" si="4"/>
-        <v>60455</v>
+        <v>60955</v>
       </c>
       <c r="AJ10" s="10">
         <f t="shared" si="5"/>
-        <v>129210</v>
+        <v>130210</v>
       </c>
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2564,11 +2561,11 @@
       </c>
       <c r="R18" s="1">
         <f>IF(Setiembre!R32&gt;0,Setiembre!R32,"")</f>
-        <v>24533.989999999998</v>
+        <v>25897.909999999996</v>
       </c>
       <c r="S18" s="1">
         <f>IF(Setiembre!S32&gt;0,Setiembre!S32,"")</f>
-        <v>911.25</v>
+        <v>1174.1399999999999</v>
       </c>
       <c r="T18" s="1">
         <f>IF(Setiembre!T32&gt;0,Setiembre!T32,"")</f>
@@ -2600,7 +2597,7 @@
       </c>
       <c r="AA18" s="1">
         <f>IF(Setiembre!AA32&gt;0,Setiembre!AA32,"")</f>
-        <v>2297.0300000000002</v>
+        <v>2374.73</v>
       </c>
     </row>
     <row r="19" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3522,7 +3519,7 @@
       </c>
       <c r="F29" s="1">
         <f>IF(ISNUMBER(Setiembre!F32),F7-Setiembre!F32,"")</f>
-        <v>208</v>
+        <v>708</v>
       </c>
       <c r="G29" s="1" t="str">
         <f>IF(ISNUMBER(Setiembre!G32),G7-Setiembre!G32,"")</f>
@@ -3570,11 +3567,11 @@
       </c>
       <c r="R29" s="1">
         <f>IF(ISNUMBER(Setiembre!R32),R7-Setiembre!R32,"")</f>
-        <v>-5533.989999999998</v>
+        <v>-6897.9099999999962</v>
       </c>
       <c r="S29" s="1">
         <f>IF(ISNUMBER(Setiembre!S32),S7-Setiembre!S32,"")</f>
-        <v>1088.75</v>
+        <v>825.86000000000013</v>
       </c>
       <c r="T29" s="1">
         <f>IF(ISNUMBER(Setiembre!T32),T7-Setiembre!T32,"")</f>
@@ -3606,11 +3603,11 @@
       </c>
       <c r="AA29" s="1">
         <f>IF(ISNUMBER(Setiembre!AA32),AA7-Setiembre!AA32,"")</f>
-        <v>2702.97</v>
+        <v>2625.27</v>
       </c>
       <c r="AC29" s="12">
         <f t="shared" si="7"/>
-        <v>4494.9400000000005</v>
+        <v>3290.4300000000026</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3974,7 +3971,7 @@
       </c>
       <c r="F33" s="12">
         <f t="shared" si="8"/>
-        <v>-1678</v>
+        <v>-1178</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="8"/>
@@ -4022,11 +4019,11 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>-1216.119999999999</v>
+        <v>-2580.0399999999972</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
-        <v>3024.4300000000003</v>
+        <v>2761.5400000000004</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="8"/>
@@ -4058,11 +4055,11 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>-15235.9</v>
+        <v>-15313.599999999999</v>
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>-6990.0000000000018</v>
+        <v>-8194.5099999999984</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11644,7 +11641,10 @@
       <c r="P30" s="35"/>
       <c r="Q30" s="35"/>
       <c r="R30" s="35"/>
-      <c r="S30" s="35"/>
+      <c r="S30" s="35">
+        <f>265.01-2.12</f>
+        <v>262.89</v>
+      </c>
       <c r="T30" s="35"/>
       <c r="U30" s="35"/>
       <c r="V30" s="35"/>
@@ -11652,11 +11652,14 @@
       <c r="X30" s="35"/>
       <c r="Y30" s="35"/>
       <c r="Z30" s="35"/>
-      <c r="AA30" s="35"/>
+      <c r="AA30" s="35">
+        <f>79-1.3</f>
+        <v>77.7</v>
+      </c>
       <c r="AB30" s="36"/>
       <c r="AC30" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>340.59</v>
       </c>
       <c r="AD30" s="35"/>
     </row>
@@ -11680,7 +11683,10 @@
       <c r="O31" s="35"/>
       <c r="P31" s="35"/>
       <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
+      <c r="R31" s="35">
+        <f>1004-14.15+381-6.93</f>
+        <v>1363.9199999999998</v>
+      </c>
       <c r="S31" s="35"/>
       <c r="T31" s="35"/>
       <c r="U31" s="35"/>
@@ -11693,7 +11699,7 @@
       <c r="AB31" s="36"/>
       <c r="AC31" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1363.9199999999998</v>
       </c>
       <c r="AD31" s="35"/>
     </row>
@@ -11767,11 +11773,11 @@
       </c>
       <c r="R32" s="12">
         <f t="shared" si="1"/>
-        <v>24533.989999999998</v>
+        <v>25897.909999999996</v>
       </c>
       <c r="S32" s="12">
         <f t="shared" si="1"/>
-        <v>911.25</v>
+        <v>1174.1399999999999</v>
       </c>
       <c r="T32" s="12">
         <f t="shared" si="1"/>
@@ -11803,7 +11809,7 @@
       </c>
       <c r="AA32" s="12">
         <f t="shared" si="1"/>
-        <v>2297.0300000000002</v>
+        <v>2374.73</v>
       </c>
       <c r="AB32" s="38" t="str">
         <f t="shared" si="1"/>
@@ -11811,7 +11817,7 @@
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>
-        <v>165860.38000000003</v>
+        <v>167564.89000000004</v>
       </c>
       <c r="AD32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="92">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -317,6 +317,9 @@
   <si>
     <t>gas y calefacción</t>
   </si>
+  <si>
+    <t>Arreglo porton y luz</t>
+  </si>
 </sst>
 </file>
 
@@ -426,7 +429,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -541,6 +544,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -569,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -645,6 +654,7 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -979,36 +989,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
-      <c r="V1" s="43"/>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
-      <c r="AB1" s="43"/>
+      <c r="A1" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="44"/>
+      <c r="W1" s="44"/>
+      <c r="X1" s="44"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="44"/>
+      <c r="AA1" s="44"/>
+      <c r="AB1" s="44"/>
     </row>
     <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1642,7 +1652,7 @@
         <v>42</v>
       </c>
       <c r="B8" s="1">
-        <v>25000</v>
+        <v>27138.14</v>
       </c>
       <c r="D8" s="1">
         <v>15750</v>
@@ -1669,10 +1679,10 @@
         <v>26738</v>
       </c>
       <c r="L8" s="1">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="M8" s="1">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="N8" s="1">
         <v>810</v>
@@ -1710,7 +1720,7 @@
       <c r="AB8" s="6"/>
       <c r="AC8" s="1">
         <f>SUM(B8:AB8)</f>
-        <v>180298</v>
+        <v>191436.14</v>
       </c>
       <c r="AD8" s="7">
         <f t="shared" si="1"/>
@@ -1728,15 +1738,15 @@
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="3"/>
-        <v>75149</v>
+        <v>77718.070000000007</v>
       </c>
       <c r="AI8" s="9">
         <f t="shared" si="4"/>
-        <v>74399</v>
+        <v>79968.070000000007</v>
       </c>
       <c r="AJ8" s="10">
         <f t="shared" si="5"/>
-        <v>149548</v>
+        <v>157686.14000000001</v>
       </c>
     </row>
     <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1941,36 +1951,36 @@
       </c>
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="44"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="44"/>
-      <c r="M12" s="44"/>
-      <c r="N12" s="44"/>
-      <c r="O12" s="44"/>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="44"/>
-      <c r="R12" s="44"/>
-      <c r="S12" s="44"/>
-      <c r="T12" s="44"/>
-      <c r="U12" s="44"/>
-      <c r="V12" s="44"/>
-      <c r="W12" s="44"/>
-      <c r="X12" s="44"/>
-      <c r="Y12" s="44"/>
-      <c r="Z12" s="44"/>
-      <c r="AA12" s="44"/>
-      <c r="AB12" s="44"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="45"/>
+      <c r="N12" s="45"/>
+      <c r="O12" s="45"/>
+      <c r="P12" s="45"/>
+      <c r="Q12" s="45"/>
+      <c r="R12" s="45"/>
+      <c r="S12" s="45"/>
+      <c r="T12" s="45"/>
+      <c r="U12" s="45"/>
+      <c r="V12" s="45"/>
+      <c r="W12" s="45"/>
+      <c r="X12" s="45"/>
+      <c r="Y12" s="45"/>
+      <c r="Z12" s="45"/>
+      <c r="AA12" s="45"/>
+      <c r="AB12" s="45"/>
     </row>
     <row r="13" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -2604,9 +2614,9 @@
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="1" t="str">
+      <c r="B19" s="1">
         <f>IF(Octubre!B33&gt;0,Octubre!B33,"")</f>
-        <v/>
+        <v>27138.14</v>
       </c>
       <c r="C19" s="1" t="str">
         <f>IF(Octubre!C33&gt;0,Octubre!C33,"")</f>
@@ -2620,45 +2630,45 @@
         <f>IF(Octubre!E33&gt;0,Octubre!E33,"")</f>
         <v/>
       </c>
-      <c r="F19" s="1" t="str">
+      <c r="F19" s="1">
         <f>IF(Octubre!F33&gt;0,Octubre!F33,"")</f>
-        <v/>
+        <v>18447</v>
       </c>
       <c r="G19" s="1" t="str">
         <f>IF(Octubre!G33&gt;0,Octubre!G33,"")</f>
         <v/>
       </c>
-      <c r="H19" s="1" t="str">
+      <c r="H19" s="1">
         <f>IF(Octubre!H33&gt;0,Octubre!H33,"")</f>
-        <v/>
-      </c>
-      <c r="I19" s="1" t="str">
+        <v>3291.56</v>
+      </c>
+      <c r="I19" s="1">
         <f>IF(Octubre!I33&gt;0,Octubre!I33,"")</f>
-        <v/>
-      </c>
-      <c r="J19" s="1" t="str">
+        <v>3274.43</v>
+      </c>
+      <c r="J19" s="1">
         <f>IF(Octubre!J33&gt;0,Octubre!J33,"")</f>
-        <v/>
-      </c>
-      <c r="K19" s="1" t="str">
+        <v>700</v>
+      </c>
+      <c r="K19" s="1">
         <f>IF(Octubre!K33&gt;0,Octubre!K33,"")</f>
-        <v/>
-      </c>
-      <c r="L19" s="1" t="str">
+        <v>26737.25</v>
+      </c>
+      <c r="L19" s="1">
         <f>IF(Octubre!L33&gt;0,Octubre!L33,"")</f>
-        <v/>
+        <v>17990.03</v>
       </c>
       <c r="M19" s="1" t="str">
         <f>IF(Octubre!M33&gt;0,Octubre!M33,"")</f>
         <v/>
       </c>
-      <c r="N19" s="1" t="str">
+      <c r="N19" s="1">
         <f>IF(Octubre!N33&gt;0,Octubre!N33,"")</f>
-        <v/>
-      </c>
-      <c r="O19" s="1" t="str">
+        <v>810</v>
+      </c>
+      <c r="O19" s="1">
         <f>IF(Octubre!O33&gt;0,Octubre!O33,"")</f>
-        <v/>
+        <v>491.81</v>
       </c>
       <c r="P19" s="1" t="str">
         <f>IF(Octubre!P33&gt;0,Octubre!P33,"")</f>
@@ -2668,17 +2678,17 @@
         <f>IF(Octubre!Q33&gt;0,Octubre!Q33,"")</f>
         <v/>
       </c>
-      <c r="R19" s="1" t="str">
+      <c r="R19" s="1">
         <f>IF(Octubre!R33&gt;0,Octubre!R33,"")</f>
-        <v/>
+        <v>7019.1100000000006</v>
       </c>
       <c r="S19" s="1" t="str">
         <f>IF(Octubre!S33&gt;0,Octubre!S33,"")</f>
         <v/>
       </c>
-      <c r="T19" s="1" t="str">
+      <c r="T19" s="1">
         <f>IF(Octubre!T33&gt;0,Octubre!T33,"")</f>
-        <v/>
+        <v>1534.43</v>
       </c>
       <c r="U19" s="1" t="str">
         <f>IF(Octubre!U33&gt;0,Octubre!U33,"")</f>
@@ -2704,9 +2714,9 @@
         <f>IF(Octubre!Z33&gt;0,Octubre!Z33,"")</f>
         <v/>
       </c>
-      <c r="AA19" s="1" t="str">
+      <c r="AA19" s="1">
         <f>IF(Octubre!AA33&gt;0,Octubre!AA33,"")</f>
-        <v/>
+        <v>2500</v>
       </c>
     </row>
     <row r="20" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2928,36 +2938,36 @@
       </c>
     </row>
     <row r="23" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="45"/>
-      <c r="P23" s="45"/>
-      <c r="Q23" s="45"/>
-      <c r="R23" s="45"/>
-      <c r="S23" s="45"/>
-      <c r="T23" s="45"/>
-      <c r="U23" s="45"/>
-      <c r="V23" s="45"/>
-      <c r="W23" s="45"/>
-      <c r="X23" s="45"/>
-      <c r="Y23" s="45"/>
-      <c r="Z23" s="45"/>
-      <c r="AA23" s="45"/>
-      <c r="AB23" s="45"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="46"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="46"/>
+      <c r="M23" s="46"/>
+      <c r="N23" s="46"/>
+      <c r="O23" s="46"/>
+      <c r="P23" s="46"/>
+      <c r="Q23" s="46"/>
+      <c r="R23" s="46"/>
+      <c r="S23" s="46"/>
+      <c r="T23" s="46"/>
+      <c r="U23" s="46"/>
+      <c r="V23" s="46"/>
+      <c r="W23" s="46"/>
+      <c r="X23" s="46"/>
+      <c r="Y23" s="46"/>
+      <c r="Z23" s="46"/>
+      <c r="AA23" s="46"/>
+      <c r="AB23" s="46"/>
     </row>
     <row r="24" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -3615,7 +3625,7 @@
         <v>42</v>
       </c>
       <c r="B30" s="1" t="str">
-        <f>IF(ISNUMBER(Octubre!B33),#REF!-Octubre!B33,"")</f>
+        <f>IF(ISNUMBER(Setiembre!B33),B9-Setiembre!B33,"")</f>
         <v/>
       </c>
       <c r="C30" s="1" t="str">
@@ -3630,45 +3640,45 @@
         <f>IF(ISNUMBER(Octubre!E33),E8-Octubre!E33,"")</f>
         <v/>
       </c>
-      <c r="F30" s="1" t="str">
+      <c r="F30" s="1">
         <f>IF(ISNUMBER(Octubre!F33),F8-Octubre!F33,"")</f>
-        <v/>
+        <v>9053</v>
       </c>
       <c r="G30" s="1" t="str">
         <f>IF(ISNUMBER(Octubre!G33),G8-Octubre!G33,"")</f>
         <v/>
       </c>
-      <c r="H30" s="1" t="str">
+      <c r="H30" s="1">
         <f>IF(ISNUMBER(Octubre!H33),H8-Octubre!H33,"")</f>
-        <v/>
-      </c>
-      <c r="I30" s="1" t="str">
+        <v>8.4400000000000546</v>
+      </c>
+      <c r="I30" s="1">
         <f>IF(ISNUMBER(Octubre!I33),I8-Octubre!I33,"")</f>
-        <v/>
-      </c>
-      <c r="J30" s="1" t="str">
+        <v>-274.42999999999984</v>
+      </c>
+      <c r="J30" s="1">
         <f>IF(ISNUMBER(Octubre!J33),J8-Octubre!J33,"")</f>
-        <v/>
-      </c>
-      <c r="K30" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
         <f>IF(ISNUMBER(Octubre!K33),K8-Octubre!K33,"")</f>
-        <v/>
-      </c>
-      <c r="L30" s="1" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="L30" s="1">
         <f>IF(ISNUMBER(Octubre!L33),L8-Octubre!L33,"")</f>
-        <v/>
+        <v>9.9700000000011642</v>
       </c>
       <c r="M30" s="1" t="str">
         <f>IF(ISNUMBER(Octubre!M33),M8-Octubre!M33,"")</f>
         <v/>
       </c>
-      <c r="N30" s="1" t="str">
+      <c r="N30" s="1">
         <f>IF(ISNUMBER(Octubre!N33),N8-Octubre!N33,"")</f>
-        <v/>
-      </c>
-      <c r="O30" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="O30" s="1">
         <f>IF(ISNUMBER(Octubre!O33),O8-Octubre!O33,"")</f>
-        <v/>
+        <v>3908.19</v>
       </c>
       <c r="P30" s="1" t="str">
         <f>IF(ISNUMBER(Octubre!P33),P8-Octubre!P33,"")</f>
@@ -3678,17 +3688,17 @@
         <f>IF(ISNUMBER(Octubre!Q33),Q8-Octubre!Q33,"")</f>
         <v/>
       </c>
-      <c r="R30" s="1" t="str">
+      <c r="R30" s="1">
         <f>IF(ISNUMBER(Octubre!R33),R8-Octubre!R33,"")</f>
-        <v/>
+        <v>12980.89</v>
       </c>
       <c r="S30" s="1" t="str">
         <f>IF(ISNUMBER(Octubre!S33),S8-Octubre!S33,"")</f>
         <v/>
       </c>
-      <c r="T30" s="1" t="str">
+      <c r="T30" s="1">
         <f>IF(ISNUMBER(Octubre!T33),T8-Octubre!T33,"")</f>
-        <v/>
+        <v>3465.5699999999997</v>
       </c>
       <c r="U30" s="1" t="str">
         <f>IF(ISNUMBER(Octubre!U33),U8-Octubre!U33,"")</f>
@@ -3714,13 +3724,13 @@
         <f>IF(ISNUMBER(Octubre!Z33),Z8-Octubre!Z33,"")</f>
         <v/>
       </c>
-      <c r="AA30" s="1" t="str">
+      <c r="AA30" s="1">
         <f>IF(ISNUMBER(Octubre!AA33),AA8-Octubre!AA33,"")</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="AC30" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>31652.38</v>
       </c>
     </row>
     <row r="31" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3971,7 +3981,7 @@
       </c>
       <c r="F33" s="12">
         <f t="shared" si="8"/>
-        <v>-1178</v>
+        <v>7875</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="8"/>
@@ -3979,11 +3989,11 @@
       </c>
       <c r="H33" s="12">
         <f t="shared" si="8"/>
-        <v>425.32000000000016</v>
+        <v>433.76000000000022</v>
       </c>
       <c r="I33" s="12">
         <f t="shared" si="8"/>
-        <v>1076.5399999999995</v>
+        <v>802.10999999999967</v>
       </c>
       <c r="J33" s="12">
         <f t="shared" si="8"/>
@@ -3991,11 +4001,11 @@
       </c>
       <c r="K33" s="12">
         <f t="shared" si="8"/>
-        <v>101.29999999999791</v>
+        <v>102.04999999999791</v>
       </c>
       <c r="L33" s="12">
         <f t="shared" si="8"/>
-        <v>332.19999999999709</v>
+        <v>342.16999999999825</v>
       </c>
       <c r="M33" s="12">
         <f t="shared" si="8"/>
@@ -4007,7 +4017,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="8"/>
-        <v>10709.67</v>
+        <v>14617.86</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="8"/>
@@ -4019,7 +4029,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>-2580.0399999999972</v>
+        <v>10400.850000000002</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4027,7 +4037,7 @@
       </c>
       <c r="T33" s="12">
         <f t="shared" si="8"/>
-        <v>4037.9700000000007</v>
+        <v>7503.5400000000009</v>
       </c>
       <c r="U33" s="12">
         <f t="shared" si="8"/>
@@ -4055,11 +4065,11 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>-15313.599999999999</v>
+        <v>-12813.599999999999</v>
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>-8194.5099999999984</v>
+        <v>23457.869999999995</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11833,6 +11843,2772 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="17.140625" customWidth="1"/>
+    <col min="14" max="25" width="13" customWidth="1"/>
+    <col min="26" max="26" width="15.28515625" customWidth="1"/>
+    <col min="27" max="27" width="13" customWidth="1"/>
+    <col min="28" max="28" width="14" customWidth="1"/>
+    <col min="29" max="29" width="25" customWidth="1"/>
+    <col min="30" max="30" width="23.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="S1" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="T1" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="U1" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="V1" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="W1" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="X1" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y1" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z1" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA1" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC1" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD1" s="33" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="34">
+        <v>1</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35">
+        <f>1076-17.64</f>
+        <v>1058.3599999999999</v>
+      </c>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="35">
+        <f t="shared" ref="AC2:AC32" si="0">SUM(B2:AA2)</f>
+        <v>1058.3599999999999</v>
+      </c>
+      <c r="AD2" s="35"/>
+    </row>
+    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="34">
+        <v>2</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35">
+        <f>1237-39.84+540-18.97</f>
+        <v>1718.19</v>
+      </c>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="Y3" s="35"/>
+      <c r="Z3" s="35"/>
+      <c r="AA3" s="35"/>
+      <c r="AB3" s="36"/>
+      <c r="AC3" s="35">
+        <f t="shared" si="0"/>
+        <v>1718.19</v>
+      </c>
+      <c r="AD3" s="35"/>
+    </row>
+    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="34">
+        <v>3</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="43">
+        <v>18447</v>
+      </c>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35">
+        <f>500-8.19</f>
+        <v>491.81</v>
+      </c>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35">
+        <f>131-2.23</f>
+        <v>128.77000000000001</v>
+      </c>
+      <c r="S4" s="35"/>
+      <c r="T4" s="35">
+        <f>1300-21.31+260-4.26</f>
+        <v>1534.43</v>
+      </c>
+      <c r="U4" s="35"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35"/>
+      <c r="X4" s="35"/>
+      <c r="Y4" s="35"/>
+      <c r="Z4" s="35"/>
+      <c r="AA4" s="35"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="35">
+        <f t="shared" si="0"/>
+        <v>20602.010000000002</v>
+      </c>
+      <c r="AD4" s="35"/>
+    </row>
+    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="34">
+        <v>4</v>
+      </c>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
+      <c r="P5" s="35"/>
+      <c r="Q5" s="35"/>
+      <c r="R5" s="35">
+        <f>962+1100-15.77-18.03+1436-17.52+131-2.23</f>
+        <v>3575.45</v>
+      </c>
+      <c r="S5" s="35"/>
+      <c r="T5" s="35"/>
+      <c r="U5" s="35"/>
+      <c r="V5" s="35"/>
+      <c r="W5" s="35"/>
+      <c r="X5" s="35"/>
+      <c r="Y5" s="35"/>
+      <c r="Z5" s="35"/>
+      <c r="AA5" s="35"/>
+      <c r="AB5" s="36"/>
+      <c r="AC5" s="35">
+        <f t="shared" si="0"/>
+        <v>3575.45</v>
+      </c>
+      <c r="AD5" s="35"/>
+    </row>
+    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="34">
+        <v>5</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="35"/>
+      <c r="S6" s="35"/>
+      <c r="T6" s="35"/>
+      <c r="U6" s="35"/>
+      <c r="V6" s="35"/>
+      <c r="W6" s="35"/>
+      <c r="X6" s="35"/>
+      <c r="Y6" s="35"/>
+      <c r="Z6" s="35"/>
+      <c r="AA6" s="35"/>
+      <c r="AB6" s="36"/>
+      <c r="AC6" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD6" s="35"/>
+    </row>
+    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="34">
+        <v>6</v>
+      </c>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35">
+        <f>3327-35.44</f>
+        <v>3291.56</v>
+      </c>
+      <c r="I7" s="35">
+        <f>3329-54.57</f>
+        <v>3274.43</v>
+      </c>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35">
+        <v>26737.25</v>
+      </c>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="35">
+        <f>266-4.36</f>
+        <v>261.64</v>
+      </c>
+      <c r="S7" s="35"/>
+      <c r="T7" s="35"/>
+      <c r="U7" s="35"/>
+      <c r="V7" s="35"/>
+      <c r="W7" s="35"/>
+      <c r="X7" s="35"/>
+      <c r="Y7" s="35"/>
+      <c r="Z7" s="35"/>
+      <c r="AA7" s="35"/>
+      <c r="AB7" s="36"/>
+      <c r="AC7" s="35">
+        <f t="shared" si="0"/>
+        <v>33564.879999999997</v>
+      </c>
+      <c r="AD7" s="35"/>
+    </row>
+    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="34">
+        <v>7</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35">
+        <v>700</v>
+      </c>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35">
+        <v>810</v>
+      </c>
+      <c r="O8" s="35"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="35">
+        <f>281.35-4.65</f>
+        <v>276.70000000000005</v>
+      </c>
+      <c r="S8" s="35"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="35"/>
+      <c r="V8" s="35"/>
+      <c r="W8" s="35"/>
+      <c r="X8" s="35"/>
+      <c r="Y8" s="35"/>
+      <c r="Z8" s="35"/>
+      <c r="AA8" s="35"/>
+      <c r="AB8" s="36"/>
+      <c r="AC8" s="35">
+        <f t="shared" si="0"/>
+        <v>1786.7</v>
+      </c>
+      <c r="AD8" s="35"/>
+    </row>
+    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="34">
+        <v>8</v>
+      </c>
+      <c r="B9" s="35">
+        <f>76.49+18.15+21856+5187.5</f>
+        <v>27138.14</v>
+      </c>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="35"/>
+      <c r="Q9" s="35"/>
+      <c r="R9" s="35"/>
+      <c r="S9" s="35"/>
+      <c r="T9" s="35"/>
+      <c r="U9" s="35"/>
+      <c r="V9" s="35"/>
+      <c r="W9" s="35"/>
+      <c r="X9" s="35"/>
+      <c r="Y9" s="35"/>
+      <c r="Z9" s="35"/>
+      <c r="AA9" s="35">
+        <v>2500</v>
+      </c>
+      <c r="AB9" s="36"/>
+      <c r="AC9" s="35">
+        <f t="shared" si="0"/>
+        <v>29638.14</v>
+      </c>
+      <c r="AD9" s="35" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="34">
+        <v>9</v>
+      </c>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="35">
+        <f>9705.89+8284.14</f>
+        <v>17990.03</v>
+      </c>
+      <c r="M10" s="35"/>
+      <c r="N10" s="35"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="35"/>
+      <c r="Q10" s="35"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="35"/>
+      <c r="T10" s="35"/>
+      <c r="U10" s="35"/>
+      <c r="V10" s="35"/>
+      <c r="W10" s="35"/>
+      <c r="X10" s="35"/>
+      <c r="Y10" s="35"/>
+      <c r="Z10" s="35"/>
+      <c r="AA10" s="35"/>
+      <c r="AB10" s="36"/>
+      <c r="AC10" s="35">
+        <f t="shared" si="0"/>
+        <v>17990.03</v>
+      </c>
+      <c r="AD10" s="35"/>
+    </row>
+    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="34">
+        <v>10</v>
+      </c>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="35"/>
+      <c r="S11" s="35"/>
+      <c r="T11" s="35"/>
+      <c r="U11" s="35"/>
+      <c r="V11" s="35"/>
+      <c r="W11" s="35"/>
+      <c r="X11" s="35"/>
+      <c r="Y11" s="35"/>
+      <c r="Z11" s="35"/>
+      <c r="AA11" s="35"/>
+      <c r="AB11" s="36"/>
+      <c r="AC11" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="35"/>
+    </row>
+    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="34">
+        <v>11</v>
+      </c>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="35"/>
+      <c r="Q12" s="35"/>
+      <c r="R12" s="35"/>
+      <c r="S12" s="35"/>
+      <c r="T12" s="35"/>
+      <c r="U12" s="35"/>
+      <c r="V12" s="35"/>
+      <c r="W12" s="35"/>
+      <c r="X12" s="35"/>
+      <c r="Y12" s="35"/>
+      <c r="Z12" s="35"/>
+      <c r="AA12" s="35"/>
+      <c r="AB12" s="36"/>
+      <c r="AC12" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD12" s="35"/>
+    </row>
+    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="34">
+        <v>12</v>
+      </c>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="35"/>
+      <c r="S13" s="35"/>
+      <c r="T13" s="35"/>
+      <c r="U13" s="35"/>
+      <c r="V13" s="35"/>
+      <c r="W13" s="35"/>
+      <c r="X13" s="35"/>
+      <c r="Y13" s="35"/>
+      <c r="Z13" s="35"/>
+      <c r="AA13" s="35"/>
+      <c r="AB13" s="36"/>
+      <c r="AC13" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD13" s="35"/>
+    </row>
+    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="34">
+        <v>13</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="35"/>
+      <c r="U14" s="35"/>
+      <c r="V14" s="35"/>
+      <c r="W14" s="35"/>
+      <c r="X14" s="35"/>
+      <c r="Y14" s="35"/>
+      <c r="Z14" s="35"/>
+      <c r="AA14" s="35"/>
+      <c r="AB14" s="36"/>
+      <c r="AC14" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD14" s="35"/>
+    </row>
+    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="34">
+        <v>14</v>
+      </c>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="35"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="35"/>
+      <c r="U15" s="35"/>
+      <c r="V15" s="35"/>
+      <c r="W15" s="35"/>
+      <c r="X15" s="35"/>
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="35"/>
+      <c r="AA15" s="35"/>
+      <c r="AB15" s="36"/>
+      <c r="AC15" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD15" s="35"/>
+    </row>
+    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="34">
+        <v>15</v>
+      </c>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="35"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="35"/>
+      <c r="U16" s="35"/>
+      <c r="V16" s="35"/>
+      <c r="W16" s="35"/>
+      <c r="X16" s="35"/>
+      <c r="Y16" s="35"/>
+      <c r="Z16" s="35"/>
+      <c r="AA16" s="35"/>
+      <c r="AB16" s="36"/>
+      <c r="AC16" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="35"/>
+    </row>
+    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="34">
+        <v>16</v>
+      </c>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="35"/>
+      <c r="S17" s="35"/>
+      <c r="T17" s="35"/>
+      <c r="U17" s="35"/>
+      <c r="V17" s="35"/>
+      <c r="W17" s="35"/>
+      <c r="X17" s="35"/>
+      <c r="Y17" s="35"/>
+      <c r="Z17" s="35"/>
+      <c r="AA17" s="35"/>
+      <c r="AB17" s="36"/>
+      <c r="AC17" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD17" s="35"/>
+    </row>
+    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="34">
+        <v>17</v>
+      </c>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="35"/>
+      <c r="T18" s="35"/>
+      <c r="U18" s="35"/>
+      <c r="V18" s="35"/>
+      <c r="W18" s="35"/>
+      <c r="X18" s="35"/>
+      <c r="Y18" s="35"/>
+      <c r="Z18" s="35"/>
+      <c r="AA18" s="35"/>
+      <c r="AB18" s="36"/>
+      <c r="AC18" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD18" s="35"/>
+    </row>
+    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="34">
+        <v>18</v>
+      </c>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="35"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="35"/>
+      <c r="V19" s="35"/>
+      <c r="W19" s="35"/>
+      <c r="X19" s="35"/>
+      <c r="Y19" s="35"/>
+      <c r="Z19" s="35"/>
+      <c r="AA19" s="35"/>
+      <c r="AB19" s="36"/>
+      <c r="AC19" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD19" s="35"/>
+    </row>
+    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="34">
+        <v>19</v>
+      </c>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="35"/>
+      <c r="R20" s="35"/>
+      <c r="S20" s="35"/>
+      <c r="T20" s="35"/>
+      <c r="U20" s="35"/>
+      <c r="V20" s="35"/>
+      <c r="W20" s="35"/>
+      <c r="X20" s="35"/>
+      <c r="Y20" s="35"/>
+      <c r="Z20" s="35"/>
+      <c r="AA20" s="35"/>
+      <c r="AB20" s="36"/>
+      <c r="AC20" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD20" s="35"/>
+    </row>
+    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="34">
+        <v>20</v>
+      </c>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="35"/>
+      <c r="Q21" s="35"/>
+      <c r="R21" s="35"/>
+      <c r="S21" s="35"/>
+      <c r="T21" s="35"/>
+      <c r="U21" s="35"/>
+      <c r="V21" s="35"/>
+      <c r="W21" s="35"/>
+      <c r="X21" s="35"/>
+      <c r="Y21" s="35"/>
+      <c r="Z21" s="35"/>
+      <c r="AA21" s="35"/>
+      <c r="AB21" s="36"/>
+      <c r="AC21" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD21" s="35"/>
+    </row>
+    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="34">
+        <v>21</v>
+      </c>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="35"/>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="35"/>
+      <c r="S22" s="35"/>
+      <c r="T22" s="35"/>
+      <c r="U22" s="35"/>
+      <c r="V22" s="35"/>
+      <c r="W22" s="35"/>
+      <c r="X22" s="35"/>
+      <c r="Y22" s="35"/>
+      <c r="Z22" s="35"/>
+      <c r="AA22" s="35"/>
+      <c r="AB22" s="36"/>
+      <c r="AC22" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD22" s="35"/>
+    </row>
+    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="34">
+        <v>22</v>
+      </c>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="35"/>
+      <c r="S23" s="35"/>
+      <c r="T23" s="35"/>
+      <c r="U23" s="35"/>
+      <c r="V23" s="35"/>
+      <c r="W23" s="35"/>
+      <c r="X23" s="35"/>
+      <c r="Y23" s="35"/>
+      <c r="Z23" s="35"/>
+      <c r="AA23" s="35"/>
+      <c r="AB23" s="36"/>
+      <c r="AC23" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD23" s="35"/>
+    </row>
+    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="34">
+        <v>23</v>
+      </c>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="35"/>
+      <c r="Q24" s="35"/>
+      <c r="R24" s="35"/>
+      <c r="S24" s="35"/>
+      <c r="T24" s="35"/>
+      <c r="U24" s="35"/>
+      <c r="V24" s="35"/>
+      <c r="W24" s="35"/>
+      <c r="X24" s="35"/>
+      <c r="Y24" s="35"/>
+      <c r="Z24" s="35"/>
+      <c r="AA24" s="35"/>
+      <c r="AB24" s="36"/>
+      <c r="AC24" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD24" s="35"/>
+    </row>
+    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="34">
+        <v>24</v>
+      </c>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="35"/>
+      <c r="Q25" s="35"/>
+      <c r="R25" s="35"/>
+      <c r="S25" s="35"/>
+      <c r="T25" s="35"/>
+      <c r="U25" s="35"/>
+      <c r="V25" s="35"/>
+      <c r="W25" s="35"/>
+      <c r="X25" s="35"/>
+      <c r="Y25" s="35"/>
+      <c r="Z25" s="35"/>
+      <c r="AA25" s="35"/>
+      <c r="AB25" s="36"/>
+      <c r="AC25" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD25" s="35"/>
+    </row>
+    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="34">
+        <v>25</v>
+      </c>
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="35"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="35"/>
+      <c r="Q26" s="35"/>
+      <c r="R26" s="35"/>
+      <c r="S26" s="35"/>
+      <c r="T26" s="35"/>
+      <c r="U26" s="35"/>
+      <c r="V26" s="35"/>
+      <c r="W26" s="35"/>
+      <c r="X26" s="35"/>
+      <c r="Y26" s="35"/>
+      <c r="Z26" s="35"/>
+      <c r="AA26" s="35"/>
+      <c r="AB26" s="36"/>
+      <c r="AC26" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD26" s="35"/>
+    </row>
+    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="34">
+        <v>26</v>
+      </c>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="35"/>
+      <c r="N27" s="35"/>
+      <c r="O27" s="35"/>
+      <c r="P27" s="35"/>
+      <c r="Q27" s="35"/>
+      <c r="R27" s="35"/>
+      <c r="S27" s="35"/>
+      <c r="T27" s="35"/>
+      <c r="U27" s="35"/>
+      <c r="V27" s="35"/>
+      <c r="W27" s="35"/>
+      <c r="X27" s="35"/>
+      <c r="Y27" s="35"/>
+      <c r="Z27" s="35"/>
+      <c r="AA27" s="35"/>
+      <c r="AB27" s="36"/>
+      <c r="AC27" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD27" s="35"/>
+    </row>
+    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="34">
+        <v>27</v>
+      </c>
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="35"/>
+      <c r="O28" s="35"/>
+      <c r="P28" s="35"/>
+      <c r="Q28" s="35"/>
+      <c r="R28" s="35"/>
+      <c r="S28" s="35"/>
+      <c r="T28" s="35"/>
+      <c r="U28" s="35"/>
+      <c r="V28" s="35"/>
+      <c r="W28" s="35"/>
+      <c r="X28" s="35"/>
+      <c r="Y28" s="35"/>
+      <c r="Z28" s="35"/>
+      <c r="AA28" s="35"/>
+      <c r="AB28" s="36"/>
+      <c r="AC28" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD28" s="35"/>
+    </row>
+    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="34">
+        <v>28</v>
+      </c>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
+      <c r="O29" s="35"/>
+      <c r="P29" s="35"/>
+      <c r="Q29" s="35"/>
+      <c r="R29" s="35"/>
+      <c r="S29" s="35"/>
+      <c r="T29" s="35"/>
+      <c r="U29" s="35"/>
+      <c r="V29" s="35"/>
+      <c r="W29" s="35"/>
+      <c r="X29" s="35"/>
+      <c r="Y29" s="35"/>
+      <c r="Z29" s="35"/>
+      <c r="AA29" s="35"/>
+      <c r="AB29" s="36"/>
+      <c r="AC29" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD29" s="35"/>
+    </row>
+    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="34">
+        <v>29</v>
+      </c>
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
+      <c r="N30" s="35"/>
+      <c r="O30" s="35"/>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="35"/>
+      <c r="R30" s="35"/>
+      <c r="S30" s="35"/>
+      <c r="T30" s="35"/>
+      <c r="U30" s="35"/>
+      <c r="V30" s="35"/>
+      <c r="W30" s="35"/>
+      <c r="X30" s="35"/>
+      <c r="Y30" s="35"/>
+      <c r="Z30" s="35"/>
+      <c r="AA30" s="35"/>
+      <c r="AB30" s="36"/>
+      <c r="AC30" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD30" s="35"/>
+    </row>
+    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="34">
+        <v>30</v>
+      </c>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="35"/>
+      <c r="V31" s="35"/>
+      <c r="W31" s="35"/>
+      <c r="X31" s="35"/>
+      <c r="Y31" s="35"/>
+      <c r="Z31" s="35"/>
+      <c r="AA31" s="35"/>
+      <c r="AB31" s="36"/>
+      <c r="AC31" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD31" s="35"/>
+    </row>
+    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="34">
+        <v>31</v>
+      </c>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="35"/>
+      <c r="N32" s="35"/>
+      <c r="O32" s="35"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="35"/>
+      <c r="R32" s="35"/>
+      <c r="S32" s="35"/>
+      <c r="T32" s="35"/>
+      <c r="U32" s="35"/>
+      <c r="V32" s="35"/>
+      <c r="W32" s="35"/>
+      <c r="X32" s="35"/>
+      <c r="Y32" s="35"/>
+      <c r="Z32" s="35"/>
+      <c r="AA32" s="35"/>
+      <c r="AB32" s="36"/>
+      <c r="AC32" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD32" s="35"/>
+    </row>
+    <row r="33" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="12">
+        <f>IF(COUNTA(B2:B32)&gt;0,SUM(B2:B32),"")</f>
+        <v>27138.14</v>
+      </c>
+      <c r="C33" s="12" t="str">
+        <f t="shared" ref="B33:AC33" si="1">IF(COUNTA(C2:C32)&gt;0,SUM(C2:C32),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="E33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F33" s="12">
+        <f t="shared" si="1"/>
+        <v>18447</v>
+      </c>
+      <c r="G33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H33" s="12">
+        <f t="shared" si="1"/>
+        <v>3291.56</v>
+      </c>
+      <c r="I33" s="12">
+        <f t="shared" si="1"/>
+        <v>3274.43</v>
+      </c>
+      <c r="J33" s="12">
+        <f t="shared" si="1"/>
+        <v>700</v>
+      </c>
+      <c r="K33" s="12">
+        <f t="shared" si="1"/>
+        <v>26737.25</v>
+      </c>
+      <c r="L33" s="12">
+        <f t="shared" si="1"/>
+        <v>17990.03</v>
+      </c>
+      <c r="M33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="N33" s="12">
+        <f t="shared" si="1"/>
+        <v>810</v>
+      </c>
+      <c r="O33" s="12">
+        <f t="shared" si="1"/>
+        <v>491.81</v>
+      </c>
+      <c r="P33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="R33" s="12">
+        <f t="shared" si="1"/>
+        <v>7019.1100000000006</v>
+      </c>
+      <c r="S33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="T33" s="12">
+        <f t="shared" si="1"/>
+        <v>1534.43</v>
+      </c>
+      <c r="U33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="V33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="X33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Y33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Z33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AA33" s="12">
+        <f t="shared" si="1"/>
+        <v>2500</v>
+      </c>
+      <c r="AB33" s="38" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AC33" s="12">
+        <f t="shared" si="1"/>
+        <v>109933.75999999999</v>
+      </c>
+      <c r="AD33" s="39"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AD32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="27" width="13" customWidth="1"/>
+    <col min="28" max="28" width="14" customWidth="1"/>
+    <col min="29" max="29" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="S1" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="T1" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="U1" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="V1" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="W1" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="X1" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y1" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z1" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA1" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC1" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD1" s="33" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="34">
+        <v>1</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="35">
+        <f t="shared" ref="AC2:AC31" si="0">SUM(B2:AA2)</f>
+        <v>0</v>
+      </c>
+      <c r="AD2" s="35"/>
+    </row>
+    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="34">
+        <v>2</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="Y3" s="35"/>
+      <c r="Z3" s="35"/>
+      <c r="AA3" s="35"/>
+      <c r="AB3" s="36"/>
+      <c r="AC3" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD3" s="35"/>
+    </row>
+    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="34">
+        <v>3</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="35"/>
+      <c r="T4" s="35"/>
+      <c r="U4" s="35"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35"/>
+      <c r="X4" s="35"/>
+      <c r="Y4" s="35"/>
+      <c r="Z4" s="35"/>
+      <c r="AA4" s="35"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD4" s="35"/>
+    </row>
+    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="34">
+        <v>4</v>
+      </c>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
+      <c r="P5" s="35"/>
+      <c r="Q5" s="35"/>
+      <c r="R5" s="35"/>
+      <c r="S5" s="35"/>
+      <c r="T5" s="35"/>
+      <c r="U5" s="35"/>
+      <c r="V5" s="35"/>
+      <c r="W5" s="35"/>
+      <c r="X5" s="35"/>
+      <c r="Y5" s="35"/>
+      <c r="Z5" s="35"/>
+      <c r="AA5" s="35"/>
+      <c r="AB5" s="36"/>
+      <c r="AC5" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD5" s="35"/>
+    </row>
+    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="34">
+        <v>5</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="35"/>
+      <c r="S6" s="35"/>
+      <c r="T6" s="35"/>
+      <c r="U6" s="35"/>
+      <c r="V6" s="35"/>
+      <c r="W6" s="35"/>
+      <c r="X6" s="35"/>
+      <c r="Y6" s="35"/>
+      <c r="Z6" s="35"/>
+      <c r="AA6" s="35"/>
+      <c r="AB6" s="36"/>
+      <c r="AC6" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD6" s="35"/>
+    </row>
+    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="34">
+        <v>6</v>
+      </c>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="35"/>
+      <c r="S7" s="35"/>
+      <c r="T7" s="35"/>
+      <c r="U7" s="35"/>
+      <c r="V7" s="35"/>
+      <c r="W7" s="35"/>
+      <c r="X7" s="35"/>
+      <c r="Y7" s="35"/>
+      <c r="Z7" s="35"/>
+      <c r="AA7" s="35"/>
+      <c r="AB7" s="36"/>
+      <c r="AC7" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD7" s="35"/>
+    </row>
+    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="34">
+        <v>7</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="35"/>
+      <c r="S8" s="35"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="35"/>
+      <c r="V8" s="35"/>
+      <c r="W8" s="35"/>
+      <c r="X8" s="35"/>
+      <c r="Y8" s="35"/>
+      <c r="Z8" s="35"/>
+      <c r="AA8" s="35"/>
+      <c r="AB8" s="36"/>
+      <c r="AC8" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD8" s="35"/>
+    </row>
+    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="34">
+        <v>8</v>
+      </c>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="35"/>
+      <c r="Q9" s="35"/>
+      <c r="R9" s="35"/>
+      <c r="S9" s="35"/>
+      <c r="T9" s="35"/>
+      <c r="U9" s="35"/>
+      <c r="V9" s="35"/>
+      <c r="W9" s="35"/>
+      <c r="X9" s="35"/>
+      <c r="Y9" s="35"/>
+      <c r="Z9" s="35"/>
+      <c r="AA9" s="35"/>
+      <c r="AB9" s="36"/>
+      <c r="AC9" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD9" s="35"/>
+    </row>
+    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="34">
+        <v>9</v>
+      </c>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="35"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="35"/>
+      <c r="Q10" s="35"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="35"/>
+      <c r="T10" s="35"/>
+      <c r="U10" s="35"/>
+      <c r="V10" s="35"/>
+      <c r="W10" s="35"/>
+      <c r="X10" s="35"/>
+      <c r="Y10" s="35"/>
+      <c r="Z10" s="35"/>
+      <c r="AA10" s="35"/>
+      <c r="AB10" s="36"/>
+      <c r="AC10" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD10" s="35"/>
+    </row>
+    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="34">
+        <v>10</v>
+      </c>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="35"/>
+      <c r="S11" s="35"/>
+      <c r="T11" s="35"/>
+      <c r="U11" s="35"/>
+      <c r="V11" s="35"/>
+      <c r="W11" s="35"/>
+      <c r="X11" s="35"/>
+      <c r="Y11" s="35"/>
+      <c r="Z11" s="35"/>
+      <c r="AA11" s="35"/>
+      <c r="AB11" s="36"/>
+      <c r="AC11" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="35"/>
+    </row>
+    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="34">
+        <v>11</v>
+      </c>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="35"/>
+      <c r="Q12" s="35"/>
+      <c r="R12" s="35"/>
+      <c r="S12" s="35"/>
+      <c r="T12" s="35"/>
+      <c r="U12" s="35"/>
+      <c r="V12" s="35"/>
+      <c r="W12" s="35"/>
+      <c r="X12" s="35"/>
+      <c r="Y12" s="35"/>
+      <c r="Z12" s="35"/>
+      <c r="AA12" s="35"/>
+      <c r="AB12" s="36"/>
+      <c r="AC12" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD12" s="35"/>
+    </row>
+    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="34">
+        <v>12</v>
+      </c>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="35"/>
+      <c r="S13" s="35"/>
+      <c r="T13" s="35"/>
+      <c r="U13" s="35"/>
+      <c r="V13" s="35"/>
+      <c r="W13" s="35"/>
+      <c r="X13" s="35"/>
+      <c r="Y13" s="35"/>
+      <c r="Z13" s="35"/>
+      <c r="AA13" s="35"/>
+      <c r="AB13" s="36"/>
+      <c r="AC13" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD13" s="35"/>
+    </row>
+    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="34">
+        <v>13</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="35"/>
+      <c r="U14" s="35"/>
+      <c r="V14" s="35"/>
+      <c r="W14" s="35"/>
+      <c r="X14" s="35"/>
+      <c r="Y14" s="35"/>
+      <c r="Z14" s="35"/>
+      <c r="AA14" s="35"/>
+      <c r="AB14" s="36"/>
+      <c r="AC14" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD14" s="35"/>
+    </row>
+    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="34">
+        <v>14</v>
+      </c>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="35"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="35"/>
+      <c r="U15" s="35"/>
+      <c r="V15" s="35"/>
+      <c r="W15" s="35"/>
+      <c r="X15" s="35"/>
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="35"/>
+      <c r="AA15" s="35"/>
+      <c r="AB15" s="36"/>
+      <c r="AC15" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD15" s="35"/>
+    </row>
+    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="34">
+        <v>15</v>
+      </c>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="35"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="35"/>
+      <c r="U16" s="35"/>
+      <c r="V16" s="35"/>
+      <c r="W16" s="35"/>
+      <c r="X16" s="35"/>
+      <c r="Y16" s="35"/>
+      <c r="Z16" s="35"/>
+      <c r="AA16" s="35"/>
+      <c r="AB16" s="36"/>
+      <c r="AC16" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="35"/>
+    </row>
+    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="34">
+        <v>16</v>
+      </c>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="35"/>
+      <c r="S17" s="35"/>
+      <c r="T17" s="35"/>
+      <c r="U17" s="35"/>
+      <c r="V17" s="35"/>
+      <c r="W17" s="35"/>
+      <c r="X17" s="35"/>
+      <c r="Y17" s="35"/>
+      <c r="Z17" s="35"/>
+      <c r="AA17" s="35"/>
+      <c r="AB17" s="36"/>
+      <c r="AC17" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD17" s="35"/>
+    </row>
+    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="34">
+        <v>17</v>
+      </c>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="35"/>
+      <c r="T18" s="35"/>
+      <c r="U18" s="35"/>
+      <c r="V18" s="35"/>
+      <c r="W18" s="35"/>
+      <c r="X18" s="35"/>
+      <c r="Y18" s="35"/>
+      <c r="Z18" s="35"/>
+      <c r="AA18" s="35"/>
+      <c r="AB18" s="36"/>
+      <c r="AC18" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD18" s="35"/>
+    </row>
+    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="34">
+        <v>18</v>
+      </c>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="35"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="35"/>
+      <c r="V19" s="35"/>
+      <c r="W19" s="35"/>
+      <c r="X19" s="35"/>
+      <c r="Y19" s="35"/>
+      <c r="Z19" s="35"/>
+      <c r="AA19" s="35"/>
+      <c r="AB19" s="36"/>
+      <c r="AC19" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD19" s="35"/>
+    </row>
+    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="34">
+        <v>19</v>
+      </c>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="35"/>
+      <c r="R20" s="35"/>
+      <c r="S20" s="35"/>
+      <c r="T20" s="35"/>
+      <c r="U20" s="35"/>
+      <c r="V20" s="35"/>
+      <c r="W20" s="35"/>
+      <c r="X20" s="35"/>
+      <c r="Y20" s="35"/>
+      <c r="Z20" s="35"/>
+      <c r="AA20" s="35"/>
+      <c r="AB20" s="36"/>
+      <c r="AC20" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD20" s="35"/>
+    </row>
+    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="34">
+        <v>20</v>
+      </c>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="35"/>
+      <c r="Q21" s="35"/>
+      <c r="R21" s="35"/>
+      <c r="S21" s="35"/>
+      <c r="T21" s="35"/>
+      <c r="U21" s="35"/>
+      <c r="V21" s="35"/>
+      <c r="W21" s="35"/>
+      <c r="X21" s="35"/>
+      <c r="Y21" s="35"/>
+      <c r="Z21" s="35"/>
+      <c r="AA21" s="35"/>
+      <c r="AB21" s="36"/>
+      <c r="AC21" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD21" s="35"/>
+    </row>
+    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="34">
+        <v>21</v>
+      </c>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="35"/>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="35"/>
+      <c r="S22" s="35"/>
+      <c r="T22" s="35"/>
+      <c r="U22" s="35"/>
+      <c r="V22" s="35"/>
+      <c r="W22" s="35"/>
+      <c r="X22" s="35"/>
+      <c r="Y22" s="35"/>
+      <c r="Z22" s="35"/>
+      <c r="AA22" s="35"/>
+      <c r="AB22" s="36"/>
+      <c r="AC22" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD22" s="35"/>
+    </row>
+    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="34">
+        <v>22</v>
+      </c>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="35"/>
+      <c r="S23" s="35"/>
+      <c r="T23" s="35"/>
+      <c r="U23" s="35"/>
+      <c r="V23" s="35"/>
+      <c r="W23" s="35"/>
+      <c r="X23" s="35"/>
+      <c r="Y23" s="35"/>
+      <c r="Z23" s="35"/>
+      <c r="AA23" s="35"/>
+      <c r="AB23" s="36"/>
+      <c r="AC23" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD23" s="35"/>
+    </row>
+    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="34">
+        <v>23</v>
+      </c>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="35"/>
+      <c r="Q24" s="35"/>
+      <c r="R24" s="35"/>
+      <c r="S24" s="35"/>
+      <c r="T24" s="35"/>
+      <c r="U24" s="35"/>
+      <c r="V24" s="35"/>
+      <c r="W24" s="35"/>
+      <c r="X24" s="35"/>
+      <c r="Y24" s="35"/>
+      <c r="Z24" s="35"/>
+      <c r="AA24" s="35"/>
+      <c r="AB24" s="36"/>
+      <c r="AC24" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD24" s="35"/>
+    </row>
+    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="34">
+        <v>24</v>
+      </c>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="35"/>
+      <c r="Q25" s="35"/>
+      <c r="R25" s="35"/>
+      <c r="S25" s="35"/>
+      <c r="T25" s="35"/>
+      <c r="U25" s="35"/>
+      <c r="V25" s="35"/>
+      <c r="W25" s="35"/>
+      <c r="X25" s="35"/>
+      <c r="Y25" s="35"/>
+      <c r="Z25" s="35"/>
+      <c r="AA25" s="35"/>
+      <c r="AB25" s="36"/>
+      <c r="AC25" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD25" s="35"/>
+    </row>
+    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="34">
+        <v>25</v>
+      </c>
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="35"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="35"/>
+      <c r="Q26" s="35"/>
+      <c r="R26" s="35"/>
+      <c r="S26" s="35"/>
+      <c r="T26" s="35"/>
+      <c r="U26" s="35"/>
+      <c r="V26" s="35"/>
+      <c r="W26" s="35"/>
+      <c r="X26" s="35"/>
+      <c r="Y26" s="35"/>
+      <c r="Z26" s="35"/>
+      <c r="AA26" s="35"/>
+      <c r="AB26" s="36"/>
+      <c r="AC26" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD26" s="35"/>
+    </row>
+    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="34">
+        <v>26</v>
+      </c>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="35"/>
+      <c r="N27" s="35"/>
+      <c r="O27" s="35"/>
+      <c r="P27" s="35"/>
+      <c r="Q27" s="35"/>
+      <c r="R27" s="35"/>
+      <c r="S27" s="35"/>
+      <c r="T27" s="35"/>
+      <c r="U27" s="35"/>
+      <c r="V27" s="35"/>
+      <c r="W27" s="35"/>
+      <c r="X27" s="35"/>
+      <c r="Y27" s="35"/>
+      <c r="Z27" s="35"/>
+      <c r="AA27" s="35"/>
+      <c r="AB27" s="36"/>
+      <c r="AC27" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD27" s="35"/>
+    </row>
+    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="34">
+        <v>27</v>
+      </c>
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="35"/>
+      <c r="O28" s="35"/>
+      <c r="P28" s="35"/>
+      <c r="Q28" s="35"/>
+      <c r="R28" s="35"/>
+      <c r="S28" s="35"/>
+      <c r="T28" s="35"/>
+      <c r="U28" s="35"/>
+      <c r="V28" s="35"/>
+      <c r="W28" s="35"/>
+      <c r="X28" s="35"/>
+      <c r="Y28" s="35"/>
+      <c r="Z28" s="35"/>
+      <c r="AA28" s="35"/>
+      <c r="AB28" s="36"/>
+      <c r="AC28" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD28" s="35"/>
+    </row>
+    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="34">
+        <v>28</v>
+      </c>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
+      <c r="O29" s="35"/>
+      <c r="P29" s="35"/>
+      <c r="Q29" s="35"/>
+      <c r="R29" s="35"/>
+      <c r="S29" s="35"/>
+      <c r="T29" s="35"/>
+      <c r="U29" s="35"/>
+      <c r="V29" s="35"/>
+      <c r="W29" s="35"/>
+      <c r="X29" s="35"/>
+      <c r="Y29" s="35"/>
+      <c r="Z29" s="35"/>
+      <c r="AA29" s="35"/>
+      <c r="AB29" s="36"/>
+      <c r="AC29" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD29" s="35"/>
+    </row>
+    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="34">
+        <v>29</v>
+      </c>
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
+      <c r="N30" s="35"/>
+      <c r="O30" s="35"/>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="35"/>
+      <c r="R30" s="35"/>
+      <c r="S30" s="35"/>
+      <c r="T30" s="35"/>
+      <c r="U30" s="35"/>
+      <c r="V30" s="35"/>
+      <c r="W30" s="35"/>
+      <c r="X30" s="35"/>
+      <c r="Y30" s="35"/>
+      <c r="Z30" s="35"/>
+      <c r="AA30" s="35"/>
+      <c r="AB30" s="36"/>
+      <c r="AC30" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD30" s="35"/>
+    </row>
+    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="34">
+        <v>30</v>
+      </c>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="35"/>
+      <c r="V31" s="35"/>
+      <c r="W31" s="35"/>
+      <c r="X31" s="35"/>
+      <c r="Y31" s="35"/>
+      <c r="Z31" s="35"/>
+      <c r="AA31" s="35"/>
+      <c r="AB31" s="36"/>
+      <c r="AC31" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD31" s="35"/>
+    </row>
+    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="12" t="str">
+        <f t="shared" ref="B32:AC32" si="1">IF(COUNTA(B2:B31)&gt;0,SUM(B2:B31),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="D32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="E32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="G32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="N32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="P32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="R32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="S32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="T32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="U32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="V32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="X32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Y32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Z32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AA32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AB32" s="38" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AC32" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD32" s="39"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AD33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="27" width="13" customWidth="1"/>
     <col min="28" max="28" width="14" customWidth="1"/>
     <col min="29" max="29" width="25" customWidth="1"/>
@@ -13199,2715 +15975,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="27" width="13" customWidth="1"/>
-    <col min="28" max="28" width="14" customWidth="1"/>
-    <col min="29" max="29" width="25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="T1" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="U1" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="V1" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="W1" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="X1" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y1" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z1" s="33" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA1" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC1" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD1" s="33" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34">
-        <v>1</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="36"/>
-      <c r="AC2" s="35">
-        <f t="shared" ref="AC2:AC31" si="0">SUM(B2:AA2)</f>
-        <v>0</v>
-      </c>
-      <c r="AD2" s="35"/>
-    </row>
-    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="34">
-        <v>2</v>
-      </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
-      <c r="S3" s="35"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="35"/>
-      <c r="V3" s="35"/>
-      <c r="W3" s="35"/>
-      <c r="X3" s="35"/>
-      <c r="Y3" s="35"/>
-      <c r="Z3" s="35"/>
-      <c r="AA3" s="35"/>
-      <c r="AB3" s="36"/>
-      <c r="AC3" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD3" s="35"/>
-    </row>
-    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="34">
-        <v>3</v>
-      </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="35"/>
-      <c r="V4" s="35"/>
-      <c r="W4" s="35"/>
-      <c r="X4" s="35"/>
-      <c r="Y4" s="35"/>
-      <c r="Z4" s="35"/>
-      <c r="AA4" s="35"/>
-      <c r="AB4" s="36"/>
-      <c r="AC4" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD4" s="35"/>
-    </row>
-    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="34">
-        <v>4</v>
-      </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="35"/>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="35"/>
-      <c r="T5" s="35"/>
-      <c r="U5" s="35"/>
-      <c r="V5" s="35"/>
-      <c r="W5" s="35"/>
-      <c r="X5" s="35"/>
-      <c r="Y5" s="35"/>
-      <c r="Z5" s="35"/>
-      <c r="AA5" s="35"/>
-      <c r="AB5" s="36"/>
-      <c r="AC5" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD5" s="35"/>
-    </row>
-    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34">
-        <v>5</v>
-      </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
-      <c r="S6" s="35"/>
-      <c r="T6" s="35"/>
-      <c r="U6" s="35"/>
-      <c r="V6" s="35"/>
-      <c r="W6" s="35"/>
-      <c r="X6" s="35"/>
-      <c r="Y6" s="35"/>
-      <c r="Z6" s="35"/>
-      <c r="AA6" s="35"/>
-      <c r="AB6" s="36"/>
-      <c r="AC6" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD6" s="35"/>
-    </row>
-    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="34">
-        <v>6</v>
-      </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="35"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
-      <c r="N7" s="35"/>
-      <c r="O7" s="35"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-      <c r="R7" s="35"/>
-      <c r="S7" s="35"/>
-      <c r="T7" s="35"/>
-      <c r="U7" s="35"/>
-      <c r="V7" s="35"/>
-      <c r="W7" s="35"/>
-      <c r="X7" s="35"/>
-      <c r="Y7" s="35"/>
-      <c r="Z7" s="35"/>
-      <c r="AA7" s="35"/>
-      <c r="AB7" s="36"/>
-      <c r="AC7" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD7" s="35"/>
-    </row>
-    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34">
-        <v>7</v>
-      </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
-      <c r="N8" s="35"/>
-      <c r="O8" s="35"/>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="35"/>
-      <c r="S8" s="35"/>
-      <c r="T8" s="35"/>
-      <c r="U8" s="35"/>
-      <c r="V8" s="35"/>
-      <c r="W8" s="35"/>
-      <c r="X8" s="35"/>
-      <c r="Y8" s="35"/>
-      <c r="Z8" s="35"/>
-      <c r="AA8" s="35"/>
-      <c r="AB8" s="36"/>
-      <c r="AC8" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD8" s="35"/>
-    </row>
-    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="34">
-        <v>8</v>
-      </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
-      <c r="N9" s="35"/>
-      <c r="O9" s="35"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="35"/>
-      <c r="S9" s="35"/>
-      <c r="T9" s="35"/>
-      <c r="U9" s="35"/>
-      <c r="V9" s="35"/>
-      <c r="W9" s="35"/>
-      <c r="X9" s="35"/>
-      <c r="Y9" s="35"/>
-      <c r="Z9" s="35"/>
-      <c r="AA9" s="35"/>
-      <c r="AB9" s="36"/>
-      <c r="AC9" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD9" s="35"/>
-    </row>
-    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="34">
-        <v>9</v>
-      </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="35"/>
-      <c r="V10" s="35"/>
-      <c r="W10" s="35"/>
-      <c r="X10" s="35"/>
-      <c r="Y10" s="35"/>
-      <c r="Z10" s="35"/>
-      <c r="AA10" s="35"/>
-      <c r="AB10" s="36"/>
-      <c r="AC10" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD10" s="35"/>
-    </row>
-    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="34">
-        <v>10</v>
-      </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="35"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="35"/>
-      <c r="O11" s="35"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="35"/>
-      <c r="T11" s="35"/>
-      <c r="U11" s="35"/>
-      <c r="V11" s="35"/>
-      <c r="W11" s="35"/>
-      <c r="X11" s="35"/>
-      <c r="Y11" s="35"/>
-      <c r="Z11" s="35"/>
-      <c r="AA11" s="35"/>
-      <c r="AB11" s="36"/>
-      <c r="AC11" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD11" s="35"/>
-    </row>
-    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="34">
-        <v>11</v>
-      </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="35"/>
-      <c r="P12" s="35"/>
-      <c r="Q12" s="35"/>
-      <c r="R12" s="35"/>
-      <c r="S12" s="35"/>
-      <c r="T12" s="35"/>
-      <c r="U12" s="35"/>
-      <c r="V12" s="35"/>
-      <c r="W12" s="35"/>
-      <c r="X12" s="35"/>
-      <c r="Y12" s="35"/>
-      <c r="Z12" s="35"/>
-      <c r="AA12" s="35"/>
-      <c r="AB12" s="36"/>
-      <c r="AC12" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD12" s="35"/>
-    </row>
-    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="34">
-        <v>12</v>
-      </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
-      <c r="N13" s="35"/>
-      <c r="O13" s="35"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="35"/>
-      <c r="S13" s="35"/>
-      <c r="T13" s="35"/>
-      <c r="U13" s="35"/>
-      <c r="V13" s="35"/>
-      <c r="W13" s="35"/>
-      <c r="X13" s="35"/>
-      <c r="Y13" s="35"/>
-      <c r="Z13" s="35"/>
-      <c r="AA13" s="35"/>
-      <c r="AB13" s="36"/>
-      <c r="AC13" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD13" s="35"/>
-    </row>
-    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="34">
-        <v>13</v>
-      </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
-      <c r="R14" s="35"/>
-      <c r="S14" s="35"/>
-      <c r="T14" s="35"/>
-      <c r="U14" s="35"/>
-      <c r="V14" s="35"/>
-      <c r="W14" s="35"/>
-      <c r="X14" s="35"/>
-      <c r="Y14" s="35"/>
-      <c r="Z14" s="35"/>
-      <c r="AA14" s="35"/>
-      <c r="AB14" s="36"/>
-      <c r="AC14" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD14" s="35"/>
-    </row>
-    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34">
-        <v>14</v>
-      </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
-      <c r="S15" s="35"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="35"/>
-      <c r="V15" s="35"/>
-      <c r="W15" s="35"/>
-      <c r="X15" s="35"/>
-      <c r="Y15" s="35"/>
-      <c r="Z15" s="35"/>
-      <c r="AA15" s="35"/>
-      <c r="AB15" s="36"/>
-      <c r="AC15" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD15" s="35"/>
-    </row>
-    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="34">
-        <v>15</v>
-      </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="35"/>
-      <c r="T16" s="35"/>
-      <c r="U16" s="35"/>
-      <c r="V16" s="35"/>
-      <c r="W16" s="35"/>
-      <c r="X16" s="35"/>
-      <c r="Y16" s="35"/>
-      <c r="Z16" s="35"/>
-      <c r="AA16" s="35"/>
-      <c r="AB16" s="36"/>
-      <c r="AC16" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD16" s="35"/>
-    </row>
-    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="34">
-        <v>16</v>
-      </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="35"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="35"/>
-      <c r="U17" s="35"/>
-      <c r="V17" s="35"/>
-      <c r="W17" s="35"/>
-      <c r="X17" s="35"/>
-      <c r="Y17" s="35"/>
-      <c r="Z17" s="35"/>
-      <c r="AA17" s="35"/>
-      <c r="AB17" s="36"/>
-      <c r="AC17" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD17" s="35"/>
-    </row>
-    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="34">
-        <v>17</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="35"/>
-      <c r="T18" s="35"/>
-      <c r="U18" s="35"/>
-      <c r="V18" s="35"/>
-      <c r="W18" s="35"/>
-      <c r="X18" s="35"/>
-      <c r="Y18" s="35"/>
-      <c r="Z18" s="35"/>
-      <c r="AA18" s="35"/>
-      <c r="AB18" s="36"/>
-      <c r="AC18" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD18" s="35"/>
-    </row>
-    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34">
-        <v>18</v>
-      </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
-      <c r="N19" s="35"/>
-      <c r="O19" s="35"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
-      <c r="R19" s="35"/>
-      <c r="S19" s="35"/>
-      <c r="T19" s="35"/>
-      <c r="U19" s="35"/>
-      <c r="V19" s="35"/>
-      <c r="W19" s="35"/>
-      <c r="X19" s="35"/>
-      <c r="Y19" s="35"/>
-      <c r="Z19" s="35"/>
-      <c r="AA19" s="35"/>
-      <c r="AB19" s="36"/>
-      <c r="AC19" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD19" s="35"/>
-    </row>
-    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="34">
-        <v>19</v>
-      </c>
-      <c r="B20" s="35"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="35"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="35"/>
-      <c r="P20" s="35"/>
-      <c r="Q20" s="35"/>
-      <c r="R20" s="35"/>
-      <c r="S20" s="35"/>
-      <c r="T20" s="35"/>
-      <c r="U20" s="35"/>
-      <c r="V20" s="35"/>
-      <c r="W20" s="35"/>
-      <c r="X20" s="35"/>
-      <c r="Y20" s="35"/>
-      <c r="Z20" s="35"/>
-      <c r="AA20" s="35"/>
-      <c r="AB20" s="36"/>
-      <c r="AC20" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD20" s="35"/>
-    </row>
-    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="34">
-        <v>20</v>
-      </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="35"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="35"/>
-      <c r="R21" s="35"/>
-      <c r="S21" s="35"/>
-      <c r="T21" s="35"/>
-      <c r="U21" s="35"/>
-      <c r="V21" s="35"/>
-      <c r="W21" s="35"/>
-      <c r="X21" s="35"/>
-      <c r="Y21" s="35"/>
-      <c r="Z21" s="35"/>
-      <c r="AA21" s="35"/>
-      <c r="AB21" s="36"/>
-      <c r="AC21" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD21" s="35"/>
-    </row>
-    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="34">
-        <v>21</v>
-      </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="35"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="35"/>
-      <c r="T22" s="35"/>
-      <c r="U22" s="35"/>
-      <c r="V22" s="35"/>
-      <c r="W22" s="35"/>
-      <c r="X22" s="35"/>
-      <c r="Y22" s="35"/>
-      <c r="Z22" s="35"/>
-      <c r="AA22" s="35"/>
-      <c r="AB22" s="36"/>
-      <c r="AC22" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD22" s="35"/>
-    </row>
-    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="34">
-        <v>22</v>
-      </c>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
-      <c r="N23" s="35"/>
-      <c r="O23" s="35"/>
-      <c r="P23" s="35"/>
-      <c r="Q23" s="35"/>
-      <c r="R23" s="35"/>
-      <c r="S23" s="35"/>
-      <c r="T23" s="35"/>
-      <c r="U23" s="35"/>
-      <c r="V23" s="35"/>
-      <c r="W23" s="35"/>
-      <c r="X23" s="35"/>
-      <c r="Y23" s="35"/>
-      <c r="Z23" s="35"/>
-      <c r="AA23" s="35"/>
-      <c r="AB23" s="36"/>
-      <c r="AC23" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD23" s="35"/>
-    </row>
-    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="34">
-        <v>23</v>
-      </c>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="35"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35"/>
-      <c r="Q24" s="35"/>
-      <c r="R24" s="35"/>
-      <c r="S24" s="35"/>
-      <c r="T24" s="35"/>
-      <c r="U24" s="35"/>
-      <c r="V24" s="35"/>
-      <c r="W24" s="35"/>
-      <c r="X24" s="35"/>
-      <c r="Y24" s="35"/>
-      <c r="Z24" s="35"/>
-      <c r="AA24" s="35"/>
-      <c r="AB24" s="36"/>
-      <c r="AC24" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD24" s="35"/>
-    </row>
-    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="34">
-        <v>24</v>
-      </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="35"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35"/>
-      <c r="R25" s="35"/>
-      <c r="S25" s="35"/>
-      <c r="T25" s="35"/>
-      <c r="U25" s="35"/>
-      <c r="V25" s="35"/>
-      <c r="W25" s="35"/>
-      <c r="X25" s="35"/>
-      <c r="Y25" s="35"/>
-      <c r="Z25" s="35"/>
-      <c r="AA25" s="35"/>
-      <c r="AB25" s="36"/>
-      <c r="AC25" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD25" s="35"/>
-    </row>
-    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="34">
-        <v>25</v>
-      </c>
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35"/>
-      <c r="Q26" s="35"/>
-      <c r="R26" s="35"/>
-      <c r="S26" s="35"/>
-      <c r="T26" s="35"/>
-      <c r="U26" s="35"/>
-      <c r="V26" s="35"/>
-      <c r="W26" s="35"/>
-      <c r="X26" s="35"/>
-      <c r="Y26" s="35"/>
-      <c r="Z26" s="35"/>
-      <c r="AA26" s="35"/>
-      <c r="AB26" s="36"/>
-      <c r="AC26" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD26" s="35"/>
-    </row>
-    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="34">
-        <v>26</v>
-      </c>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="35"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="35"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
-      <c r="Q27" s="35"/>
-      <c r="R27" s="35"/>
-      <c r="S27" s="35"/>
-      <c r="T27" s="35"/>
-      <c r="U27" s="35"/>
-      <c r="V27" s="35"/>
-      <c r="W27" s="35"/>
-      <c r="X27" s="35"/>
-      <c r="Y27" s="35"/>
-      <c r="Z27" s="35"/>
-      <c r="AA27" s="35"/>
-      <c r="AB27" s="36"/>
-      <c r="AC27" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD27" s="35"/>
-    </row>
-    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="34">
-        <v>27</v>
-      </c>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="35"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="35"/>
-      <c r="R28" s="35"/>
-      <c r="S28" s="35"/>
-      <c r="T28" s="35"/>
-      <c r="U28" s="35"/>
-      <c r="V28" s="35"/>
-      <c r="W28" s="35"/>
-      <c r="X28" s="35"/>
-      <c r="Y28" s="35"/>
-      <c r="Z28" s="35"/>
-      <c r="AA28" s="35"/>
-      <c r="AB28" s="36"/>
-      <c r="AC28" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD28" s="35"/>
-    </row>
-    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="34">
-        <v>28</v>
-      </c>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="35"/>
-      <c r="J29" s="35"/>
-      <c r="K29" s="35"/>
-      <c r="L29" s="35"/>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="35"/>
-      <c r="P29" s="35"/>
-      <c r="Q29" s="35"/>
-      <c r="R29" s="35"/>
-      <c r="S29" s="35"/>
-      <c r="T29" s="35"/>
-      <c r="U29" s="35"/>
-      <c r="V29" s="35"/>
-      <c r="W29" s="35"/>
-      <c r="X29" s="35"/>
-      <c r="Y29" s="35"/>
-      <c r="Z29" s="35"/>
-      <c r="AA29" s="35"/>
-      <c r="AB29" s="36"/>
-      <c r="AC29" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD29" s="35"/>
-    </row>
-    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="34">
-        <v>29</v>
-      </c>
-      <c r="B30" s="35"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="35"/>
-      <c r="J30" s="35"/>
-      <c r="K30" s="35"/>
-      <c r="L30" s="35"/>
-      <c r="M30" s="35"/>
-      <c r="N30" s="35"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="35"/>
-      <c r="Q30" s="35"/>
-      <c r="R30" s="35"/>
-      <c r="S30" s="35"/>
-      <c r="T30" s="35"/>
-      <c r="U30" s="35"/>
-      <c r="V30" s="35"/>
-      <c r="W30" s="35"/>
-      <c r="X30" s="35"/>
-      <c r="Y30" s="35"/>
-      <c r="Z30" s="35"/>
-      <c r="AA30" s="35"/>
-      <c r="AB30" s="36"/>
-      <c r="AC30" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD30" s="35"/>
-    </row>
-    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="34">
-        <v>30</v>
-      </c>
-      <c r="B31" s="35"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="35"/>
-      <c r="K31" s="35"/>
-      <c r="L31" s="35"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="35"/>
-      <c r="U31" s="35"/>
-      <c r="V31" s="35"/>
-      <c r="W31" s="35"/>
-      <c r="X31" s="35"/>
-      <c r="Y31" s="35"/>
-      <c r="Z31" s="35"/>
-      <c r="AA31" s="35"/>
-      <c r="AB31" s="36"/>
-      <c r="AC31" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD31" s="35"/>
-    </row>
-    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B32" s="12" t="str">
-        <f t="shared" ref="B32:AC32" si="1">IF(COUNTA(B2:B31)&gt;0,SUM(B2:B31),"")</f>
-        <v/>
-      </c>
-      <c r="C32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="E32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="N32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="R32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="U32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="V32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Y32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AA32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB32" s="38" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AC32" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AD32" s="39"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="27" width="13" customWidth="1"/>
-    <col min="28" max="28" width="14" customWidth="1"/>
-    <col min="29" max="29" width="25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="T1" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="U1" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="V1" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="W1" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="X1" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y1" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z1" s="33" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA1" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC1" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD1" s="33" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34">
-        <v>1</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="36"/>
-      <c r="AC2" s="35">
-        <f t="shared" ref="AC2:AC32" si="0">SUM(B2:AA2)</f>
-        <v>0</v>
-      </c>
-      <c r="AD2" s="35"/>
-    </row>
-    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="34">
-        <v>2</v>
-      </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
-      <c r="S3" s="35"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="35"/>
-      <c r="V3" s="35"/>
-      <c r="W3" s="35"/>
-      <c r="X3" s="35"/>
-      <c r="Y3" s="35"/>
-      <c r="Z3" s="35"/>
-      <c r="AA3" s="35"/>
-      <c r="AB3" s="36"/>
-      <c r="AC3" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD3" s="35"/>
-    </row>
-    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="34">
-        <v>3</v>
-      </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="35"/>
-      <c r="V4" s="35"/>
-      <c r="W4" s="35"/>
-      <c r="X4" s="35"/>
-      <c r="Y4" s="35"/>
-      <c r="Z4" s="35"/>
-      <c r="AA4" s="35"/>
-      <c r="AB4" s="36"/>
-      <c r="AC4" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD4" s="35"/>
-    </row>
-    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="34">
-        <v>4</v>
-      </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="35"/>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="35"/>
-      <c r="T5" s="35"/>
-      <c r="U5" s="35"/>
-      <c r="V5" s="35"/>
-      <c r="W5" s="35"/>
-      <c r="X5" s="35"/>
-      <c r="Y5" s="35"/>
-      <c r="Z5" s="35"/>
-      <c r="AA5" s="35"/>
-      <c r="AB5" s="36"/>
-      <c r="AC5" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD5" s="35"/>
-    </row>
-    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34">
-        <v>5</v>
-      </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
-      <c r="S6" s="35"/>
-      <c r="T6" s="35"/>
-      <c r="U6" s="35"/>
-      <c r="V6" s="35"/>
-      <c r="W6" s="35"/>
-      <c r="X6" s="35"/>
-      <c r="Y6" s="35"/>
-      <c r="Z6" s="35"/>
-      <c r="AA6" s="35"/>
-      <c r="AB6" s="36"/>
-      <c r="AC6" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD6" s="35"/>
-    </row>
-    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="34">
-        <v>6</v>
-      </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="35"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
-      <c r="N7" s="35"/>
-      <c r="O7" s="35"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-      <c r="R7" s="35"/>
-      <c r="S7" s="35"/>
-      <c r="T7" s="35"/>
-      <c r="U7" s="35"/>
-      <c r="V7" s="35"/>
-      <c r="W7" s="35"/>
-      <c r="X7" s="35"/>
-      <c r="Y7" s="35"/>
-      <c r="Z7" s="35"/>
-      <c r="AA7" s="35"/>
-      <c r="AB7" s="36"/>
-      <c r="AC7" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD7" s="35"/>
-    </row>
-    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34">
-        <v>7</v>
-      </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
-      <c r="N8" s="35"/>
-      <c r="O8" s="35"/>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="35"/>
-      <c r="S8" s="35"/>
-      <c r="T8" s="35"/>
-      <c r="U8" s="35"/>
-      <c r="V8" s="35"/>
-      <c r="W8" s="35"/>
-      <c r="X8" s="35"/>
-      <c r="Y8" s="35"/>
-      <c r="Z8" s="35"/>
-      <c r="AA8" s="35"/>
-      <c r="AB8" s="36"/>
-      <c r="AC8" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD8" s="35"/>
-    </row>
-    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="34">
-        <v>8</v>
-      </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
-      <c r="N9" s="35"/>
-      <c r="O9" s="35"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="35"/>
-      <c r="S9" s="35"/>
-      <c r="T9" s="35"/>
-      <c r="U9" s="35"/>
-      <c r="V9" s="35"/>
-      <c r="W9" s="35"/>
-      <c r="X9" s="35"/>
-      <c r="Y9" s="35"/>
-      <c r="Z9" s="35"/>
-      <c r="AA9" s="35"/>
-      <c r="AB9" s="36"/>
-      <c r="AC9" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD9" s="35"/>
-    </row>
-    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="34">
-        <v>9</v>
-      </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="35"/>
-      <c r="V10" s="35"/>
-      <c r="W10" s="35"/>
-      <c r="X10" s="35"/>
-      <c r="Y10" s="35"/>
-      <c r="Z10" s="35"/>
-      <c r="AA10" s="35"/>
-      <c r="AB10" s="36"/>
-      <c r="AC10" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD10" s="35"/>
-    </row>
-    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="34">
-        <v>10</v>
-      </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="35"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="35"/>
-      <c r="O11" s="35"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="35"/>
-      <c r="T11" s="35"/>
-      <c r="U11" s="35"/>
-      <c r="V11" s="35"/>
-      <c r="W11" s="35"/>
-      <c r="X11" s="35"/>
-      <c r="Y11" s="35"/>
-      <c r="Z11" s="35"/>
-      <c r="AA11" s="35"/>
-      <c r="AB11" s="36"/>
-      <c r="AC11" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD11" s="35"/>
-    </row>
-    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="34">
-        <v>11</v>
-      </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="35"/>
-      <c r="P12" s="35"/>
-      <c r="Q12" s="35"/>
-      <c r="R12" s="35"/>
-      <c r="S12" s="35"/>
-      <c r="T12" s="35"/>
-      <c r="U12" s="35"/>
-      <c r="V12" s="35"/>
-      <c r="W12" s="35"/>
-      <c r="X12" s="35"/>
-      <c r="Y12" s="35"/>
-      <c r="Z12" s="35"/>
-      <c r="AA12" s="35"/>
-      <c r="AB12" s="36"/>
-      <c r="AC12" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD12" s="35"/>
-    </row>
-    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="34">
-        <v>12</v>
-      </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
-      <c r="N13" s="35"/>
-      <c r="O13" s="35"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="35"/>
-      <c r="S13" s="35"/>
-      <c r="T13" s="35"/>
-      <c r="U13" s="35"/>
-      <c r="V13" s="35"/>
-      <c r="W13" s="35"/>
-      <c r="X13" s="35"/>
-      <c r="Y13" s="35"/>
-      <c r="Z13" s="35"/>
-      <c r="AA13" s="35"/>
-      <c r="AB13" s="36"/>
-      <c r="AC13" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD13" s="35"/>
-    </row>
-    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="34">
-        <v>13</v>
-      </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
-      <c r="R14" s="35"/>
-      <c r="S14" s="35"/>
-      <c r="T14" s="35"/>
-      <c r="U14" s="35"/>
-      <c r="V14" s="35"/>
-      <c r="W14" s="35"/>
-      <c r="X14" s="35"/>
-      <c r="Y14" s="35"/>
-      <c r="Z14" s="35"/>
-      <c r="AA14" s="35"/>
-      <c r="AB14" s="36"/>
-      <c r="AC14" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD14" s="35"/>
-    </row>
-    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34">
-        <v>14</v>
-      </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
-      <c r="S15" s="35"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="35"/>
-      <c r="V15" s="35"/>
-      <c r="W15" s="35"/>
-      <c r="X15" s="35"/>
-      <c r="Y15" s="35"/>
-      <c r="Z15" s="35"/>
-      <c r="AA15" s="35"/>
-      <c r="AB15" s="36"/>
-      <c r="AC15" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD15" s="35"/>
-    </row>
-    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="34">
-        <v>15</v>
-      </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="35"/>
-      <c r="T16" s="35"/>
-      <c r="U16" s="35"/>
-      <c r="V16" s="35"/>
-      <c r="W16" s="35"/>
-      <c r="X16" s="35"/>
-      <c r="Y16" s="35"/>
-      <c r="Z16" s="35"/>
-      <c r="AA16" s="35"/>
-      <c r="AB16" s="36"/>
-      <c r="AC16" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD16" s="35"/>
-    </row>
-    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="34">
-        <v>16</v>
-      </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="35"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="35"/>
-      <c r="U17" s="35"/>
-      <c r="V17" s="35"/>
-      <c r="W17" s="35"/>
-      <c r="X17" s="35"/>
-      <c r="Y17" s="35"/>
-      <c r="Z17" s="35"/>
-      <c r="AA17" s="35"/>
-      <c r="AB17" s="36"/>
-      <c r="AC17" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD17" s="35"/>
-    </row>
-    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="34">
-        <v>17</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="35"/>
-      <c r="T18" s="35"/>
-      <c r="U18" s="35"/>
-      <c r="V18" s="35"/>
-      <c r="W18" s="35"/>
-      <c r="X18" s="35"/>
-      <c r="Y18" s="35"/>
-      <c r="Z18" s="35"/>
-      <c r="AA18" s="35"/>
-      <c r="AB18" s="36"/>
-      <c r="AC18" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD18" s="35"/>
-    </row>
-    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34">
-        <v>18</v>
-      </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
-      <c r="N19" s="35"/>
-      <c r="O19" s="35"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
-      <c r="R19" s="35"/>
-      <c r="S19" s="35"/>
-      <c r="T19" s="35"/>
-      <c r="U19" s="35"/>
-      <c r="V19" s="35"/>
-      <c r="W19" s="35"/>
-      <c r="X19" s="35"/>
-      <c r="Y19" s="35"/>
-      <c r="Z19" s="35"/>
-      <c r="AA19" s="35"/>
-      <c r="AB19" s="36"/>
-      <c r="AC19" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD19" s="35"/>
-    </row>
-    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="34">
-        <v>19</v>
-      </c>
-      <c r="B20" s="35"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="35"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="35"/>
-      <c r="P20" s="35"/>
-      <c r="Q20" s="35"/>
-      <c r="R20" s="35"/>
-      <c r="S20" s="35"/>
-      <c r="T20" s="35"/>
-      <c r="U20" s="35"/>
-      <c r="V20" s="35"/>
-      <c r="W20" s="35"/>
-      <c r="X20" s="35"/>
-      <c r="Y20" s="35"/>
-      <c r="Z20" s="35"/>
-      <c r="AA20" s="35"/>
-      <c r="AB20" s="36"/>
-      <c r="AC20" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD20" s="35"/>
-    </row>
-    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="34">
-        <v>20</v>
-      </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="35"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="35"/>
-      <c r="R21" s="35"/>
-      <c r="S21" s="35"/>
-      <c r="T21" s="35"/>
-      <c r="U21" s="35"/>
-      <c r="V21" s="35"/>
-      <c r="W21" s="35"/>
-      <c r="X21" s="35"/>
-      <c r="Y21" s="35"/>
-      <c r="Z21" s="35"/>
-      <c r="AA21" s="35"/>
-      <c r="AB21" s="36"/>
-      <c r="AC21" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD21" s="35"/>
-    </row>
-    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="34">
-        <v>21</v>
-      </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="35"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="35"/>
-      <c r="T22" s="35"/>
-      <c r="U22" s="35"/>
-      <c r="V22" s="35"/>
-      <c r="W22" s="35"/>
-      <c r="X22" s="35"/>
-      <c r="Y22" s="35"/>
-      <c r="Z22" s="35"/>
-      <c r="AA22" s="35"/>
-      <c r="AB22" s="36"/>
-      <c r="AC22" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD22" s="35"/>
-    </row>
-    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="34">
-        <v>22</v>
-      </c>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
-      <c r="N23" s="35"/>
-      <c r="O23" s="35"/>
-      <c r="P23" s="35"/>
-      <c r="Q23" s="35"/>
-      <c r="R23" s="35"/>
-      <c r="S23" s="35"/>
-      <c r="T23" s="35"/>
-      <c r="U23" s="35"/>
-      <c r="V23" s="35"/>
-      <c r="W23" s="35"/>
-      <c r="X23" s="35"/>
-      <c r="Y23" s="35"/>
-      <c r="Z23" s="35"/>
-      <c r="AA23" s="35"/>
-      <c r="AB23" s="36"/>
-      <c r="AC23" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD23" s="35"/>
-    </row>
-    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="34">
-        <v>23</v>
-      </c>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="35"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35"/>
-      <c r="Q24" s="35"/>
-      <c r="R24" s="35"/>
-      <c r="S24" s="35"/>
-      <c r="T24" s="35"/>
-      <c r="U24" s="35"/>
-      <c r="V24" s="35"/>
-      <c r="W24" s="35"/>
-      <c r="X24" s="35"/>
-      <c r="Y24" s="35"/>
-      <c r="Z24" s="35"/>
-      <c r="AA24" s="35"/>
-      <c r="AB24" s="36"/>
-      <c r="AC24" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD24" s="35"/>
-    </row>
-    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="34">
-        <v>24</v>
-      </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="35"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35"/>
-      <c r="R25" s="35"/>
-      <c r="S25" s="35"/>
-      <c r="T25" s="35"/>
-      <c r="U25" s="35"/>
-      <c r="V25" s="35"/>
-      <c r="W25" s="35"/>
-      <c r="X25" s="35"/>
-      <c r="Y25" s="35"/>
-      <c r="Z25" s="35"/>
-      <c r="AA25" s="35"/>
-      <c r="AB25" s="36"/>
-      <c r="AC25" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD25" s="35"/>
-    </row>
-    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="34">
-        <v>25</v>
-      </c>
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35"/>
-      <c r="Q26" s="35"/>
-      <c r="R26" s="35"/>
-      <c r="S26" s="35"/>
-      <c r="T26" s="35"/>
-      <c r="U26" s="35"/>
-      <c r="V26" s="35"/>
-      <c r="W26" s="35"/>
-      <c r="X26" s="35"/>
-      <c r="Y26" s="35"/>
-      <c r="Z26" s="35"/>
-      <c r="AA26" s="35"/>
-      <c r="AB26" s="36"/>
-      <c r="AC26" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD26" s="35"/>
-    </row>
-    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="34">
-        <v>26</v>
-      </c>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="35"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="35"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
-      <c r="Q27" s="35"/>
-      <c r="R27" s="35"/>
-      <c r="S27" s="35"/>
-      <c r="T27" s="35"/>
-      <c r="U27" s="35"/>
-      <c r="V27" s="35"/>
-      <c r="W27" s="35"/>
-      <c r="X27" s="35"/>
-      <c r="Y27" s="35"/>
-      <c r="Z27" s="35"/>
-      <c r="AA27" s="35"/>
-      <c r="AB27" s="36"/>
-      <c r="AC27" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD27" s="35"/>
-    </row>
-    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="34">
-        <v>27</v>
-      </c>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="35"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="35"/>
-      <c r="R28" s="35"/>
-      <c r="S28" s="35"/>
-      <c r="T28" s="35"/>
-      <c r="U28" s="35"/>
-      <c r="V28" s="35"/>
-      <c r="W28" s="35"/>
-      <c r="X28" s="35"/>
-      <c r="Y28" s="35"/>
-      <c r="Z28" s="35"/>
-      <c r="AA28" s="35"/>
-      <c r="AB28" s="36"/>
-      <c r="AC28" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD28" s="35"/>
-    </row>
-    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="34">
-        <v>28</v>
-      </c>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="35"/>
-      <c r="J29" s="35"/>
-      <c r="K29" s="35"/>
-      <c r="L29" s="35"/>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="35"/>
-      <c r="P29" s="35"/>
-      <c r="Q29" s="35"/>
-      <c r="R29" s="35"/>
-      <c r="S29" s="35"/>
-      <c r="T29" s="35"/>
-      <c r="U29" s="35"/>
-      <c r="V29" s="35"/>
-      <c r="W29" s="35"/>
-      <c r="X29" s="35"/>
-      <c r="Y29" s="35"/>
-      <c r="Z29" s="35"/>
-      <c r="AA29" s="35"/>
-      <c r="AB29" s="36"/>
-      <c r="AC29" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD29" s="35"/>
-    </row>
-    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="34">
-        <v>29</v>
-      </c>
-      <c r="B30" s="35"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="35"/>
-      <c r="J30" s="35"/>
-      <c r="K30" s="35"/>
-      <c r="L30" s="35"/>
-      <c r="M30" s="35"/>
-      <c r="N30" s="35"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="35"/>
-      <c r="Q30" s="35"/>
-      <c r="R30" s="35"/>
-      <c r="S30" s="35"/>
-      <c r="T30" s="35"/>
-      <c r="U30" s="35"/>
-      <c r="V30" s="35"/>
-      <c r="W30" s="35"/>
-      <c r="X30" s="35"/>
-      <c r="Y30" s="35"/>
-      <c r="Z30" s="35"/>
-      <c r="AA30" s="35"/>
-      <c r="AB30" s="36"/>
-      <c r="AC30" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD30" s="35"/>
-    </row>
-    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="34">
-        <v>30</v>
-      </c>
-      <c r="B31" s="35"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="35"/>
-      <c r="K31" s="35"/>
-      <c r="L31" s="35"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="35"/>
-      <c r="U31" s="35"/>
-      <c r="V31" s="35"/>
-      <c r="W31" s="35"/>
-      <c r="X31" s="35"/>
-      <c r="Y31" s="35"/>
-      <c r="Z31" s="35"/>
-      <c r="AA31" s="35"/>
-      <c r="AB31" s="36"/>
-      <c r="AC31" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD31" s="35"/>
-    </row>
-    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="34">
-        <v>31</v>
-      </c>
-      <c r="B32" s="35"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="35"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="35"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="35"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="35"/>
-      <c r="P32" s="35"/>
-      <c r="Q32" s="35"/>
-      <c r="R32" s="35"/>
-      <c r="S32" s="35"/>
-      <c r="T32" s="35"/>
-      <c r="U32" s="35"/>
-      <c r="V32" s="35"/>
-      <c r="W32" s="35"/>
-      <c r="X32" s="35"/>
-      <c r="Y32" s="35"/>
-      <c r="Z32" s="35"/>
-      <c r="AA32" s="35"/>
-      <c r="AB32" s="36"/>
-      <c r="AC32" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD32" s="35"/>
-    </row>
-    <row r="33" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B33" s="12" t="str">
-        <f t="shared" ref="B33:AC33" si="1">IF(COUNTA(B2:B32)&gt;0,SUM(B2:B32),"")</f>
-        <v/>
-      </c>
-      <c r="C33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="E33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="N33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="R33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="U33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="V33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Y33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AA33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB33" s="38" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AC33" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AD33" s="39"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
 </file>
--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="93">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -319,6 +319,9 @@
   </si>
   <si>
     <t>Arreglo porton y luz</t>
+  </si>
+  <si>
+    <t>llave</t>
   </si>
 </sst>
 </file>
@@ -1664,7 +1667,7 @@
         <v>27500</v>
       </c>
       <c r="G8" s="1">
-        <v>2200</v>
+        <v>1100</v>
       </c>
       <c r="H8" s="1">
         <v>3300</v>
@@ -1720,7 +1723,7 @@
       <c r="AB8" s="6"/>
       <c r="AC8" s="1">
         <f>SUM(B8:AB8)</f>
-        <v>191436.14</v>
+        <v>190336.14</v>
       </c>
       <c r="AD8" s="7">
         <f t="shared" si="1"/>
@@ -1738,15 +1741,15 @@
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="3"/>
-        <v>77718.070000000007</v>
+        <v>77168.070000000007</v>
       </c>
       <c r="AI8" s="9">
         <f t="shared" si="4"/>
-        <v>79968.070000000007</v>
+        <v>79418.070000000007</v>
       </c>
       <c r="AJ8" s="10">
         <f t="shared" si="5"/>
-        <v>157686.14000000001</v>
+        <v>156586.14000000001</v>
       </c>
     </row>
     <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2634,9 +2637,9 @@
         <f>IF(Octubre!F33&gt;0,Octubre!F33,"")</f>
         <v>18447</v>
       </c>
-      <c r="G19" s="1" t="str">
+      <c r="G19" s="1">
         <f>IF(Octubre!G33&gt;0,Octubre!G33,"")</f>
-        <v/>
+        <v>998.36</v>
       </c>
       <c r="H19" s="1">
         <f>IF(Octubre!H33&gt;0,Octubre!H33,"")</f>
@@ -2680,7 +2683,7 @@
       </c>
       <c r="R19" s="1">
         <f>IF(Octubre!R33&gt;0,Octubre!R33,"")</f>
-        <v>7019.1100000000006</v>
+        <v>7748.6</v>
       </c>
       <c r="S19" s="1" t="str">
         <f>IF(Octubre!S33&gt;0,Octubre!S33,"")</f>
@@ -2716,7 +2719,7 @@
       </c>
       <c r="AA19" s="1">
         <f>IF(Octubre!AA33&gt;0,Octubre!AA33,"")</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="20" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3644,9 +3647,9 @@
         <f>IF(ISNUMBER(Octubre!F33),F8-Octubre!F33,"")</f>
         <v>9053</v>
       </c>
-      <c r="G30" s="1" t="str">
+      <c r="G30" s="1">
         <f>IF(ISNUMBER(Octubre!G33),G8-Octubre!G33,"")</f>
-        <v/>
+        <v>101.63999999999999</v>
       </c>
       <c r="H30" s="1">
         <f>IF(ISNUMBER(Octubre!H33),H8-Octubre!H33,"")</f>
@@ -3690,7 +3693,7 @@
       </c>
       <c r="R30" s="1">
         <f>IF(ISNUMBER(Octubre!R33),R8-Octubre!R33,"")</f>
-        <v>12980.89</v>
+        <v>12251.4</v>
       </c>
       <c r="S30" s="1" t="str">
         <f>IF(ISNUMBER(Octubre!S33),S8-Octubre!S33,"")</f>
@@ -3726,11 +3729,11 @@
       </c>
       <c r="AA30" s="1">
         <f>IF(ISNUMBER(Octubre!AA33),AA8-Octubre!AA33,"")</f>
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="AC30" s="12">
         <f t="shared" si="7"/>
-        <v>31652.38</v>
+        <v>30524.53</v>
       </c>
     </row>
     <row r="31" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3985,7 +3988,7 @@
       </c>
       <c r="G33" s="12">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>106.63999999999999</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="8"/>
@@ -4029,7 +4032,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>10400.850000000002</v>
+        <v>9671.3600000000024</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4065,11 +4068,11 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>-12813.599999999999</v>
+        <v>-13313.599999999999</v>
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>23457.869999999995</v>
+        <v>22330.019999999997</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12297,7 +12300,10 @@
       <c r="D10" s="35"/>
       <c r="E10" s="35"/>
       <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
+      <c r="G10" s="35">
+        <f>1015-16.64</f>
+        <v>998.36</v>
+      </c>
       <c r="H10" s="35"/>
       <c r="I10" s="35"/>
       <c r="J10" s="35"/>
@@ -12311,7 +12317,10 @@
       <c r="O10" s="35"/>
       <c r="P10" s="35"/>
       <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
+      <c r="R10" s="35">
+        <f>743-13.51</f>
+        <v>729.49</v>
+      </c>
       <c r="S10" s="35"/>
       <c r="T10" s="35"/>
       <c r="U10" s="35"/>
@@ -12320,13 +12329,17 @@
       <c r="X10" s="35"/>
       <c r="Y10" s="35"/>
       <c r="Z10" s="35"/>
-      <c r="AA10" s="35"/>
+      <c r="AA10" s="35">
+        <v>500</v>
+      </c>
       <c r="AB10" s="36"/>
       <c r="AC10" s="35">
         <f t="shared" si="0"/>
-        <v>17990.03</v>
-      </c>
-      <c r="AD10" s="35"/>
+        <v>20217.88</v>
+      </c>
+      <c r="AD10" s="35" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34">
@@ -13166,9 +13179,9 @@
         <f t="shared" si="1"/>
         <v>18447</v>
       </c>
-      <c r="G33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="G33" s="12">
+        <f t="shared" si="1"/>
+        <v>998.36</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="1"/>
@@ -13212,7 +13225,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="1"/>
-        <v>7019.1100000000006</v>
+        <v>7748.6</v>
       </c>
       <c r="S33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -13248,7 +13261,7 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="1"/>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="AB33" s="38" t="str">
         <f t="shared" si="1"/>
@@ -13256,7 +13269,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>109933.75999999999</v>
+        <v>112161.61</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" firstSheet="1" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Noviembre" sheetId="8" r:id="rId8"/>
     <sheet name="Diciembre" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="94">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -322,6 +322,9 @@
   </si>
   <si>
     <t>llave</t>
+  </si>
+  <si>
+    <t>libros roci y auriculares</t>
   </si>
 </sst>
 </file>
@@ -2625,9 +2628,9 @@
         <f>IF(Octubre!C33&gt;0,Octubre!C33,"")</f>
         <v/>
       </c>
-      <c r="D19" s="1" t="str">
+      <c r="D19" s="1">
         <f>IF(Octubre!D33&gt;0,Octubre!D33,"")</f>
-        <v/>
+        <v>15751.26</v>
       </c>
       <c r="E19" s="1" t="str">
         <f>IF(Octubre!E33&gt;0,Octubre!E33,"")</f>
@@ -2635,7 +2638,7 @@
       </c>
       <c r="F19" s="1">
         <f>IF(Octubre!F33&gt;0,Octubre!F33,"")</f>
-        <v>18447</v>
+        <v>25901</v>
       </c>
       <c r="G19" s="1">
         <f>IF(Octubre!G33&gt;0,Octubre!G33,"")</f>
@@ -2673,9 +2676,9 @@
         <f>IF(Octubre!O33&gt;0,Octubre!O33,"")</f>
         <v>491.81</v>
       </c>
-      <c r="P19" s="1" t="str">
+      <c r="P19" s="1">
         <f>IF(Octubre!P33&gt;0,Octubre!P33,"")</f>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="Q19" s="1" t="str">
         <f>IF(Octubre!Q33&gt;0,Octubre!Q33,"")</f>
@@ -2683,11 +2686,11 @@
       </c>
       <c r="R19" s="1">
         <f>IF(Octubre!R33&gt;0,Octubre!R33,"")</f>
-        <v>7748.6</v>
-      </c>
-      <c r="S19" s="1" t="str">
+        <v>9613.19</v>
+      </c>
+      <c r="S19" s="1">
         <f>IF(Octubre!S33&gt;0,Octubre!S33,"")</f>
-        <v/>
+        <v>560.72</v>
       </c>
       <c r="T19" s="1">
         <f>IF(Octubre!T33&gt;0,Octubre!T33,"")</f>
@@ -2701,9 +2704,9 @@
         <f>IF(Octubre!V33&gt;0,Octubre!V33,"")</f>
         <v/>
       </c>
-      <c r="W19" s="1" t="str">
+      <c r="W19" s="1">
         <f>IF(Octubre!W33&gt;0,Octubre!W33,"")</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="X19" s="1" t="str">
         <f>IF(Octubre!X33&gt;0,Octubre!X33,"")</f>
@@ -2719,7 +2722,7 @@
       </c>
       <c r="AA19" s="1">
         <f>IF(Octubre!AA33&gt;0,Octubre!AA33,"")</f>
-        <v>3000</v>
+        <v>5072.79</v>
       </c>
     </row>
     <row r="20" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3631,21 +3634,21 @@
         <f>IF(ISNUMBER(Setiembre!B33),B9-Setiembre!B33,"")</f>
         <v/>
       </c>
-      <c r="C30" s="1" t="str">
+      <c r="C30" s="1">
         <f>IF(ISNUMBER(Octubre!C33),C8-Octubre!C33,"")</f>
-        <v/>
-      </c>
-      <c r="D30" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="D30" s="1">
         <f>IF(ISNUMBER(Octubre!D33),D8-Octubre!D33,"")</f>
-        <v/>
-      </c>
-      <c r="E30" s="1" t="str">
+        <v>-1.2600000000002183</v>
+      </c>
+      <c r="E30" s="1">
         <f>IF(ISNUMBER(Octubre!E33),E8-Octubre!E33,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F30" s="1">
         <f>IF(ISNUMBER(Octubre!F33),F8-Octubre!F33,"")</f>
-        <v>9053</v>
+        <v>1599</v>
       </c>
       <c r="G30" s="1">
         <f>IF(ISNUMBER(Octubre!G33),G8-Octubre!G33,"")</f>
@@ -3683,9 +3686,9 @@
         <f>IF(ISNUMBER(Octubre!O33),O8-Octubre!O33,"")</f>
         <v>3908.19</v>
       </c>
-      <c r="P30" s="1" t="str">
+      <c r="P30" s="1">
         <f>IF(ISNUMBER(Octubre!P33),P8-Octubre!P33,"")</f>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="Q30" s="1" t="str">
         <f>IF(ISNUMBER(Octubre!Q33),Q8-Octubre!Q33,"")</f>
@@ -3693,27 +3696,27 @@
       </c>
       <c r="R30" s="1">
         <f>IF(ISNUMBER(Octubre!R33),R8-Octubre!R33,"")</f>
-        <v>12251.4</v>
-      </c>
-      <c r="S30" s="1" t="str">
+        <v>10386.81</v>
+      </c>
+      <c r="S30" s="1">
         <f>IF(ISNUMBER(Octubre!S33),S8-Octubre!S33,"")</f>
-        <v/>
+        <v>1439.28</v>
       </c>
       <c r="T30" s="1">
         <f>IF(ISNUMBER(Octubre!T33),T8-Octubre!T33,"")</f>
         <v>3465.5699999999997</v>
       </c>
-      <c r="U30" s="1" t="str">
+      <c r="U30" s="1">
         <f>IF(ISNUMBER(Octubre!U33),U8-Octubre!U33,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V30" s="1" t="str">
         <f>IF(ISNUMBER(Octubre!V33),V8-Octubre!V33,"")</f>
         <v/>
       </c>
-      <c r="W30" s="1" t="str">
+      <c r="W30" s="1">
         <f>IF(ISNUMBER(Octubre!W33),W8-Octubre!W33,"")</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="X30" s="1" t="str">
         <f>IF(ISNUMBER(Octubre!X33),X8-Octubre!X33,"")</f>
@@ -3729,11 +3732,11 @@
       </c>
       <c r="AA30" s="1">
         <f>IF(ISNUMBER(Octubre!AA33),AA8-Octubre!AA33,"")</f>
-        <v>2000</v>
+        <v>-72.789999999999964</v>
       </c>
       <c r="AC30" s="12">
         <f t="shared" si="7"/>
-        <v>30524.53</v>
+        <v>24871.17</v>
       </c>
     </row>
     <row r="31" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3976,7 +3979,7 @@
       </c>
       <c r="D33" s="12">
         <f t="shared" si="8"/>
-        <v>56.709999999999127</v>
+        <v>55.449999999998909</v>
       </c>
       <c r="E33" s="12">
         <f t="shared" si="8"/>
@@ -3984,7 +3987,7 @@
       </c>
       <c r="F33" s="12">
         <f t="shared" si="8"/>
-        <v>7875</v>
+        <v>421</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="8"/>
@@ -4024,7 +4027,7 @@
       </c>
       <c r="P33" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="8"/>
@@ -4032,11 +4035,11 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>9671.3600000000024</v>
+        <v>7806.7700000000023</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
-        <v>2761.5400000000004</v>
+        <v>4200.8200000000006</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="8"/>
@@ -4052,7 +4055,7 @@
       </c>
       <c r="W33" s="12">
         <f t="shared" si="8"/>
-        <v>1483.6</v>
+        <v>3983.6</v>
       </c>
       <c r="X33" s="12">
         <f t="shared" si="8"/>
@@ -4068,11 +4071,11 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>-13313.599999999999</v>
+        <v>-15386.39</v>
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>22330.019999999997</v>
+        <v>16676.659999999996</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11955,9 +11958,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
+      <c r="C2" s="35">
+        <v>0</v>
+      </c>
       <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
+      <c r="E2" s="35">
+        <v>0</v>
+      </c>
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
@@ -11976,7 +11983,9 @@
       </c>
       <c r="S2" s="35"/>
       <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
+      <c r="U2" s="35">
+        <v>0</v>
+      </c>
       <c r="V2" s="35"/>
       <c r="W2" s="35"/>
       <c r="X2" s="35"/>
@@ -12270,7 +12279,10 @@
       <c r="O9" s="35"/>
       <c r="P9" s="35"/>
       <c r="Q9" s="35"/>
-      <c r="R9" s="35"/>
+      <c r="R9" s="35">
+        <f>342-3.37</f>
+        <v>338.63</v>
+      </c>
       <c r="S9" s="35"/>
       <c r="T9" s="35"/>
       <c r="U9" s="35"/>
@@ -12285,7 +12297,7 @@
       <c r="AB9" s="36"/>
       <c r="AC9" s="35">
         <f t="shared" si="0"/>
-        <v>29638.14</v>
+        <v>29976.77</v>
       </c>
       <c r="AD9" s="35" t="s">
         <v>91</v>
@@ -12361,8 +12373,14 @@
       <c r="O11" s="35"/>
       <c r="P11" s="35"/>
       <c r="Q11" s="35"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="35"/>
+      <c r="R11" s="35">
+        <f>1240-91.48</f>
+        <v>1148.52</v>
+      </c>
+      <c r="S11" s="35">
+        <f>108+461-1.97-6.31</f>
+        <v>560.72</v>
+      </c>
       <c r="T11" s="35"/>
       <c r="U11" s="35"/>
       <c r="V11" s="35"/>
@@ -12370,13 +12388,18 @@
       <c r="X11" s="35"/>
       <c r="Y11" s="35"/>
       <c r="Z11" s="35"/>
-      <c r="AA11" s="35"/>
+      <c r="AA11" s="35">
+        <f>1640+440-7.21</f>
+        <v>2072.79</v>
+      </c>
       <c r="AB11" s="36"/>
       <c r="AC11" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD11" s="35"/>
+        <v>3782.0299999999997</v>
+      </c>
+      <c r="AD11" s="35" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="34">
@@ -12398,12 +12421,17 @@
       <c r="O12" s="35"/>
       <c r="P12" s="35"/>
       <c r="Q12" s="35"/>
-      <c r="R12" s="35"/>
+      <c r="R12" s="35">
+        <f>385-7.56</f>
+        <v>377.44</v>
+      </c>
       <c r="S12" s="35"/>
       <c r="T12" s="35"/>
       <c r="U12" s="35"/>
       <c r="V12" s="35"/>
-      <c r="W12" s="35"/>
+      <c r="W12" s="35">
+        <v>500</v>
+      </c>
       <c r="X12" s="35"/>
       <c r="Y12" s="35"/>
       <c r="Z12" s="35"/>
@@ -12411,7 +12439,7 @@
       <c r="AB12" s="36"/>
       <c r="AC12" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>877.44</v>
       </c>
       <c r="AD12" s="35"/>
     </row>
@@ -12495,9 +12523,13 @@
       </c>
       <c r="B15" s="35"/>
       <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
+      <c r="D15" s="35">
+        <v>15751.26</v>
+      </c>
       <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
+      <c r="F15" s="35">
+        <v>7454</v>
+      </c>
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
       <c r="I15" s="35"/>
@@ -12507,7 +12539,9 @@
       <c r="M15" s="35"/>
       <c r="N15" s="35"/>
       <c r="O15" s="35"/>
-      <c r="P15" s="35"/>
+      <c r="P15" s="35">
+        <v>1800</v>
+      </c>
       <c r="Q15" s="35"/>
       <c r="R15" s="35"/>
       <c r="S15" s="35"/>
@@ -12522,7 +12556,7 @@
       <c r="AB15" s="36"/>
       <c r="AC15" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25005.260000000002</v>
       </c>
       <c r="AD15" s="35"/>
     </row>
@@ -13163,21 +13197,21 @@
         <f>IF(COUNTA(B2:B32)&gt;0,SUM(B2:B32),"")</f>
         <v>27138.14</v>
       </c>
-      <c r="C33" s="12" t="str">
-        <f t="shared" ref="B33:AC33" si="1">IF(COUNTA(C2:C32)&gt;0,SUM(C2:C32),"")</f>
-        <v/>
-      </c>
-      <c r="D33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="E33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="C33" s="12">
+        <f t="shared" ref="C33:AC33" si="1">IF(COUNTA(C2:C32)&gt;0,SUM(C2:C32),"")</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="12">
+        <f t="shared" si="1"/>
+        <v>15751.26</v>
+      </c>
+      <c r="E33" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" si="1"/>
-        <v>18447</v>
+        <v>25901</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="1"/>
@@ -13215,9 +13249,9 @@
         <f t="shared" si="1"/>
         <v>491.81</v>
       </c>
-      <c r="P33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="P33" s="12">
+        <f t="shared" si="1"/>
+        <v>1800</v>
       </c>
       <c r="Q33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -13225,27 +13259,27 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="1"/>
-        <v>7748.6</v>
-      </c>
-      <c r="S33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <v>9613.19</v>
+      </c>
+      <c r="S33" s="12">
+        <f t="shared" si="1"/>
+        <v>560.72</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="1"/>
         <v>1534.43</v>
       </c>
-      <c r="U33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="U33" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="V33" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="W33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="W33" s="12">
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="X33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -13261,7 +13295,7 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="1"/>
-        <v>3000</v>
+        <v>5072.79</v>
       </c>
       <c r="AB33" s="38" t="str">
         <f t="shared" si="1"/>
@@ -13269,7 +13303,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>112161.61</v>
+        <v>142164.97</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -1688,7 +1688,7 @@
         <v>18000</v>
       </c>
       <c r="M8" s="1">
-        <v>18000</v>
+        <v>16700</v>
       </c>
       <c r="N8" s="1">
         <v>810</v>
@@ -1726,7 +1726,7 @@
       <c r="AB8" s="6"/>
       <c r="AC8" s="1">
         <f>SUM(B8:AB8)</f>
-        <v>190336.14</v>
+        <v>189036.14</v>
       </c>
       <c r="AD8" s="7">
         <f t="shared" si="1"/>
@@ -1744,11 +1744,11 @@
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="3"/>
-        <v>77168.070000000007</v>
+        <v>77818.070000000007</v>
       </c>
       <c r="AI8" s="9">
         <f t="shared" si="4"/>
-        <v>79418.070000000007</v>
+        <v>78768.070000000007</v>
       </c>
       <c r="AJ8" s="10">
         <f t="shared" si="5"/>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="R19" s="1">
         <f>IF(Octubre!R33&gt;0,Octubre!R33,"")</f>
-        <v>9613.19</v>
+        <v>10926.310000000001</v>
       </c>
       <c r="S19" s="1">
         <f>IF(Octubre!S33&gt;0,Octubre!S33,"")</f>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="R30" s="1">
         <f>IF(ISNUMBER(Octubre!R33),R8-Octubre!R33,"")</f>
-        <v>10386.81</v>
+        <v>9073.6899999999987</v>
       </c>
       <c r="S30" s="1">
         <f>IF(ISNUMBER(Octubre!S33),S8-Octubre!S33,"")</f>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="AC30" s="12">
         <f t="shared" si="7"/>
-        <v>24871.17</v>
+        <v>23558.05</v>
       </c>
     </row>
     <row r="31" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>7806.7700000000023</v>
+        <v>6493.6500000000015</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>16676.659999999996</v>
+        <v>15363.539999999997</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12543,7 +12543,10 @@
         <v>1800</v>
       </c>
       <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
+      <c r="R15" s="35">
+        <f>280+673+382-11.03-6.26-4.59</f>
+        <v>1313.1200000000001</v>
+      </c>
       <c r="S15" s="35"/>
       <c r="T15" s="35"/>
       <c r="U15" s="35"/>
@@ -12556,7 +12559,7 @@
       <c r="AB15" s="36"/>
       <c r="AC15" s="35">
         <f t="shared" si="0"/>
-        <v>25005.260000000002</v>
+        <v>26318.38</v>
       </c>
       <c r="AD15" s="35"/>
     </row>
@@ -13259,7 +13262,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="1"/>
-        <v>9613.19</v>
+        <v>10926.310000000001</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="1"/>
@@ -13303,7 +13306,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>142164.97</v>
+        <v>143478.09</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/289bf34ef3ebdbf8/Desktop/Nico/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_3528FC9679616F11138CF261575EFE9D5C3E667E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62BA9EAD-42C5-4C6C-A885-C6B806D146A5}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="6"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -22,7 +23,7 @@
     <sheet name="Noviembre" sheetId="8" r:id="rId8"/>
     <sheet name="Diciembre" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -330,7 +331,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
@@ -789,6 +790,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -964,37 +969,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AJ54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="8" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="1"/>
     <col min="7" max="7" width="12" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="1"/>
+    <col min="8" max="8" width="9.109375" style="1"/>
     <col min="9" max="11" width="14" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5703125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.140625" style="1" customWidth="1"/>
-    <col min="17" max="20" width="9.140625" style="1"/>
-    <col min="21" max="21" width="17.85546875" style="1" customWidth="1"/>
-    <col min="22" max="22" width="10.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.44140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="10.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.109375" style="1" customWidth="1"/>
+    <col min="17" max="20" width="9.109375" style="1"/>
+    <col min="21" max="21" width="17.88671875" style="1" customWidth="1"/>
+    <col min="22" max="22" width="10.5546875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.6640625" style="1" customWidth="1"/>
     <col min="24" max="24" width="15" style="1" customWidth="1"/>
-    <col min="25" max="25" width="9.140625" style="1"/>
-    <col min="26" max="26" width="15.85546875" style="1" customWidth="1"/>
-    <col min="27" max="27" width="9.140625" style="1"/>
+    <col min="25" max="25" width="9.109375" style="1"/>
+    <col min="26" max="26" width="15.88671875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="9.109375" style="1"/>
     <col min="28" max="28" width="13" style="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="29" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
@@ -1026,7 +1031,7 @@
       <c r="AA1" s="44"/>
       <c r="AB1" s="44"/>
     </row>
-    <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1136,7 +1141,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>37</v>
       </c>
@@ -1241,7 +1246,7 @@
         <v>132950</v>
       </c>
     </row>
-    <row r="4" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
@@ -1346,7 +1351,7 @@
         <v>142900</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>39</v>
       </c>
@@ -1452,7 +1457,7 @@
         <v>114219</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>40</v>
       </c>
@@ -1548,7 +1553,7 @@
         <v>117732.97</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>41</v>
       </c>
@@ -1653,7 +1658,7 @@
         <v>135649</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>42</v>
       </c>
@@ -1755,7 +1760,7 @@
         <v>156586.14000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>43</v>
       </c>
@@ -1857,7 +1862,7 @@
         <v>117079</v>
       </c>
     </row>
-    <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>44</v>
       </c>
@@ -1956,7 +1961,7 @@
         <v>130210</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="45" t="s">
         <v>45</v>
       </c>
@@ -1988,7 +1993,7 @@
       <c r="AA12" s="45"/>
       <c r="AB12" s="45"/>
     </row>
-    <row r="13" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>1</v>
       </c>
@@ -2071,7 +2076,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
@@ -2180,7 +2185,7 @@
         <v>4705.57</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>38</v>
       </c>
@@ -2289,7 +2294,7 @@
         <v>21845.239999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
@@ -2398,7 +2403,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>40</v>
       </c>
@@ -2507,7 +2512,7 @@
         <v>6388.06</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
@@ -2616,7 +2621,7 @@
         <v>2374.73</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -2674,7 +2679,7 @@
       </c>
       <c r="O19" s="1">
         <f>IF(Octubre!O33&gt;0,Octubre!O33,"")</f>
-        <v>491.81</v>
+        <v>983.62</v>
       </c>
       <c r="P19" s="1">
         <f>IF(Octubre!P33&gt;0,Octubre!P33,"")</f>
@@ -2686,15 +2691,15 @@
       </c>
       <c r="R19" s="1">
         <f>IF(Octubre!R33&gt;0,Octubre!R33,"")</f>
-        <v>10926.310000000001</v>
+        <v>21412.340000000004</v>
       </c>
       <c r="S19" s="1">
         <f>IF(Octubre!S33&gt;0,Octubre!S33,"")</f>
-        <v>560.72</v>
+        <v>1082.03</v>
       </c>
       <c r="T19" s="1">
         <f>IF(Octubre!T33&gt;0,Octubre!T33,"")</f>
-        <v>1534.43</v>
+        <v>3358.04</v>
       </c>
       <c r="U19" s="1" t="str">
         <f>IF(Octubre!U33&gt;0,Octubre!U33,"")</f>
@@ -2708,9 +2713,9 @@
         <f>IF(Octubre!W33&gt;0,Octubre!W33,"")</f>
         <v>500</v>
       </c>
-      <c r="X19" s="1" t="str">
+      <c r="X19" s="1">
         <f>IF(Octubre!X33&gt;0,Octubre!X33,"")</f>
-        <v/>
+        <v>232.5</v>
       </c>
       <c r="Y19" s="1" t="str">
         <f>IF(Octubre!Y33&gt;0,Octubre!Y33,"")</f>
@@ -2725,7 +2730,7 @@
         <v>5072.79</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>43</v>
       </c>
@@ -2834,7 +2839,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>44</v>
       </c>
@@ -2943,7 +2948,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="46" t="s">
         <v>48</v>
       </c>
@@ -2975,7 +2980,7 @@
       <c r="AA23" s="46"/>
       <c r="AB23" s="46"/>
     </row>
-    <row r="24" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>1</v>
       </c>
@@ -3061,7 +3066,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>37</v>
       </c>
@@ -3174,7 +3179,7 @@
         <v>12166.969999999994</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
@@ -3287,7 +3292,7 @@
         <v>-22136.239999999994</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>39</v>
       </c>
@@ -3400,7 +3405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>40</v>
       </c>
@@ -3513,7 +3518,7 @@
         <v>-1515.670000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>41</v>
       </c>
@@ -3626,7 +3631,7 @@
         <v>3290.4300000000026</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>42</v>
       </c>
@@ -3684,7 +3689,7 @@
       </c>
       <c r="O30" s="1">
         <f>IF(ISNUMBER(Octubre!O33),O8-Octubre!O33,"")</f>
-        <v>3908.19</v>
+        <v>3416.38</v>
       </c>
       <c r="P30" s="1">
         <f>IF(ISNUMBER(Octubre!P33),P8-Octubre!P33,"")</f>
@@ -3696,15 +3701,15 @@
       </c>
       <c r="R30" s="1">
         <f>IF(ISNUMBER(Octubre!R33),R8-Octubre!R33,"")</f>
-        <v>9073.6899999999987</v>
+        <v>-1412.3400000000038</v>
       </c>
       <c r="S30" s="1">
         <f>IF(ISNUMBER(Octubre!S33),S8-Octubre!S33,"")</f>
-        <v>1439.28</v>
+        <v>917.97</v>
       </c>
       <c r="T30" s="1">
         <f>IF(ISNUMBER(Octubre!T33),T8-Octubre!T33,"")</f>
-        <v>3465.5699999999997</v>
+        <v>1641.96</v>
       </c>
       <c r="U30" s="1">
         <f>IF(ISNUMBER(Octubre!U33),U8-Octubre!U33,"")</f>
@@ -3718,9 +3723,9 @@
         <f>IF(ISNUMBER(Octubre!W33),W8-Octubre!W33,"")</f>
         <v>2500</v>
       </c>
-      <c r="X30" s="1" t="str">
+      <c r="X30" s="1">
         <f>IF(ISNUMBER(Octubre!X33),X8-Octubre!X33,"")</f>
-        <v/>
+        <v>567.5</v>
       </c>
       <c r="Y30" s="1" t="str">
         <f>IF(ISNUMBER(Octubre!Y33),Y8-Octubre!Y33,"")</f>
@@ -3736,10 +3741,10 @@
       </c>
       <c r="AC30" s="12">
         <f t="shared" si="7"/>
-        <v>23558.05</v>
-      </c>
-    </row>
-    <row r="31" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10802.789999999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>43</v>
       </c>
@@ -3852,7 +3857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>44</v>
       </c>
@@ -3965,7 +3970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
         <v>50</v>
       </c>
@@ -4023,7 +4028,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="8"/>
-        <v>14617.86</v>
+        <v>14126.05</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="8"/>
@@ -4035,15 +4040,15 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>6493.6500000000015</v>
+        <v>-3992.380000000001</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
-        <v>4200.8200000000006</v>
+        <v>3679.51</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="8"/>
-        <v>7503.5400000000009</v>
+        <v>5679.93</v>
       </c>
       <c r="U33" s="12">
         <f t="shared" si="8"/>
@@ -4059,7 +4064,7 @@
       </c>
       <c r="X33" s="12">
         <f t="shared" si="8"/>
-        <v>3764.7</v>
+        <v>4332.2</v>
       </c>
       <c r="Y33" s="12">
         <f t="shared" si="8"/>
@@ -4075,15 +4080,15 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>15363.539999999997</v>
-      </c>
-    </row>
-    <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2608.2799999999952</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="15"/>
       <c r="B37" s="15" t="s">
         <v>52</v>
@@ -4123,7 +4128,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="16" t="s">
         <v>51</v>
       </c>
@@ -4152,7 +4157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="21" t="s">
         <v>56</v>
       </c>
@@ -4161,12 +4166,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="23" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="24" t="s">
         <v>58</v>
       </c>
@@ -4177,57 +4182,57 @@
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="25"/>
       <c r="B43" s="26"/>
       <c r="C43" s="27"/>
     </row>
-    <row r="44" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="25"/>
       <c r="B44" s="26"/>
       <c r="C44" s="27"/>
     </row>
-    <row r="45" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="25"/>
       <c r="B45" s="26"/>
       <c r="C45" s="27"/>
     </row>
-    <row r="46" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="25"/>
       <c r="B46" s="26"/>
       <c r="C46" s="27"/>
     </row>
-    <row r="47" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="25"/>
       <c r="B47" s="26"/>
       <c r="C47" s="27"/>
     </row>
-    <row r="48" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="25"/>
       <c r="B48" s="26"/>
       <c r="C48" s="27"/>
     </row>
-    <row r="49" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="25"/>
       <c r="B49" s="26"/>
       <c r="C49" s="27"/>
     </row>
-    <row r="50" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="25"/>
       <c r="B50" s="26"/>
       <c r="C50" s="27"/>
     </row>
-    <row r="51" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="25"/>
       <c r="B51" s="26"/>
       <c r="C51" s="27"/>
     </row>
-    <row r="52" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="25"/>
       <c r="B52" s="26"/>
       <c r="C52" s="27"/>
     </row>
-    <row r="53" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="28" t="s">
         <v>61</v>
       </c>
@@ -4237,7 +4242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="16" t="s">
         <v>62</v>
       </c>
@@ -4271,34 +4276,34 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AD33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" customWidth="1"/>
     <col min="5" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="12.28515625" customWidth="1"/>
-    <col min="10" max="11" width="15.85546875" customWidth="1"/>
-    <col min="12" max="12" width="19.42578125" customWidth="1"/>
-    <col min="13" max="13" width="22.42578125" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" customWidth="1"/>
+    <col min="10" max="11" width="15.88671875" customWidth="1"/>
+    <col min="12" max="12" width="19.44140625" customWidth="1"/>
+    <col min="13" max="13" width="22.44140625" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="22.28515625" customWidth="1"/>
+    <col min="15" max="15" width="22.33203125" customWidth="1"/>
     <col min="16" max="17" width="13" customWidth="1"/>
-    <col min="18" max="19" width="10.28515625" customWidth="1"/>
-    <col min="20" max="20" width="7.140625" customWidth="1"/>
-    <col min="21" max="21" width="20.140625" customWidth="1"/>
+    <col min="18" max="19" width="10.33203125" customWidth="1"/>
+    <col min="20" max="20" width="7.109375" customWidth="1"/>
+    <col min="21" max="21" width="20.109375" customWidth="1"/>
     <col min="22" max="23" width="13" customWidth="1"/>
-    <col min="24" max="24" width="17.42578125" customWidth="1"/>
-    <col min="25" max="25" width="9.140625" customWidth="1"/>
-    <col min="26" max="26" width="12.42578125" customWidth="1"/>
-    <col min="27" max="27" width="6.5703125" customWidth="1"/>
-    <col min="28" max="28" width="13.28515625" customWidth="1"/>
+    <col min="24" max="24" width="17.44140625" customWidth="1"/>
+    <col min="25" max="25" width="9.109375" customWidth="1"/>
+    <col min="26" max="26" width="12.44140625" customWidth="1"/>
+    <col min="27" max="27" width="6.5546875" customWidth="1"/>
+    <col min="28" max="28" width="13.33203125" customWidth="1"/>
     <col min="29" max="29" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
         <v>1</v>
       </c>
@@ -4390,7 +4395,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34">
         <v>1</v>
       </c>
@@ -4427,7 +4432,7 @@
       </c>
       <c r="AD2" s="35"/>
     </row>
-    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34">
         <v>2</v>
       </c>
@@ -4464,7 +4469,7 @@
       </c>
       <c r="AD3" s="35"/>
     </row>
-    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="34">
         <v>3</v>
       </c>
@@ -4503,7 +4508,7 @@
       </c>
       <c r="AD4" s="35"/>
     </row>
-    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>4</v>
       </c>
@@ -4544,7 +4549,7 @@
       </c>
       <c r="AD5" s="35"/>
     </row>
-    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="34">
         <v>5</v>
       </c>
@@ -4585,7 +4590,7 @@
       </c>
       <c r="AD6" s="35"/>
     </row>
-    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>6</v>
       </c>
@@ -4643,7 +4648,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34">
         <v>7</v>
       </c>
@@ -4690,7 +4695,7 @@
       </c>
       <c r="AD8" s="35"/>
     </row>
-    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>8</v>
       </c>
@@ -4744,7 +4749,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="34">
         <v>9</v>
       </c>
@@ -4786,7 +4791,7 @@
       </c>
       <c r="AD10" s="35"/>
     </row>
-    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>10</v>
       </c>
@@ -4831,7 +4836,7 @@
       </c>
       <c r="AD11" s="35"/>
     </row>
-    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="34">
         <v>11</v>
       </c>
@@ -4875,7 +4880,7 @@
       </c>
       <c r="AD12" s="35"/>
     </row>
-    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>12</v>
       </c>
@@ -4925,7 +4930,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="34">
         <v>13</v>
       </c>
@@ -4968,7 +4973,7 @@
       </c>
       <c r="AD14" s="35"/>
     </row>
-    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>14</v>
       </c>
@@ -5005,7 +5010,7 @@
       </c>
       <c r="AD15" s="35"/>
     </row>
-    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="34">
         <v>15</v>
       </c>
@@ -5047,7 +5052,7 @@
       </c>
       <c r="AD16" s="35"/>
     </row>
-    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>16</v>
       </c>
@@ -5087,7 +5092,7 @@
       </c>
       <c r="AD17" s="35"/>
     </row>
-    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="34">
         <v>17</v>
       </c>
@@ -5124,7 +5129,7 @@
       </c>
       <c r="AD18" s="35"/>
     </row>
-    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>18</v>
       </c>
@@ -5164,7 +5169,7 @@
       </c>
       <c r="AD19" s="35"/>
     </row>
-    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="34">
         <v>19</v>
       </c>
@@ -5207,7 +5212,7 @@
       </c>
       <c r="AD20" s="35"/>
     </row>
-    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>20</v>
       </c>
@@ -5247,7 +5252,7 @@
       </c>
       <c r="AD21" s="35"/>
     </row>
-    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="34">
         <v>21</v>
       </c>
@@ -5293,7 +5298,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>22</v>
       </c>
@@ -5333,7 +5338,7 @@
       </c>
       <c r="AD23" s="35"/>
     </row>
-    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="34">
         <v>23</v>
       </c>
@@ -5372,7 +5377,7 @@
       </c>
       <c r="AD24" s="35"/>
     </row>
-    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>24</v>
       </c>
@@ -5422,7 +5427,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="34">
         <v>25</v>
       </c>
@@ -5464,7 +5469,7 @@
       </c>
       <c r="AD26" s="35"/>
     </row>
-    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>26</v>
       </c>
@@ -5509,7 +5514,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="34">
         <v>27</v>
       </c>
@@ -5549,7 +5554,7 @@
       </c>
       <c r="AD28" s="35"/>
     </row>
-    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>28</v>
       </c>
@@ -5589,7 +5594,7 @@
       </c>
       <c r="AD29" s="35"/>
     </row>
-    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="34">
         <v>29</v>
       </c>
@@ -5629,7 +5634,7 @@
       </c>
       <c r="AD30" s="35"/>
     </row>
-    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>30</v>
       </c>
@@ -5666,7 +5671,7 @@
       </c>
       <c r="AD31" s="35"/>
     </row>
-    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="34">
         <v>31</v>
       </c>
@@ -5715,7 +5720,7 @@
       </c>
       <c r="AD32" s="35"/>
     </row>
-    <row r="33" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
         <v>53</v>
       </c>
@@ -5840,32 +5845,32 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AE32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" customWidth="1"/>
     <col min="5" max="9" width="13" customWidth="1"/>
-    <col min="10" max="11" width="15.85546875" customWidth="1"/>
+    <col min="10" max="11" width="15.88671875" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
-    <col min="13" max="13" width="21.28515625" customWidth="1"/>
+    <col min="13" max="13" width="21.33203125" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" customWidth="1"/>
+    <col min="15" max="15" width="13.88671875" customWidth="1"/>
     <col min="16" max="20" width="13" customWidth="1"/>
-    <col min="21" max="21" width="20.28515625" customWidth="1"/>
+    <col min="21" max="21" width="20.33203125" customWidth="1"/>
     <col min="22" max="23" width="13" customWidth="1"/>
     <col min="24" max="24" width="21" customWidth="1"/>
     <col min="25" max="25" width="13" customWidth="1"/>
-    <col min="26" max="27" width="21.42578125" customWidth="1"/>
+    <col min="26" max="27" width="21.44140625" customWidth="1"/>
     <col min="28" max="28" width="13" customWidth="1"/>
     <col min="29" max="29" width="14" customWidth="1"/>
     <col min="30" max="30" width="25" customWidth="1"/>
-    <col min="31" max="31" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="28.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
         <v>1</v>
       </c>
@@ -5960,7 +5965,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34">
         <v>1</v>
       </c>
@@ -6006,7 +6011,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34">
         <v>2</v>
       </c>
@@ -6055,7 +6060,7 @@
       </c>
       <c r="AE3" s="35"/>
     </row>
-    <row r="4" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="34">
         <v>3</v>
       </c>
@@ -6096,7 +6101,7 @@
       </c>
       <c r="AE4" s="35"/>
     </row>
-    <row r="5" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>4</v>
       </c>
@@ -6142,7 +6147,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="34">
         <v>5</v>
       </c>
@@ -6190,7 +6195,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>6</v>
       </c>
@@ -6228,7 +6233,7 @@
       </c>
       <c r="AE7" s="35"/>
     </row>
-    <row r="8" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34">
         <v>7</v>
       </c>
@@ -6269,7 +6274,7 @@
       </c>
       <c r="AE8" s="35"/>
     </row>
-    <row r="9" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>8</v>
       </c>
@@ -6314,7 +6319,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="34">
         <v>9</v>
       </c>
@@ -6363,7 +6368,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>10</v>
       </c>
@@ -6419,7 +6424,7 @@
       </c>
       <c r="AE11" s="35"/>
     </row>
-    <row r="12" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="34">
         <v>11</v>
       </c>
@@ -6462,7 +6467,7 @@
       </c>
       <c r="AE12" s="35"/>
     </row>
-    <row r="13" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>12</v>
       </c>
@@ -6503,7 +6508,7 @@
       </c>
       <c r="AE13" s="35"/>
     </row>
-    <row r="14" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="34">
         <v>13</v>
       </c>
@@ -6550,7 +6555,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>14</v>
       </c>
@@ -6598,7 +6603,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="34">
         <v>15</v>
       </c>
@@ -6642,7 +6647,7 @@
       </c>
       <c r="AE16" s="35"/>
     </row>
-    <row r="17" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>16</v>
       </c>
@@ -6685,7 +6690,7 @@
       </c>
       <c r="AE17" s="35"/>
     </row>
-    <row r="18" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="34">
         <v>17</v>
       </c>
@@ -6728,7 +6733,7 @@
       </c>
       <c r="AE18" s="35"/>
     </row>
-    <row r="19" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>18</v>
       </c>
@@ -6773,7 +6778,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="34">
         <v>19</v>
       </c>
@@ -6811,7 +6816,7 @@
       </c>
       <c r="AE20" s="35"/>
     </row>
-    <row r="21" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>20</v>
       </c>
@@ -6851,7 +6856,7 @@
       </c>
       <c r="AE21" s="35"/>
     </row>
-    <row r="22" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="34">
         <v>21</v>
       </c>
@@ -6894,7 +6899,7 @@
       </c>
       <c r="AE22" s="35"/>
     </row>
-    <row r="23" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>22</v>
       </c>
@@ -6932,7 +6937,7 @@
       </c>
       <c r="AE23" s="35"/>
     </row>
-    <row r="24" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="34">
         <v>23</v>
       </c>
@@ -6970,7 +6975,7 @@
       </c>
       <c r="AE24" s="35"/>
     </row>
-    <row r="25" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>24</v>
       </c>
@@ -7015,7 +7020,7 @@
       </c>
       <c r="AE25" s="35"/>
     </row>
-    <row r="26" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="34">
         <v>25</v>
       </c>
@@ -7053,7 +7058,7 @@
       </c>
       <c r="AE26" s="35"/>
     </row>
-    <row r="27" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>26</v>
       </c>
@@ -7091,7 +7096,7 @@
       </c>
       <c r="AE27" s="35"/>
     </row>
-    <row r="28" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="34">
         <v>27</v>
       </c>
@@ -7129,7 +7134,7 @@
       </c>
       <c r="AE28" s="35"/>
     </row>
-    <row r="29" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>28</v>
       </c>
@@ -7167,7 +7172,7 @@
       </c>
       <c r="AE29" s="35"/>
     </row>
-    <row r="30" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="34">
         <v>29</v>
       </c>
@@ -7205,7 +7210,7 @@
       </c>
       <c r="AE30" s="35"/>
     </row>
-    <row r="31" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>30</v>
       </c>
@@ -7243,7 +7248,7 @@
       </c>
       <c r="AE31" s="35"/>
     </row>
-    <row r="32" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
         <v>53</v>
       </c>
@@ -7372,9 +7377,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AD33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="27" width="13" customWidth="1"/>
@@ -7382,7 +7387,7 @@
     <col min="29" max="29" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
         <v>1</v>
       </c>
@@ -7474,7 +7479,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34">
         <v>1</v>
       </c>
@@ -7511,7 +7516,7 @@
       </c>
       <c r="AD2" s="35"/>
     </row>
-    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34">
         <v>2</v>
       </c>
@@ -7548,7 +7553,7 @@
       </c>
       <c r="AD3" s="35"/>
     </row>
-    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="34">
         <v>3</v>
       </c>
@@ -7585,7 +7590,7 @@
       </c>
       <c r="AD4" s="35"/>
     </row>
-    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>4</v>
       </c>
@@ -7622,7 +7627,7 @@
       </c>
       <c r="AD5" s="35"/>
     </row>
-    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="34">
         <v>5</v>
       </c>
@@ -7659,7 +7664,7 @@
       </c>
       <c r="AD6" s="35"/>
     </row>
-    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>6</v>
       </c>
@@ -7696,7 +7701,7 @@
       </c>
       <c r="AD7" s="35"/>
     </row>
-    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34">
         <v>7</v>
       </c>
@@ -7733,7 +7738,7 @@
       </c>
       <c r="AD8" s="35"/>
     </row>
-    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>8</v>
       </c>
@@ -7770,7 +7775,7 @@
       </c>
       <c r="AD9" s="35"/>
     </row>
-    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="34">
         <v>9</v>
       </c>
@@ -7807,7 +7812,7 @@
       </c>
       <c r="AD10" s="35"/>
     </row>
-    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>10</v>
       </c>
@@ -7844,7 +7849,7 @@
       </c>
       <c r="AD11" s="35"/>
     </row>
-    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="34">
         <v>11</v>
       </c>
@@ -7881,7 +7886,7 @@
       </c>
       <c r="AD12" s="35"/>
     </row>
-    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>12</v>
       </c>
@@ -7918,7 +7923,7 @@
       </c>
       <c r="AD13" s="35"/>
     </row>
-    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="34">
         <v>13</v>
       </c>
@@ -7955,7 +7960,7 @@
       </c>
       <c r="AD14" s="35"/>
     </row>
-    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>14</v>
       </c>
@@ -7992,7 +7997,7 @@
       </c>
       <c r="AD15" s="35"/>
     </row>
-    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="34">
         <v>15</v>
       </c>
@@ -8029,7 +8034,7 @@
       </c>
       <c r="AD16" s="35"/>
     </row>
-    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>16</v>
       </c>
@@ -8066,7 +8071,7 @@
       </c>
       <c r="AD17" s="35"/>
     </row>
-    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="34">
         <v>17</v>
       </c>
@@ -8103,7 +8108,7 @@
       </c>
       <c r="AD18" s="35"/>
     </row>
-    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>18</v>
       </c>
@@ -8140,7 +8145,7 @@
       </c>
       <c r="AD19" s="35"/>
     </row>
-    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="34">
         <v>19</v>
       </c>
@@ -8177,7 +8182,7 @@
       </c>
       <c r="AD20" s="35"/>
     </row>
-    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>20</v>
       </c>
@@ -8214,7 +8219,7 @@
       </c>
       <c r="AD21" s="35"/>
     </row>
-    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="34">
         <v>21</v>
       </c>
@@ -8251,7 +8256,7 @@
       </c>
       <c r="AD22" s="35"/>
     </row>
-    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>22</v>
       </c>
@@ -8288,7 +8293,7 @@
       </c>
       <c r="AD23" s="35"/>
     </row>
-    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="34">
         <v>23</v>
       </c>
@@ -8325,7 +8330,7 @@
       </c>
       <c r="AD24" s="35"/>
     </row>
-    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>24</v>
       </c>
@@ -8362,7 +8367,7 @@
       </c>
       <c r="AD25" s="35"/>
     </row>
-    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="34">
         <v>25</v>
       </c>
@@ -8399,7 +8404,7 @@
       </c>
       <c r="AD26" s="35"/>
     </row>
-    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>26</v>
       </c>
@@ -8436,7 +8441,7 @@
       </c>
       <c r="AD27" s="35"/>
     </row>
-    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="34">
         <v>27</v>
       </c>
@@ -8473,7 +8478,7 @@
       </c>
       <c r="AD28" s="35"/>
     </row>
-    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>28</v>
       </c>
@@ -8510,7 +8515,7 @@
       </c>
       <c r="AD29" s="35"/>
     </row>
-    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="34">
         <v>29</v>
       </c>
@@ -8547,7 +8552,7 @@
       </c>
       <c r="AD30" s="35"/>
     </row>
-    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>30</v>
       </c>
@@ -8584,7 +8589,7 @@
       </c>
       <c r="AD31" s="35"/>
     </row>
-    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="34">
         <v>31</v>
       </c>
@@ -8667,7 +8672,7 @@
       </c>
       <c r="AD32" s="35"/>
     </row>
-    <row r="33" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
         <v>53</v>
       </c>
@@ -8792,36 +8797,36 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AD33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.42578125" customWidth="1"/>
-    <col min="10" max="10" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" customWidth="1"/>
+    <col min="10" max="10" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="16" max="20" width="13" customWidth="1"/>
-    <col min="21" max="21" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="22" max="23" width="13" customWidth="1"/>
-    <col min="24" max="24" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="13" customWidth="1"/>
-    <col min="26" max="26" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="13" customWidth="1"/>
     <col min="28" max="28" width="14" customWidth="1"/>
     <col min="29" max="29" width="25" customWidth="1"/>
-    <col min="30" max="30" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
         <v>1</v>
       </c>
@@ -8913,7 +8918,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34">
         <v>1</v>
       </c>
@@ -8950,7 +8955,7 @@
       </c>
       <c r="AD2" s="35"/>
     </row>
-    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34">
         <v>2</v>
       </c>
@@ -8993,7 +8998,7 @@
       </c>
       <c r="AD3" s="35"/>
     </row>
-    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="34">
         <v>3</v>
       </c>
@@ -9036,7 +9041,7 @@
       </c>
       <c r="AD4" s="35"/>
     </row>
-    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>4</v>
       </c>
@@ -9081,7 +9086,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="34">
         <v>5</v>
       </c>
@@ -9121,7 +9126,7 @@
       </c>
       <c r="AD6" s="35"/>
     </row>
-    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>6</v>
       </c>
@@ -9179,7 +9184,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34">
         <v>7</v>
       </c>
@@ -9216,7 +9221,7 @@
       </c>
       <c r="AD8" s="35"/>
     </row>
-    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>8</v>
       </c>
@@ -9259,7 +9264,7 @@
       </c>
       <c r="AD9" s="35"/>
     </row>
-    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="34">
         <v>9</v>
       </c>
@@ -9302,7 +9307,7 @@
       </c>
       <c r="AD10" s="35"/>
     </row>
-    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>10</v>
       </c>
@@ -9354,7 +9359,7 @@
       </c>
       <c r="AD11" s="35"/>
     </row>
-    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="34">
         <v>11</v>
       </c>
@@ -9395,7 +9400,7 @@
       </c>
       <c r="AD12" s="35"/>
     </row>
-    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>12</v>
       </c>
@@ -9434,7 +9439,7 @@
       </c>
       <c r="AD13" s="35"/>
     </row>
-    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="34">
         <v>13</v>
       </c>
@@ -9479,7 +9484,7 @@
       </c>
       <c r="AD14" s="35"/>
     </row>
-    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>14</v>
       </c>
@@ -9521,7 +9526,7 @@
       </c>
       <c r="AD15" s="35"/>
     </row>
-    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="34">
         <v>15</v>
       </c>
@@ -9564,7 +9569,7 @@
       </c>
       <c r="AD16" s="35"/>
     </row>
-    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>16</v>
       </c>
@@ -9609,7 +9614,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="34">
         <v>17</v>
       </c>
@@ -9650,7 +9655,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>18</v>
       </c>
@@ -9695,7 +9700,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="34">
         <v>19</v>
       </c>
@@ -9745,7 +9750,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>20</v>
       </c>
@@ -9795,7 +9800,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="34">
         <v>21</v>
       </c>
@@ -9842,7 +9847,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>22</v>
       </c>
@@ -9883,7 +9888,7 @@
       </c>
       <c r="AD23" s="35"/>
     </row>
-    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="34">
         <v>23</v>
       </c>
@@ -9923,7 +9928,7 @@
       </c>
       <c r="AD24" s="35"/>
     </row>
-    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>24</v>
       </c>
@@ -9960,7 +9965,7 @@
       </c>
       <c r="AD25" s="35"/>
     </row>
-    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="34">
         <v>25</v>
       </c>
@@ -9997,7 +10002,7 @@
       </c>
       <c r="AD26" s="35"/>
     </row>
-    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>26</v>
       </c>
@@ -10037,7 +10042,7 @@
       </c>
       <c r="AD27" s="35"/>
     </row>
-    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="34">
         <v>27</v>
       </c>
@@ -10079,7 +10084,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>28</v>
       </c>
@@ -10116,7 +10121,7 @@
       </c>
       <c r="AD29" s="35"/>
     </row>
-    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="34">
         <v>29</v>
       </c>
@@ -10153,7 +10158,7 @@
       </c>
       <c r="AD30" s="35"/>
     </row>
-    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>30</v>
       </c>
@@ -10196,7 +10201,7 @@
       </c>
       <c r="AD31" s="35"/>
     </row>
-    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="34">
         <v>31</v>
       </c>
@@ -10244,7 +10249,7 @@
       </c>
       <c r="AD32" s="35"/>
     </row>
-    <row r="33" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
         <v>53</v>
       </c>
@@ -10369,23 +10374,23 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AD32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
     <col min="5" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="15.7109375" customWidth="1"/>
+    <col min="13" max="13" width="15.6640625" customWidth="1"/>
     <col min="14" max="25" width="13" customWidth="1"/>
-    <col min="26" max="26" width="16.140625" customWidth="1"/>
+    <col min="26" max="26" width="16.109375" customWidth="1"/>
     <col min="27" max="27" width="13" customWidth="1"/>
     <col min="28" max="28" width="14" customWidth="1"/>
     <col min="29" max="29" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
         <v>1</v>
       </c>
@@ -10477,7 +10482,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34">
         <v>1</v>
       </c>
@@ -10517,7 +10522,7 @@
       </c>
       <c r="AD2" s="35"/>
     </row>
-    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34">
         <v>2</v>
       </c>
@@ -10561,7 +10566,7 @@
       </c>
       <c r="AD3" s="35"/>
     </row>
-    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="34">
         <v>3</v>
       </c>
@@ -10611,7 +10616,7 @@
       </c>
       <c r="AD4" s="35"/>
     </row>
-    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>4</v>
       </c>
@@ -10653,7 +10658,7 @@
       </c>
       <c r="AD5" s="35"/>
     </row>
-    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="34">
         <v>5</v>
       </c>
@@ -10699,7 +10704,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>6</v>
       </c>
@@ -10748,7 +10753,7 @@
       </c>
       <c r="AD7" s="35"/>
     </row>
-    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34">
         <v>7</v>
       </c>
@@ -10785,7 +10790,7 @@
       </c>
       <c r="AD8" s="35"/>
     </row>
-    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>8</v>
       </c>
@@ -10825,7 +10830,7 @@
       </c>
       <c r="AD9" s="35"/>
     </row>
-    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="34">
         <v>9</v>
       </c>
@@ -10865,7 +10870,7 @@
       </c>
       <c r="AD10" s="35"/>
     </row>
-    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>10</v>
       </c>
@@ -10907,7 +10912,7 @@
       </c>
       <c r="AD11" s="35"/>
     </row>
-    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="34">
         <v>11</v>
       </c>
@@ -10955,7 +10960,7 @@
       </c>
       <c r="AD12" s="35"/>
     </row>
-    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>12</v>
       </c>
@@ -10992,7 +10997,7 @@
       </c>
       <c r="AD13" s="35"/>
     </row>
-    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="34">
         <v>13</v>
       </c>
@@ -11035,7 +11040,7 @@
       </c>
       <c r="AD14" s="35"/>
     </row>
-    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>14</v>
       </c>
@@ -11078,7 +11083,7 @@
       </c>
       <c r="AD15" s="35"/>
     </row>
-    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="34">
         <v>15</v>
       </c>
@@ -11117,7 +11122,7 @@
       </c>
       <c r="AD16" s="35"/>
     </row>
-    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>16</v>
       </c>
@@ -11154,7 +11159,7 @@
       </c>
       <c r="AD17" s="35"/>
     </row>
-    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="34">
         <v>17</v>
       </c>
@@ -11197,7 +11202,7 @@
       </c>
       <c r="AD18" s="35"/>
     </row>
-    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>18</v>
       </c>
@@ -11240,7 +11245,7 @@
       </c>
       <c r="AD19" s="35"/>
     </row>
-    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="34">
         <v>19</v>
       </c>
@@ -11280,7 +11285,7 @@
       </c>
       <c r="AD20" s="35"/>
     </row>
-    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>20</v>
       </c>
@@ -11317,7 +11322,7 @@
       </c>
       <c r="AD21" s="35"/>
     </row>
-    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="34">
         <v>21</v>
       </c>
@@ -11354,7 +11359,7 @@
       </c>
       <c r="AD22" s="35"/>
     </row>
-    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>22</v>
       </c>
@@ -11394,7 +11399,7 @@
       </c>
       <c r="AD23" s="35"/>
     </row>
-    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="34">
         <v>23</v>
       </c>
@@ -11431,7 +11436,7 @@
       </c>
       <c r="AD24" s="35"/>
     </row>
-    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>24</v>
       </c>
@@ -11473,7 +11478,7 @@
       </c>
       <c r="AD25" s="35"/>
     </row>
-    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="34">
         <v>25</v>
       </c>
@@ -11522,7 +11527,7 @@
       </c>
       <c r="AD26" s="35"/>
     </row>
-    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>26</v>
       </c>
@@ -11559,7 +11564,7 @@
       </c>
       <c r="AD27" s="35"/>
     </row>
-    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="34">
         <v>27</v>
       </c>
@@ -11596,7 +11601,7 @@
       </c>
       <c r="AD28" s="35"/>
     </row>
-    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>28</v>
       </c>
@@ -11636,7 +11641,7 @@
       </c>
       <c r="AD29" s="35"/>
     </row>
-    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="34">
         <v>29</v>
       </c>
@@ -11679,7 +11684,7 @@
       </c>
       <c r="AD30" s="35"/>
     </row>
-    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>30</v>
       </c>
@@ -11719,7 +11724,7 @@
       </c>
       <c r="AD31" s="35"/>
     </row>
-    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
         <v>53</v>
       </c>
@@ -11844,24 +11849,24 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AD33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
     <col min="5" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="17.140625" customWidth="1"/>
+    <col min="13" max="13" width="17.109375" customWidth="1"/>
     <col min="14" max="25" width="13" customWidth="1"/>
-    <col min="26" max="26" width="15.28515625" customWidth="1"/>
+    <col min="26" max="26" width="15.33203125" customWidth="1"/>
     <col min="27" max="27" width="13" customWidth="1"/>
     <col min="28" max="28" width="14" customWidth="1"/>
     <col min="29" max="29" width="25" customWidth="1"/>
-    <col min="30" max="30" width="23.7109375" customWidth="1"/>
+    <col min="30" max="30" width="23.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
         <v>1</v>
       </c>
@@ -11953,7 +11958,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34">
         <v>1</v>
       </c>
@@ -11999,7 +12004,7 @@
       </c>
       <c r="AD2" s="35"/>
     </row>
-    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34">
         <v>2</v>
       </c>
@@ -12039,7 +12044,7 @@
       </c>
       <c r="AD3" s="35"/>
     </row>
-    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="34">
         <v>3</v>
       </c>
@@ -12087,7 +12092,7 @@
       </c>
       <c r="AD4" s="35"/>
     </row>
-    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>4</v>
       </c>
@@ -12127,7 +12132,7 @@
       </c>
       <c r="AD5" s="35"/>
     </row>
-    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="34">
         <v>5</v>
       </c>
@@ -12164,7 +12169,7 @@
       </c>
       <c r="AD6" s="35"/>
     </row>
-    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>6</v>
       </c>
@@ -12212,7 +12217,7 @@
       </c>
       <c r="AD7" s="35"/>
     </row>
-    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34">
         <v>7</v>
       </c>
@@ -12256,7 +12261,7 @@
       </c>
       <c r="AD8" s="35"/>
     </row>
-    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>8</v>
       </c>
@@ -12303,7 +12308,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="34">
         <v>9</v>
       </c>
@@ -12353,7 +12358,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>10</v>
       </c>
@@ -12401,7 +12406,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="34">
         <v>11</v>
       </c>
@@ -12443,7 +12448,7 @@
       </c>
       <c r="AD12" s="35"/>
     </row>
-    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>12</v>
       </c>
@@ -12480,7 +12485,7 @@
       </c>
       <c r="AD13" s="35"/>
     </row>
-    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="34">
         <v>13</v>
       </c>
@@ -12517,7 +12522,7 @@
       </c>
       <c r="AD14" s="35"/>
     </row>
-    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>14</v>
       </c>
@@ -12563,7 +12568,7 @@
       </c>
       <c r="AD15" s="35"/>
     </row>
-    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="34">
         <v>15</v>
       </c>
@@ -12589,18 +12594,20 @@
       <c r="U16" s="35"/>
       <c r="V16" s="35"/>
       <c r="W16" s="35"/>
-      <c r="X16" s="35"/>
+      <c r="X16" s="35">
+        <v>232.5</v>
+      </c>
       <c r="Y16" s="35"/>
       <c r="Z16" s="35"/>
       <c r="AA16" s="35"/>
       <c r="AB16" s="36"/>
       <c r="AC16" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>232.5</v>
       </c>
       <c r="AD16" s="35"/>
     </row>
-    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>16</v>
       </c>
@@ -12620,7 +12627,10 @@
       <c r="O17" s="35"/>
       <c r="P17" s="35"/>
       <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
+      <c r="R17" s="35">
+        <f>1056-77.9</f>
+        <v>978.1</v>
+      </c>
       <c r="S17" s="35"/>
       <c r="T17" s="35"/>
       <c r="U17" s="35"/>
@@ -12633,11 +12643,11 @@
       <c r="AB17" s="36"/>
       <c r="AC17" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>978.1</v>
       </c>
       <c r="AD17" s="35"/>
     </row>
-    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="34">
         <v>17</v>
       </c>
@@ -12657,9 +12667,15 @@
       <c r="O18" s="35"/>
       <c r="P18" s="35"/>
       <c r="Q18" s="35"/>
-      <c r="R18" s="35"/>
+      <c r="R18" s="35">
+        <f>2213.22-34.71+460-33.95</f>
+        <v>2604.56</v>
+      </c>
       <c r="S18" s="35"/>
-      <c r="T18" s="35"/>
+      <c r="T18" s="35">
+        <f>1000-16.39</f>
+        <v>983.61</v>
+      </c>
       <c r="U18" s="35"/>
       <c r="V18" s="35"/>
       <c r="W18" s="35"/>
@@ -12670,11 +12686,11 @@
       <c r="AB18" s="36"/>
       <c r="AC18" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3588.17</v>
       </c>
       <c r="AD18" s="35"/>
     </row>
-    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>18</v>
       </c>
@@ -12694,9 +12710,14 @@
       <c r="O19" s="35"/>
       <c r="P19" s="35"/>
       <c r="Q19" s="35"/>
-      <c r="R19" s="35"/>
+      <c r="R19" s="35">
+        <f>316-5.18+790+1090.89-13.03-18.37</f>
+        <v>2160.31</v>
+      </c>
       <c r="S19" s="35"/>
-      <c r="T19" s="35"/>
+      <c r="T19" s="35">
+        <v>340</v>
+      </c>
       <c r="U19" s="35"/>
       <c r="V19" s="35"/>
       <c r="W19" s="35"/>
@@ -12707,11 +12728,11 @@
       <c r="AB19" s="36"/>
       <c r="AC19" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2500.31</v>
       </c>
       <c r="AD19" s="35"/>
     </row>
-    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="34">
         <v>19</v>
       </c>
@@ -12728,12 +12749,20 @@
       <c r="L20" s="35"/>
       <c r="M20" s="35"/>
       <c r="N20" s="35"/>
-      <c r="O20" s="35"/>
+      <c r="O20" s="35">
+        <f>500-8.19</f>
+        <v>491.81</v>
+      </c>
       <c r="P20" s="35"/>
       <c r="Q20" s="35"/>
       <c r="R20" s="35"/>
-      <c r="S20" s="35"/>
-      <c r="T20" s="35"/>
+      <c r="S20" s="35">
+        <f>530-8.69</f>
+        <v>521.30999999999995</v>
+      </c>
+      <c r="T20" s="35">
+        <v>500</v>
+      </c>
       <c r="U20" s="35"/>
       <c r="V20" s="35"/>
       <c r="W20" s="35"/>
@@ -12744,11 +12773,11 @@
       <c r="AB20" s="36"/>
       <c r="AC20" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1513.12</v>
       </c>
       <c r="AD20" s="35"/>
     </row>
-    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>20</v>
       </c>
@@ -12785,7 +12814,7 @@
       </c>
       <c r="AD21" s="35"/>
     </row>
-    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="34">
         <v>21</v>
       </c>
@@ -12805,7 +12834,10 @@
       <c r="O22" s="35"/>
       <c r="P22" s="35"/>
       <c r="Q22" s="35"/>
-      <c r="R22" s="35"/>
+      <c r="R22" s="35">
+        <f>819-6.64-12.83-21.77-21.2+405+1328+1293+358</f>
+        <v>4140.5599999999995</v>
+      </c>
       <c r="S22" s="35"/>
       <c r="T22" s="35"/>
       <c r="U22" s="35"/>
@@ -12818,11 +12850,11 @@
       <c r="AB22" s="36"/>
       <c r="AC22" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4140.5599999999995</v>
       </c>
       <c r="AD22" s="35"/>
     </row>
-    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>22</v>
       </c>
@@ -12842,7 +12874,9 @@
       <c r="O23" s="35"/>
       <c r="P23" s="35"/>
       <c r="Q23" s="35"/>
-      <c r="R23" s="35"/>
+      <c r="R23" s="35">
+        <v>602.5</v>
+      </c>
       <c r="S23" s="35"/>
       <c r="T23" s="35"/>
       <c r="U23" s="35"/>
@@ -12855,11 +12889,11 @@
       <c r="AB23" s="36"/>
       <c r="AC23" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>602.5</v>
       </c>
       <c r="AD23" s="35"/>
     </row>
-    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="34">
         <v>23</v>
       </c>
@@ -12896,7 +12930,7 @@
       </c>
       <c r="AD24" s="35"/>
     </row>
-    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>24</v>
       </c>
@@ -12933,7 +12967,7 @@
       </c>
       <c r="AD25" s="35"/>
     </row>
-    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="34">
         <v>25</v>
       </c>
@@ -12970,7 +13004,7 @@
       </c>
       <c r="AD26" s="35"/>
     </row>
-    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>26</v>
       </c>
@@ -13007,7 +13041,7 @@
       </c>
       <c r="AD27" s="35"/>
     </row>
-    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="34">
         <v>27</v>
       </c>
@@ -13044,7 +13078,7 @@
       </c>
       <c r="AD28" s="35"/>
     </row>
-    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>28</v>
       </c>
@@ -13081,7 +13115,7 @@
       </c>
       <c r="AD29" s="35"/>
     </row>
-    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="34">
         <v>29</v>
       </c>
@@ -13118,7 +13152,7 @@
       </c>
       <c r="AD30" s="35"/>
     </row>
-    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>30</v>
       </c>
@@ -13155,7 +13189,7 @@
       </c>
       <c r="AD31" s="35"/>
     </row>
-    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="34">
         <v>31</v>
       </c>
@@ -13192,7 +13226,7 @@
       </c>
       <c r="AD32" s="35"/>
     </row>
-    <row r="33" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
         <v>53</v>
       </c>
@@ -13250,7 +13284,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="1"/>
-        <v>491.81</v>
+        <v>983.62</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="1"/>
@@ -13262,15 +13296,15 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="1"/>
-        <v>10926.310000000001</v>
+        <v>21412.340000000004</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="1"/>
-        <v>560.72</v>
+        <v>1082.03</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="1"/>
-        <v>1534.43</v>
+        <v>3358.04</v>
       </c>
       <c r="U33" s="12">
         <f t="shared" si="1"/>
@@ -13284,9 +13318,9 @@
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="X33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="X33" s="12">
+        <f t="shared" si="1"/>
+        <v>232.5</v>
       </c>
       <c r="Y33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -13306,7 +13340,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>143478.09</v>
+        <v>157033.35</v>
       </c>
       <c r="AD33" s="39"/>
     </row>
@@ -13317,9 +13351,9 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AD32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="27" width="13" customWidth="1"/>
@@ -13327,7 +13361,7 @@
     <col min="29" max="29" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
         <v>1</v>
       </c>
@@ -13419,7 +13453,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34">
         <v>1</v>
       </c>
@@ -13456,7 +13490,7 @@
       </c>
       <c r="AD2" s="35"/>
     </row>
-    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34">
         <v>2</v>
       </c>
@@ -13493,7 +13527,7 @@
       </c>
       <c r="AD3" s="35"/>
     </row>
-    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="34">
         <v>3</v>
       </c>
@@ -13530,7 +13564,7 @@
       </c>
       <c r="AD4" s="35"/>
     </row>
-    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>4</v>
       </c>
@@ -13567,7 +13601,7 @@
       </c>
       <c r="AD5" s="35"/>
     </row>
-    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="34">
         <v>5</v>
       </c>
@@ -13604,7 +13638,7 @@
       </c>
       <c r="AD6" s="35"/>
     </row>
-    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>6</v>
       </c>
@@ -13641,7 +13675,7 @@
       </c>
       <c r="AD7" s="35"/>
     </row>
-    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34">
         <v>7</v>
       </c>
@@ -13678,7 +13712,7 @@
       </c>
       <c r="AD8" s="35"/>
     </row>
-    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>8</v>
       </c>
@@ -13715,7 +13749,7 @@
       </c>
       <c r="AD9" s="35"/>
     </row>
-    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="34">
         <v>9</v>
       </c>
@@ -13752,7 +13786,7 @@
       </c>
       <c r="AD10" s="35"/>
     </row>
-    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>10</v>
       </c>
@@ -13789,7 +13823,7 @@
       </c>
       <c r="AD11" s="35"/>
     </row>
-    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="34">
         <v>11</v>
       </c>
@@ -13826,7 +13860,7 @@
       </c>
       <c r="AD12" s="35"/>
     </row>
-    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>12</v>
       </c>
@@ -13863,7 +13897,7 @@
       </c>
       <c r="AD13" s="35"/>
     </row>
-    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="34">
         <v>13</v>
       </c>
@@ -13900,7 +13934,7 @@
       </c>
       <c r="AD14" s="35"/>
     </row>
-    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>14</v>
       </c>
@@ -13937,7 +13971,7 @@
       </c>
       <c r="AD15" s="35"/>
     </row>
-    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="34">
         <v>15</v>
       </c>
@@ -13974,7 +14008,7 @@
       </c>
       <c r="AD16" s="35"/>
     </row>
-    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>16</v>
       </c>
@@ -14011,7 +14045,7 @@
       </c>
       <c r="AD17" s="35"/>
     </row>
-    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="34">
         <v>17</v>
       </c>
@@ -14048,7 +14082,7 @@
       </c>
       <c r="AD18" s="35"/>
     </row>
-    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>18</v>
       </c>
@@ -14085,7 +14119,7 @@
       </c>
       <c r="AD19" s="35"/>
     </row>
-    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="34">
         <v>19</v>
       </c>
@@ -14122,7 +14156,7 @@
       </c>
       <c r="AD20" s="35"/>
     </row>
-    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>20</v>
       </c>
@@ -14159,7 +14193,7 @@
       </c>
       <c r="AD21" s="35"/>
     </row>
-    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="34">
         <v>21</v>
       </c>
@@ -14196,7 +14230,7 @@
       </c>
       <c r="AD22" s="35"/>
     </row>
-    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>22</v>
       </c>
@@ -14233,7 +14267,7 @@
       </c>
       <c r="AD23" s="35"/>
     </row>
-    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="34">
         <v>23</v>
       </c>
@@ -14270,7 +14304,7 @@
       </c>
       <c r="AD24" s="35"/>
     </row>
-    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>24</v>
       </c>
@@ -14307,7 +14341,7 @@
       </c>
       <c r="AD25" s="35"/>
     </row>
-    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="34">
         <v>25</v>
       </c>
@@ -14344,7 +14378,7 @@
       </c>
       <c r="AD26" s="35"/>
     </row>
-    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>26</v>
       </c>
@@ -14381,7 +14415,7 @@
       </c>
       <c r="AD27" s="35"/>
     </row>
-    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="34">
         <v>27</v>
       </c>
@@ -14418,7 +14452,7 @@
       </c>
       <c r="AD28" s="35"/>
     </row>
-    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>28</v>
       </c>
@@ -14455,7 +14489,7 @@
       </c>
       <c r="AD29" s="35"/>
     </row>
-    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="34">
         <v>29</v>
       </c>
@@ -14492,7 +14526,7 @@
       </c>
       <c r="AD30" s="35"/>
     </row>
-    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>30</v>
       </c>
@@ -14529,7 +14563,7 @@
       </c>
       <c r="AD31" s="35"/>
     </row>
-    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
         <v>53</v>
       </c>
@@ -14654,9 +14688,9 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AD33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="27" width="13" customWidth="1"/>
@@ -14664,7 +14698,7 @@
     <col min="29" max="29" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
         <v>1</v>
       </c>
@@ -14756,7 +14790,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34">
         <v>1</v>
       </c>
@@ -14793,7 +14827,7 @@
       </c>
       <c r="AD2" s="35"/>
     </row>
-    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34">
         <v>2</v>
       </c>
@@ -14830,7 +14864,7 @@
       </c>
       <c r="AD3" s="35"/>
     </row>
-    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="34">
         <v>3</v>
       </c>
@@ -14867,7 +14901,7 @@
       </c>
       <c r="AD4" s="35"/>
     </row>
-    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>4</v>
       </c>
@@ -14904,7 +14938,7 @@
       </c>
       <c r="AD5" s="35"/>
     </row>
-    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="34">
         <v>5</v>
       </c>
@@ -14941,7 +14975,7 @@
       </c>
       <c r="AD6" s="35"/>
     </row>
-    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>6</v>
       </c>
@@ -14978,7 +15012,7 @@
       </c>
       <c r="AD7" s="35"/>
     </row>
-    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34">
         <v>7</v>
       </c>
@@ -15015,7 +15049,7 @@
       </c>
       <c r="AD8" s="35"/>
     </row>
-    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>8</v>
       </c>
@@ -15052,7 +15086,7 @@
       </c>
       <c r="AD9" s="35"/>
     </row>
-    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="34">
         <v>9</v>
       </c>
@@ -15089,7 +15123,7 @@
       </c>
       <c r="AD10" s="35"/>
     </row>
-    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>10</v>
       </c>
@@ -15126,7 +15160,7 @@
       </c>
       <c r="AD11" s="35"/>
     </row>
-    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="34">
         <v>11</v>
       </c>
@@ -15163,7 +15197,7 @@
       </c>
       <c r="AD12" s="35"/>
     </row>
-    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>12</v>
       </c>
@@ -15200,7 +15234,7 @@
       </c>
       <c r="AD13" s="35"/>
     </row>
-    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="34">
         <v>13</v>
       </c>
@@ -15237,7 +15271,7 @@
       </c>
       <c r="AD14" s="35"/>
     </row>
-    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>14</v>
       </c>
@@ -15274,7 +15308,7 @@
       </c>
       <c r="AD15" s="35"/>
     </row>
-    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="34">
         <v>15</v>
       </c>
@@ -15311,7 +15345,7 @@
       </c>
       <c r="AD16" s="35"/>
     </row>
-    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>16</v>
       </c>
@@ -15348,7 +15382,7 @@
       </c>
       <c r="AD17" s="35"/>
     </row>
-    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="34">
         <v>17</v>
       </c>
@@ -15385,7 +15419,7 @@
       </c>
       <c r="AD18" s="35"/>
     </row>
-    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>18</v>
       </c>
@@ -15422,7 +15456,7 @@
       </c>
       <c r="AD19" s="35"/>
     </row>
-    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="34">
         <v>19</v>
       </c>
@@ -15459,7 +15493,7 @@
       </c>
       <c r="AD20" s="35"/>
     </row>
-    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>20</v>
       </c>
@@ -15496,7 +15530,7 @@
       </c>
       <c r="AD21" s="35"/>
     </row>
-    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="34">
         <v>21</v>
       </c>
@@ -15533,7 +15567,7 @@
       </c>
       <c r="AD22" s="35"/>
     </row>
-    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>22</v>
       </c>
@@ -15570,7 +15604,7 @@
       </c>
       <c r="AD23" s="35"/>
     </row>
-    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="34">
         <v>23</v>
       </c>
@@ -15607,7 +15641,7 @@
       </c>
       <c r="AD24" s="35"/>
     </row>
-    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>24</v>
       </c>
@@ -15644,7 +15678,7 @@
       </c>
       <c r="AD25" s="35"/>
     </row>
-    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="34">
         <v>25</v>
       </c>
@@ -15681,7 +15715,7 @@
       </c>
       <c r="AD26" s="35"/>
     </row>
-    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>26</v>
       </c>
@@ -15718,7 +15752,7 @@
       </c>
       <c r="AD27" s="35"/>
     </row>
-    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="34">
         <v>27</v>
       </c>
@@ -15755,7 +15789,7 @@
       </c>
       <c r="AD28" s="35"/>
     </row>
-    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>28</v>
       </c>
@@ -15792,7 +15826,7 @@
       </c>
       <c r="AD29" s="35"/>
     </row>
-    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="34">
         <v>29</v>
       </c>
@@ -15829,7 +15863,7 @@
       </c>
       <c r="AD30" s="35"/>
     </row>
-    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>30</v>
       </c>
@@ -15866,7 +15900,7 @@
       </c>
       <c r="AD31" s="35"/>
     </row>
-    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="34">
         <v>31</v>
       </c>
@@ -15903,7 +15937,7 @@
       </c>
       <c r="AD32" s="35"/>
     </row>
-    <row r="33" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
         <v>53</v>
       </c>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/289bf34ef3ebdbf8/Desktop/Nico/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_3528FC9679616F11138CF261575EFE9D5C3E667E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62BA9EAD-42C5-4C6C-A885-C6B806D146A5}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_3528FC9679616F11138CF261575EFE9D5C3E667E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{279A7867-ABBF-40F1-ADE2-CD7B172CC853}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2669,9 +2669,9 @@
         <f>IF(Octubre!L33&gt;0,Octubre!L33,"")</f>
         <v>17990.03</v>
       </c>
-      <c r="M19" s="1" t="str">
+      <c r="M19" s="1">
         <f>IF(Octubre!M33&gt;0,Octubre!M33,"")</f>
-        <v/>
+        <v>16693.46</v>
       </c>
       <c r="N19" s="1">
         <f>IF(Octubre!N33&gt;0,Octubre!N33,"")</f>
@@ -3679,9 +3679,9 @@
         <f>IF(ISNUMBER(Octubre!L33),L8-Octubre!L33,"")</f>
         <v>9.9700000000011642</v>
       </c>
-      <c r="M30" s="1" t="str">
+      <c r="M30" s="1">
         <f>IF(ISNUMBER(Octubre!M33),M8-Octubre!M33,"")</f>
-        <v/>
+        <v>6.5400000000008731</v>
       </c>
       <c r="N30" s="1">
         <f>IF(ISNUMBER(Octubre!N33),N8-Octubre!N33,"")</f>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AC30" s="12">
         <f t="shared" si="7"/>
-        <v>10802.789999999997</v>
+        <v>10809.329999999998</v>
       </c>
     </row>
     <row r="31" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="M33" s="12">
         <f t="shared" si="8"/>
-        <v>-13678.119999999999</v>
+        <v>-13671.579999999998</v>
       </c>
       <c r="N33" s="12">
         <f t="shared" si="8"/>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>2608.2799999999952</v>
+        <v>2614.8199999999961</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12829,7 +12829,10 @@
       <c r="J22" s="35"/>
       <c r="K22" s="35"/>
       <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
+      <c r="M22" s="35">
+        <f>15187.97+1505.49</f>
+        <v>16693.46</v>
+      </c>
       <c r="N22" s="35"/>
       <c r="O22" s="35"/>
       <c r="P22" s="35"/>
@@ -12850,7 +12853,7 @@
       <c r="AB22" s="36"/>
       <c r="AC22" s="35">
         <f t="shared" si="0"/>
-        <v>4140.5599999999995</v>
+        <v>20834.019999999997</v>
       </c>
       <c r="AD22" s="35"/>
     </row>
@@ -13274,9 +13277,9 @@
         <f t="shared" si="1"/>
         <v>17990.03</v>
       </c>
-      <c r="M33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="M33" s="12">
+        <f t="shared" si="1"/>
+        <v>16693.46</v>
       </c>
       <c r="N33" s="12">
         <f t="shared" si="1"/>
@@ -13340,7 +13343,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>157033.35</v>
+        <v>173726.81</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/289bf34ef3ebdbf8/Desktop/Nico/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_3528FC9679616F11138CF261575EFE9D5C3E667E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{279A7867-ABBF-40F1-ADE2-CD7B172CC853}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="11_3528FC9679616F11138CF261575EFE9D5C3E667E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FF28754-EB8E-4972-BB7C-7EBB2970BDF5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -971,7 +971,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AJ54"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" style="1" customWidth="1"/>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="O19" s="1">
         <f>IF(Octubre!O33&gt;0,Octubre!O33,"")</f>
-        <v>983.62</v>
+        <v>4904.62</v>
       </c>
       <c r="P19" s="1">
         <f>IF(Octubre!P33&gt;0,Octubre!P33,"")</f>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="R19" s="1">
         <f>IF(Octubre!R33&gt;0,Octubre!R33,"")</f>
-        <v>21412.340000000004</v>
+        <v>22584.360000000004</v>
       </c>
       <c r="S19" s="1">
         <f>IF(Octubre!S33&gt;0,Octubre!S33,"")</f>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="O30" s="1">
         <f>IF(ISNUMBER(Octubre!O33),O8-Octubre!O33,"")</f>
-        <v>3416.38</v>
+        <v>-504.61999999999989</v>
       </c>
       <c r="P30" s="1">
         <f>IF(ISNUMBER(Octubre!P33),P8-Octubre!P33,"")</f>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="R30" s="1">
         <f>IF(ISNUMBER(Octubre!R33),R8-Octubre!R33,"")</f>
-        <v>-1412.3400000000038</v>
+        <v>-2584.3600000000042</v>
       </c>
       <c r="S30" s="1">
         <f>IF(ISNUMBER(Octubre!S33),S8-Octubre!S33,"")</f>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AC30" s="12">
         <f t="shared" si="7"/>
-        <v>10809.329999999998</v>
+        <v>5716.3099999999977</v>
       </c>
     </row>
     <row r="31" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="8"/>
-        <v>14126.05</v>
+        <v>10205.049999999999</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="8"/>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>-3992.380000000001</v>
+        <v>-5164.4000000000015</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>2614.8199999999961</v>
+        <v>-2478.2000000000044</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4278,7 +4278,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AD33"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="13" customWidth="1"/>
@@ -5847,7 +5847,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AE32"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="13" customWidth="1"/>
@@ -7379,7 +7379,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AD33"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="27" width="13" customWidth="1"/>
@@ -8799,7 +8799,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AD33"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="13" customWidth="1"/>
@@ -10376,7 +10376,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AD32"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="13" customWidth="1"/>
@@ -11851,7 +11851,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AD33"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="13" customWidth="1"/>
@@ -12878,7 +12878,8 @@
       <c r="P23" s="35"/>
       <c r="Q23" s="35"/>
       <c r="R23" s="35">
-        <v>602.5</v>
+        <f>602.5+1172.02</f>
+        <v>1774.52</v>
       </c>
       <c r="S23" s="35"/>
       <c r="T23" s="35"/>
@@ -12892,7 +12893,7 @@
       <c r="AB23" s="36"/>
       <c r="AC23" s="35">
         <f t="shared" si="0"/>
-        <v>602.5</v>
+        <v>1774.52</v>
       </c>
       <c r="AD23" s="35"/>
     </row>
@@ -12913,7 +12914,9 @@
       <c r="L24" s="35"/>
       <c r="M24" s="35"/>
       <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
+      <c r="O24" s="35">
+        <v>3921</v>
+      </c>
       <c r="P24" s="35"/>
       <c r="Q24" s="35"/>
       <c r="R24" s="35"/>
@@ -12929,7 +12932,7 @@
       <c r="AB24" s="36"/>
       <c r="AC24" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3921</v>
       </c>
       <c r="AD24" s="35"/>
     </row>
@@ -13287,7 +13290,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="1"/>
-        <v>983.62</v>
+        <v>4904.62</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="1"/>
@@ -13299,7 +13302,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="1"/>
-        <v>21412.340000000004</v>
+        <v>22584.360000000004</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="1"/>
@@ -13343,7 +13346,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>173726.81</v>
+        <v>178819.83</v>
       </c>
       <c r="AD33" s="39"/>
     </row>
@@ -13356,7 +13359,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AD32"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="27" width="13" customWidth="1"/>
@@ -14693,7 +14696,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AD33"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="27" width="13" customWidth="1"/>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/289bf34ef3ebdbf8/Desktop/Nico/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="11_3528FC9679616F11138CF261575EFE9D5C3E667E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FF28754-EB8E-4972-BB7C-7EBB2970BDF5}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_3528FC9679616F11138CF261575EFE9D5C3E667E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7831965D-6584-4DC5-AC53-68E5FF0C1E36}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="O19" s="1">
         <f>IF(Octubre!O33&gt;0,Octubre!O33,"")</f>
-        <v>4904.62</v>
+        <v>3963.58</v>
       </c>
       <c r="P19" s="1">
         <f>IF(Octubre!P33&gt;0,Octubre!P33,"")</f>
@@ -2691,15 +2691,15 @@
       </c>
       <c r="R19" s="1">
         <f>IF(Octubre!R33&gt;0,Octubre!R33,"")</f>
-        <v>22584.360000000004</v>
+        <v>24729.650000000005</v>
       </c>
       <c r="S19" s="1">
         <f>IF(Octubre!S33&gt;0,Octubre!S33,"")</f>
-        <v>1082.03</v>
+        <v>4082.0299999999997</v>
       </c>
       <c r="T19" s="1">
         <f>IF(Octubre!T33&gt;0,Octubre!T33,"")</f>
-        <v>3358.04</v>
+        <v>7255.42</v>
       </c>
       <c r="U19" s="1" t="str">
         <f>IF(Octubre!U33&gt;0,Octubre!U33,"")</f>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="O30" s="1">
         <f>IF(ISNUMBER(Octubre!O33),O8-Octubre!O33,"")</f>
-        <v>-504.61999999999989</v>
+        <v>436.42000000000007</v>
       </c>
       <c r="P30" s="1">
         <f>IF(ISNUMBER(Octubre!P33),P8-Octubre!P33,"")</f>
@@ -3701,15 +3701,15 @@
       </c>
       <c r="R30" s="1">
         <f>IF(ISNUMBER(Octubre!R33),R8-Octubre!R33,"")</f>
-        <v>-2584.3600000000042</v>
+        <v>-4729.6500000000051</v>
       </c>
       <c r="S30" s="1">
         <f>IF(ISNUMBER(Octubre!S33),S8-Octubre!S33,"")</f>
-        <v>917.97</v>
+        <v>-2082.0299999999997</v>
       </c>
       <c r="T30" s="1">
         <f>IF(ISNUMBER(Octubre!T33),T8-Octubre!T33,"")</f>
-        <v>1641.96</v>
+        <v>-2255.42</v>
       </c>
       <c r="U30" s="1">
         <f>IF(ISNUMBER(Octubre!U33),U8-Octubre!U33,"")</f>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AC30" s="12">
         <f t="shared" si="7"/>
-        <v>5716.3099999999977</v>
+        <v>-2385.3200000000024</v>
       </c>
     </row>
     <row r="31" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="8"/>
-        <v>10205.049999999999</v>
+        <v>11146.09</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="8"/>
@@ -4040,15 +4040,15 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>-5164.4000000000015</v>
+        <v>-7309.6900000000023</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
-        <v>3679.51</v>
+        <v>679.51000000000067</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="8"/>
-        <v>5679.93</v>
+        <v>1782.5500000000006</v>
       </c>
       <c r="U33" s="12">
         <f t="shared" si="8"/>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>-2478.2000000000044</v>
+        <v>-10579.830000000002</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12953,12 +12953,20 @@
       <c r="L25" s="35"/>
       <c r="M25" s="35"/>
       <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
+      <c r="O25" s="35">
+        <v>-941.04</v>
+      </c>
       <c r="P25" s="35"/>
       <c r="Q25" s="35"/>
-      <c r="R25" s="35"/>
+      <c r="R25" s="35">
+        <f>67-1.1+206.89-3.39+1395-19.27</f>
+        <v>1645.13</v>
+      </c>
       <c r="S25" s="35"/>
-      <c r="T25" s="35"/>
+      <c r="T25" s="35">
+        <f>1100+440+160-2.62</f>
+        <v>1697.38</v>
+      </c>
       <c r="U25" s="35"/>
       <c r="V25" s="35"/>
       <c r="W25" s="35"/>
@@ -12969,7 +12977,7 @@
       <c r="AB25" s="36"/>
       <c r="AC25" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2401.4700000000003</v>
       </c>
       <c r="AD25" s="35"/>
     </row>
@@ -12993,9 +13001,16 @@
       <c r="O26" s="35"/>
       <c r="P26" s="35"/>
       <c r="Q26" s="35"/>
-      <c r="R26" s="35"/>
-      <c r="S26" s="35"/>
-      <c r="T26" s="35"/>
+      <c r="R26" s="35">
+        <f>540-39.84</f>
+        <v>500.15999999999997</v>
+      </c>
+      <c r="S26" s="35">
+        <v>3000</v>
+      </c>
+      <c r="T26" s="35">
+        <v>2200</v>
+      </c>
       <c r="U26" s="35"/>
       <c r="V26" s="35"/>
       <c r="W26" s="35"/>
@@ -13006,7 +13021,7 @@
       <c r="AB26" s="36"/>
       <c r="AC26" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5700.16</v>
       </c>
       <c r="AD26" s="35"/>
     </row>
@@ -13289,8 +13304,8 @@
         <v>810</v>
       </c>
       <c r="O33" s="12">
-        <f t="shared" si="1"/>
-        <v>4904.62</v>
+        <f>IF(COUNTA(O2:O32)&gt;0,SUM(O2:O32),"")</f>
+        <v>3963.58</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="1"/>
@@ -13302,15 +13317,15 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="1"/>
-        <v>22584.360000000004</v>
+        <v>24729.650000000005</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="1"/>
-        <v>1082.03</v>
+        <v>4082.0299999999997</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="1"/>
-        <v>3358.04</v>
+        <v>7255.42</v>
       </c>
       <c r="U33" s="12">
         <f t="shared" si="1"/>
@@ -13346,7 +13361,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>178819.83</v>
+        <v>186921.46</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/289bf34ef3ebdbf8/Desktop/Nico/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="11_3528FC9679616F11138CF261575EFE9D5C3E667E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7831965D-6584-4DC5-AC53-68E5FF0C1E36}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="11_3528FC9679616F11138CF261575EFE9D5C3E667E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{813554D3-26ED-4233-8B7A-084F051B83B9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="Noviembre" sheetId="8" r:id="rId8"/>
     <sheet name="Diciembre" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="95">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t>libros roci y auriculares</t>
+  </si>
+  <si>
+    <t>luces y sellador baño</t>
   </si>
 </sst>
 </file>
@@ -2691,7 +2694,7 @@
       </c>
       <c r="R19" s="1">
         <f>IF(Octubre!R33&gt;0,Octubre!R33,"")</f>
-        <v>24729.650000000005</v>
+        <v>25980.160000000003</v>
       </c>
       <c r="S19" s="1">
         <f>IF(Octubre!S33&gt;0,Octubre!S33,"")</f>
@@ -2727,7 +2730,7 @@
       </c>
       <c r="AA19" s="1">
         <f>IF(Octubre!AA33&gt;0,Octubre!AA33,"")</f>
-        <v>5072.79</v>
+        <v>7220.91</v>
       </c>
     </row>
     <row r="20" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3701,7 +3704,7 @@
       </c>
       <c r="R30" s="1">
         <f>IF(ISNUMBER(Octubre!R33),R8-Octubre!R33,"")</f>
-        <v>-4729.6500000000051</v>
+        <v>-5980.1600000000035</v>
       </c>
       <c r="S30" s="1">
         <f>IF(ISNUMBER(Octubre!S33),S8-Octubre!S33,"")</f>
@@ -3737,11 +3740,11 @@
       </c>
       <c r="AA30" s="1">
         <f>IF(ISNUMBER(Octubre!AA33),AA8-Octubre!AA33,"")</f>
-        <v>-72.789999999999964</v>
+        <v>-2220.91</v>
       </c>
       <c r="AC30" s="12">
         <f t="shared" si="7"/>
-        <v>-2385.3200000000024</v>
+        <v>-5783.9500000000007</v>
       </c>
     </row>
     <row r="31" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4040,7 +4043,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>-7309.6900000000023</v>
+        <v>-8560.2000000000007</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4076,11 +4079,11 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>-15386.39</v>
+        <v>-17534.509999999998</v>
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>-10579.830000000002</v>
+        <v>-13978.46</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -13017,13 +13020,18 @@
       <c r="X26" s="35"/>
       <c r="Y26" s="35"/>
       <c r="Z26" s="35"/>
-      <c r="AA26" s="35"/>
+      <c r="AA26" s="35">
+        <f>409+340-7.44</f>
+        <v>741.56</v>
+      </c>
       <c r="AB26" s="36"/>
       <c r="AC26" s="35">
         <f t="shared" si="0"/>
-        <v>5700.16</v>
-      </c>
-      <c r="AD26" s="35"/>
+        <v>6441.7199999999993</v>
+      </c>
+      <c r="AD26" s="35" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
@@ -13045,7 +13053,10 @@
       <c r="O27" s="35"/>
       <c r="P27" s="35"/>
       <c r="Q27" s="35"/>
-      <c r="R27" s="35"/>
+      <c r="R27" s="35">
+        <f>451+821-13.45-8.04</f>
+        <v>1250.51</v>
+      </c>
       <c r="S27" s="35"/>
       <c r="T27" s="35"/>
       <c r="U27" s="35"/>
@@ -13054,13 +13065,18 @@
       <c r="X27" s="35"/>
       <c r="Y27" s="35"/>
       <c r="Z27" s="35"/>
-      <c r="AA27" s="35"/>
+      <c r="AA27" s="35">
+        <f>485-7.95+945-15.49</f>
+        <v>1406.56</v>
+      </c>
       <c r="AB27" s="36"/>
       <c r="AC27" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD27" s="35"/>
+        <v>2657.0699999999997</v>
+      </c>
+      <c r="AD27" s="35" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="34">
@@ -13317,7 +13333,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="1"/>
-        <v>24729.650000000005</v>
+        <v>25980.160000000003</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="1"/>
@@ -13353,7 +13369,7 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="1"/>
-        <v>5072.79</v>
+        <v>7220.91</v>
       </c>
       <c r="AB33" s="38" t="str">
         <f t="shared" si="1"/>
@@ -13361,7 +13377,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>186921.46</v>
+        <v>190320.09</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/289bf34ef3ebdbf8/Desktop/Nico/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="11_3528FC9679616F11138CF261575EFE9D5C3E667E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{813554D3-26ED-4233-8B7A-084F051B83B9}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="11_3528FC9679616F11138CF261575EFE9D5C3E667E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{055BA2EC-CD94-484B-A894-4E7F8D74BEEB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -2686,19 +2686,19 @@
       </c>
       <c r="P19" s="1">
         <f>IF(Octubre!P33&gt;0,Octubre!P33,"")</f>
-        <v>1800</v>
-      </c>
-      <c r="Q19" s="1" t="str">
+        <v>3600</v>
+      </c>
+      <c r="Q19" s="1">
         <f>IF(Octubre!Q33&gt;0,Octubre!Q33,"")</f>
-        <v/>
+        <v>2508.1999999999998</v>
       </c>
       <c r="R19" s="1">
         <f>IF(Octubre!R33&gt;0,Octubre!R33,"")</f>
-        <v>25980.160000000003</v>
+        <v>27515.760000000006</v>
       </c>
       <c r="S19" s="1">
         <f>IF(Octubre!S33&gt;0,Octubre!S33,"")</f>
-        <v>4082.0299999999997</v>
+        <v>4313.4399999999996</v>
       </c>
       <c r="T19" s="1">
         <f>IF(Octubre!T33&gt;0,Octubre!T33,"")</f>
@@ -3696,19 +3696,19 @@
       </c>
       <c r="P30" s="1">
         <f>IF(ISNUMBER(Octubre!P33),P8-Octubre!P33,"")</f>
-        <v>1800</v>
-      </c>
-      <c r="Q30" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="1">
         <f>IF(ISNUMBER(Octubre!Q33),Q8-Octubre!Q33,"")</f>
-        <v/>
+        <v>-8.1999999999998181</v>
       </c>
       <c r="R30" s="1">
         <f>IF(ISNUMBER(Octubre!R33),R8-Octubre!R33,"")</f>
-        <v>-5980.1600000000035</v>
+        <v>-7515.7600000000057</v>
       </c>
       <c r="S30" s="1">
         <f>IF(ISNUMBER(Octubre!S33),S8-Octubre!S33,"")</f>
-        <v>-2082.0299999999997</v>
+        <v>-2313.4399999999996</v>
       </c>
       <c r="T30" s="1">
         <f>IF(ISNUMBER(Octubre!T33),T8-Octubre!T33,"")</f>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="AC30" s="12">
         <f t="shared" si="7"/>
-        <v>-5783.9500000000007</v>
+        <v>-9359.1600000000035</v>
       </c>
     </row>
     <row r="31" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4035,19 +4035,19 @@
       </c>
       <c r="P33" s="12">
         <f t="shared" si="8"/>
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="8"/>
-        <v>42.620000000000346</v>
+        <v>34.420000000000528</v>
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>-8560.2000000000007</v>
+        <v>-10095.800000000003</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
-        <v>679.51000000000067</v>
+        <v>448.10000000000082</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="8"/>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>-13978.46</v>
+        <v>-17553.670000000002</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -13098,7 +13098,10 @@
       <c r="O28" s="35"/>
       <c r="P28" s="35"/>
       <c r="Q28" s="35"/>
-      <c r="R28" s="35"/>
+      <c r="R28" s="35">
+        <f>684+562-11.21-9.21</f>
+        <v>1225.58</v>
+      </c>
       <c r="S28" s="35"/>
       <c r="T28" s="35"/>
       <c r="U28" s="35"/>
@@ -13111,7 +13114,7 @@
       <c r="AB28" s="36"/>
       <c r="AC28" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1225.58</v>
       </c>
       <c r="AD28" s="35"/>
     </row>
@@ -13133,10 +13136,21 @@
       <c r="M29" s="35"/>
       <c r="N29" s="35"/>
       <c r="O29" s="35"/>
-      <c r="P29" s="35"/>
-      <c r="Q29" s="35"/>
-      <c r="R29" s="35"/>
-      <c r="S29" s="35"/>
+      <c r="P29" s="35">
+        <v>1800</v>
+      </c>
+      <c r="Q29" s="35">
+        <f>2550-41.8</f>
+        <v>2508.1999999999998</v>
+      </c>
+      <c r="R29" s="35">
+        <f>315.19-5.17</f>
+        <v>310.02</v>
+      </c>
+      <c r="S29" s="35">
+        <f>234-2.59</f>
+        <v>231.41</v>
+      </c>
       <c r="T29" s="35"/>
       <c r="U29" s="35"/>
       <c r="V29" s="35"/>
@@ -13148,7 +13162,7 @@
       <c r="AB29" s="36"/>
       <c r="AC29" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4849.6299999999992</v>
       </c>
       <c r="AD29" s="35"/>
     </row>
@@ -13325,19 +13339,19 @@
       </c>
       <c r="P33" s="12">
         <f t="shared" si="1"/>
-        <v>1800</v>
-      </c>
-      <c r="Q33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <v>3600</v>
+      </c>
+      <c r="Q33" s="12">
+        <f t="shared" si="1"/>
+        <v>2508.1999999999998</v>
       </c>
       <c r="R33" s="12">
         <f t="shared" si="1"/>
-        <v>25980.160000000003</v>
+        <v>27515.760000000006</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="1"/>
-        <v>4082.0299999999997</v>
+        <v>4313.4399999999996</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="1"/>
@@ -13377,7 +13391,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>190320.09</v>
+        <v>196395.3</v>
       </c>
       <c r="AD33" s="39"/>
     </row>
